--- a/outputs/excel/pronostics_tournoi.xlsx
+++ b/outputs/excel/pronostics_tournoi.xlsx
@@ -32,16 +32,22 @@
     <t>inactivity</t>
   </si>
   <si>
+    <t>CROSNIER Stéphane</t>
+  </si>
+  <si>
     <t>SUYS Olivier</t>
   </si>
   <si>
+    <t>BLAYE Arnaud</t>
+  </si>
+  <si>
     <t>DUMAS Emmanuel</t>
   </si>
   <si>
     <t>LANDEMAINE Thierry</t>
   </si>
   <si>
-    <t>BLAYE Arnaud</t>
+    <t>LECLÈRE Christophe</t>
   </si>
   <si>
     <t>PINEL Florian</t>
@@ -53,55 +59,49 @@
     <t>DURAND Jean-Marc</t>
   </si>
   <si>
-    <t>LECLÈRE Christophe</t>
+    <t>CAMBLONCQ Thierry</t>
+  </si>
+  <si>
+    <t>OLIVIER Philippe</t>
+  </si>
+  <si>
+    <t>BARCET Vincent</t>
+  </si>
+  <si>
+    <t>BROSSEAU Dany</t>
+  </si>
+  <si>
+    <t>RODRIGUES Marvin</t>
+  </si>
+  <si>
+    <t>TRUCCHI Sébastien</t>
+  </si>
+  <si>
+    <t>BERNARD Pierre</t>
   </si>
   <si>
     <t>COSTE Denis</t>
   </si>
   <si>
-    <t>BROSSEAU Dany</t>
-  </si>
-  <si>
-    <t>TRUCCHI Sébastien</t>
-  </si>
-  <si>
-    <t>CAMBLONCQ Thierry</t>
-  </si>
-  <si>
-    <t>BERNARD Pierre</t>
-  </si>
-  <si>
-    <t>OLIVIER Philippe</t>
-  </si>
-  <si>
-    <t>RODRIGUES Marvin</t>
+    <t>ROUX Pierre-Damien</t>
   </si>
   <si>
     <t>BAKAYOKO Ahmed</t>
   </si>
   <si>
-    <t>DUCHAINE Laurent</t>
-  </si>
-  <si>
-    <t>ROUX Pierre-Damien</t>
+    <t>KERBIRIOU Jean-Luc</t>
+  </si>
+  <si>
+    <t>BONTHOUX Julien</t>
+  </si>
+  <si>
+    <t>SUYS Alain</t>
   </si>
   <si>
     <t>ROCCHIA Philippe</t>
   </si>
   <si>
-    <t>KERBIRIOU Jean-Luc</t>
-  </si>
-  <si>
-    <t>BARCET Vincent</t>
-  </si>
-  <si>
-    <t>BARBET Catherine</t>
-  </si>
-  <si>
-    <t>CALAIS Jean-Manuel</t>
-  </si>
-  <si>
-    <t>BONTHOUX Julien</t>
+    <t>FOURY Christian</t>
   </si>
   <si>
     <t>elo_original</t>
@@ -619,13 +619,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>2121</v>
+        <v>2200</v>
       </c>
       <c r="C2">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -633,13 +633,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>2092</v>
+        <v>2195</v>
       </c>
       <c r="C3">
-        <v>354</v>
+        <v>219</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -647,10 +647,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>2078</v>
+        <v>2155</v>
       </c>
       <c r="C4">
-        <v>391</v>
+        <v>526</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>2028</v>
+        <v>2116</v>
       </c>
       <c r="C5">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -675,13 +675,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>2021</v>
+        <v>2097</v>
       </c>
       <c r="C6">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -689,13 +689,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>2013</v>
+        <v>2035</v>
       </c>
       <c r="C7">
-        <v>200</v>
+        <v>449</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -703,13 +703,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>1951</v>
+        <v>2026</v>
       </c>
       <c r="C8">
-        <v>199</v>
+        <v>426</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -717,13 +717,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="1">
-        <v>1933</v>
+        <v>1992</v>
       </c>
       <c r="C9">
-        <v>396</v>
+        <v>220</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -731,13 +731,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1">
-        <v>1923</v>
+        <v>1981</v>
       </c>
       <c r="C10">
-        <v>122</v>
+        <v>245</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -745,13 +745,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="1">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="C11">
-        <v>267</v>
+        <v>172</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -759,10 +759,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="1">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="C12">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -773,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="1">
-        <v>1915</v>
+        <v>1908</v>
       </c>
       <c r="C13">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="1">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="C14">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -801,13 +801,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="1">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="C15">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -818,10 +818,10 @@
         <v>1902</v>
       </c>
       <c r="C16">
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -829,10 +829,10 @@
         <v>19</v>
       </c>
       <c r="B17" s="1">
-        <v>1872</v>
+        <v>1898</v>
       </c>
       <c r="C17">
-        <v>361</v>
+        <v>230</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="1">
-        <v>1868</v>
+        <v>1881</v>
       </c>
       <c r="C18">
-        <v>264</v>
+        <v>151</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -857,13 +857,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="1">
-        <v>1855</v>
+        <v>1871</v>
       </c>
       <c r="C19">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -871,13 +871,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="1">
-        <v>1846</v>
+        <v>1870</v>
       </c>
       <c r="C20">
-        <v>35</v>
+        <v>406</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -885,13 +885,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>1844</v>
+        <v>1863</v>
       </c>
       <c r="C21">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -899,13 +899,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="1">
-        <v>1840</v>
+        <v>1849</v>
       </c>
       <c r="C22">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -913,13 +913,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="1">
-        <v>1834</v>
+        <v>1848</v>
       </c>
       <c r="C23">
-        <v>314</v>
+        <v>128</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -927,13 +927,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="1">
-        <v>1833</v>
+        <v>1846</v>
       </c>
       <c r="C24">
-        <v>215</v>
+        <v>35</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -941,13 +941,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="1">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="C25">
-        <v>138</v>
+        <v>225</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +962,7 @@
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="7.7109375" customWidth="1"/>
@@ -997,19 +997,22 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>2121</v>
+        <v>2200</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2200</v>
       </c>
       <c r="D2" s="1">
-        <v>2121</v>
+        <v>2200</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1017,19 +1020,19 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>2092</v>
+        <v>2195</v>
       </c>
       <c r="D3" s="1">
-        <v>2092</v>
+        <v>2195</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>354</v>
+        <v>219</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1037,16 +1040,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>2078</v>
+        <v>2155</v>
       </c>
       <c r="D4" s="1">
-        <v>2078</v>
+        <v>2155</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>391</v>
+        <v>526</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1057,16 +1060,16 @@
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>2028</v>
+        <v>2116</v>
       </c>
       <c r="D5" s="1">
-        <v>2028</v>
+        <v>2116</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1077,19 +1080,19 @@
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>2021</v>
+        <v>2097</v>
       </c>
       <c r="D6" s="1">
-        <v>2021</v>
+        <v>2097</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>388</v>
+        <v>431</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1097,19 +1100,19 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>2013</v>
+        <v>2035</v>
       </c>
       <c r="D7" s="1">
-        <v>2013</v>
+        <v>2035</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>200</v>
+        <v>449</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1117,19 +1120,19 @@
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>1951</v>
+        <v>2026</v>
       </c>
       <c r="D8" s="1">
-        <v>1951</v>
+        <v>2026</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>199</v>
+        <v>426</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1137,19 +1140,19 @@
         <v>11</v>
       </c>
       <c r="B9" s="1">
-        <v>1933</v>
+        <v>1992</v>
       </c>
       <c r="D9" s="1">
-        <v>1933</v>
+        <v>1992</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>396</v>
+        <v>220</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1157,19 +1160,19 @@
         <v>12</v>
       </c>
       <c r="B10" s="1">
-        <v>1923</v>
+        <v>1981</v>
       </c>
       <c r="D10" s="1">
-        <v>1923</v>
+        <v>1981</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>122</v>
+        <v>245</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1177,19 +1180,19 @@
         <v>13</v>
       </c>
       <c r="B11" s="1">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="D11" s="1">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>267</v>
+        <v>172</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1197,16 +1200,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="1">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D12" s="1">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>286</v>
+        <v>333</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1217,16 +1220,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="1">
-        <v>1915</v>
+        <v>1908</v>
       </c>
       <c r="D13" s="1">
-        <v>1915</v>
+        <v>1908</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1237,16 +1240,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="1">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="D14" s="1">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1257,19 +1260,19 @@
         <v>17</v>
       </c>
       <c r="B15" s="1">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="D15" s="1">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1286,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>199</v>
+        <v>311</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1297,16 +1300,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="1">
-        <v>1872</v>
+        <v>1898</v>
       </c>
       <c r="D17" s="1">
-        <v>1872</v>
+        <v>1898</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>361</v>
+        <v>230</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1317,16 +1320,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="1">
-        <v>1868</v>
+        <v>1881</v>
       </c>
       <c r="D18" s="1">
-        <v>1868</v>
+        <v>1881</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>264</v>
+        <v>151</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1337,19 +1340,19 @@
         <v>21</v>
       </c>
       <c r="B19" s="1">
-        <v>1855</v>
+        <v>1871</v>
       </c>
       <c r="D19" s="1">
-        <v>1855</v>
+        <v>1871</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1357,19 +1360,19 @@
         <v>22</v>
       </c>
       <c r="B20" s="1">
-        <v>1846</v>
+        <v>1870</v>
       </c>
       <c r="D20" s="1">
-        <v>1846</v>
+        <v>1870</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>35</v>
+        <v>406</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1377,19 +1380,19 @@
         <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>1844</v>
+        <v>1863</v>
       </c>
       <c r="D21" s="1">
-        <v>1844</v>
+        <v>1863</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1397,19 +1400,19 @@
         <v>24</v>
       </c>
       <c r="B22" s="1">
-        <v>1840</v>
+        <v>1849</v>
       </c>
       <c r="D22" s="1">
-        <v>1840</v>
+        <v>1849</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1417,19 +1420,19 @@
         <v>25</v>
       </c>
       <c r="B23" s="1">
-        <v>1834</v>
+        <v>1848</v>
       </c>
       <c r="D23" s="1">
-        <v>1834</v>
+        <v>1848</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>314</v>
+        <v>128</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1437,19 +1440,19 @@
         <v>26</v>
       </c>
       <c r="B24" s="1">
-        <v>1833</v>
+        <v>1846</v>
       </c>
       <c r="D24" s="1">
-        <v>1833</v>
+        <v>1846</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>215</v>
+        <v>35</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1457,19 +1460,19 @@
         <v>27</v>
       </c>
       <c r="B25" s="1">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="D25" s="1">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>138</v>
+        <v>225</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1483,7 +1486,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="24" width="21.7109375" style="3" customWidth="1"/>
+    <col min="2" max="22" width="21.7109375" style="3" customWidth="1"/>
+    <col min="23" max="23" width="20.7109375" style="3" customWidth="1"/>
+    <col min="24" max="24" width="21.7109375" style="3" customWidth="1"/>
     <col min="25" max="25" width="20.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1569,73 +1574,73 @@
         <v>4</v>
       </c>
       <c r="C2" s="3">
-        <v>0.5416377027147634</v>
+        <v>0.5071950817090514</v>
       </c>
       <c r="D2" s="3">
-        <v>0.5615679389736461</v>
+        <v>0.5644004902404213</v>
       </c>
       <c r="E2" s="3">
-        <v>0.6307302886162022</v>
+        <v>0.6185841220890307</v>
       </c>
       <c r="F2" s="3">
-        <v>0.6400649998028851</v>
+        <v>0.6440338538222926</v>
       </c>
       <c r="G2" s="3">
-        <v>0.6506046279338725</v>
+        <v>0.7210782431975601</v>
       </c>
       <c r="H2" s="3">
-        <v>0.726830072276731</v>
+        <v>0.7313778578393882</v>
       </c>
       <c r="I2" s="3">
-        <v>0.7469129214289432</v>
+        <v>0.7680520031675839</v>
       </c>
       <c r="J2" s="3">
-        <v>0.7576391748622517</v>
+        <v>0.7791406208194696</v>
       </c>
       <c r="K2" s="3">
-        <v>0.7628849803052542</v>
+        <v>0.8376154583713974</v>
       </c>
       <c r="L2" s="3">
-        <v>0.7649612635526892</v>
+        <v>0.8376154583713974</v>
       </c>
       <c r="M2" s="3">
-        <v>0.7659946707664889</v>
+        <v>0.8430219644140362</v>
       </c>
       <c r="N2" s="3">
-        <v>0.7690759234333929</v>
+        <v>0.8445395282300351</v>
       </c>
       <c r="O2" s="3">
-        <v>0.777153105314726</v>
+        <v>0.8475387239958501</v>
       </c>
       <c r="P2" s="3">
-        <v>0.7791406208194696</v>
+        <v>0.8475387239958501</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.8074241816712792</v>
+        <v>0.8504903015468027</v>
       </c>
       <c r="R2" s="3">
-        <v>0.8109791581199478</v>
+        <v>0.8625119039913111</v>
       </c>
       <c r="S2" s="3">
-        <v>0.8221846111535023</v>
+        <v>0.8691968654550538</v>
       </c>
       <c r="T2" s="3">
-        <v>0.8296328234313434</v>
+        <v>0.8698499490743091</v>
       </c>
       <c r="U2" s="3">
-        <v>0.8312539156520465</v>
+        <v>0.8743442268185462</v>
       </c>
       <c r="V2" s="3">
-        <v>0.834459181708983</v>
+        <v>0.8829346041256821</v>
       </c>
       <c r="W2" s="3">
-        <v>0.8391753178526756</v>
+        <v>0.8835282880564392</v>
       </c>
       <c r="X2" s="3">
-        <v>0.8399506946347535</v>
+        <v>0.8847078164911643</v>
       </c>
       <c r="Y2" s="3">
-        <v>0.8430219644140362</v>
+        <v>0.8926766600061541</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1643,73 +1648,73 @@
         <v>5</v>
       </c>
       <c r="B3" s="3">
-        <v>0.4583622972852365</v>
+        <v>0.4928049182909486</v>
       </c>
       <c r="D3" s="3">
-        <v>0.5201367220358165</v>
+        <v>0.5573116337622928</v>
       </c>
       <c r="E3" s="3">
-        <v>0.5910755963149433</v>
+        <v>0.6117705007810643</v>
       </c>
       <c r="F3" s="3">
-        <v>0.6007782458900109</v>
+        <v>0.6374083767444845</v>
       </c>
       <c r="G3" s="3">
-        <v>0.6117705007810643</v>
+        <v>0.7152527510491987</v>
       </c>
       <c r="H3" s="3">
-        <v>0.6924633925795177</v>
+        <v>0.7256856462717871</v>
       </c>
       <c r="I3" s="3">
-        <v>0.7140789025853503</v>
+        <v>0.7628849803052542</v>
       </c>
       <c r="J3" s="3">
-        <v>0.7256856462717871</v>
+        <v>0.7741479777018306</v>
       </c>
       <c r="K3" s="3">
-        <v>0.7313778578393882</v>
+        <v>0.8336624691834381</v>
       </c>
       <c r="L3" s="3">
-        <v>0.7336337024138074</v>
+        <v>0.8336624691834381</v>
       </c>
       <c r="M3" s="3">
-        <v>0.7347570893165466</v>
+        <v>0.8391753178526756</v>
       </c>
       <c r="N3" s="3">
-        <v>0.7381090325404187</v>
+        <v>0.840723042661615</v>
       </c>
       <c r="O3" s="3">
-        <v>0.7469129214289432</v>
+        <v>0.8437822479242926</v>
       </c>
       <c r="P3" s="3">
-        <v>0.7490830628775357</v>
+        <v>0.8437822479242926</v>
       </c>
       <c r="Q3" s="3">
-        <v>0.7801296039931584</v>
+        <v>0.8467934030726807</v>
       </c>
       <c r="R3" s="3">
-        <v>0.784053683887815</v>
+        <v>0.8590630023766738</v>
       </c>
       <c r="S3" s="3">
-        <v>0.7964546997117258</v>
+        <v>0.8658895824550439</v>
       </c>
       <c r="T3" s="3">
-        <v>0.8047246934992595</v>
+        <v>0.8665566437895401</v>
       </c>
       <c r="U3" s="3">
-        <v>0.8065275228171078</v>
+        <v>0.8711477984045555</v>
       </c>
       <c r="V3" s="3">
-        <v>0.8100951586047567</v>
+        <v>0.8799266880106169</v>
       </c>
       <c r="W3" s="3">
-        <v>0.8153518152833006</v>
+        <v>0.8805335622474012</v>
       </c>
       <c r="X3" s="3">
-        <v>0.8162168965756028</v>
+        <v>0.8817393593419074</v>
       </c>
       <c r="Y3" s="3">
-        <v>0.8196458144946892</v>
+        <v>0.8898878421811328</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1717,73 +1722,73 @@
         <v>6</v>
       </c>
       <c r="B4" s="3">
-        <v>0.438432061026354</v>
+        <v>0.4355995097595788</v>
       </c>
       <c r="C4" s="3">
-        <v>0.4798632779641835</v>
+        <v>0.4426883662377072</v>
       </c>
       <c r="E4" s="3">
-        <v>0.5714631174083814</v>
+        <v>0.5558909611168531</v>
       </c>
       <c r="F4" s="3">
-        <v>0.581301478368915</v>
+        <v>0.5827018849642301</v>
       </c>
       <c r="G4" s="3">
-        <v>0.5924662305843318</v>
+        <v>0.6661394245831221</v>
       </c>
       <c r="H4" s="3">
-        <v>0.6750402010402987</v>
+        <v>0.6775605800851006</v>
       </c>
       <c r="I4" s="3">
-        <v>0.6973450785898532</v>
+        <v>0.718756829898782</v>
       </c>
       <c r="J4" s="3">
-        <v>0.7093546305987634</v>
+        <v>0.7313778578393882</v>
       </c>
       <c r="K4" s="3">
-        <v>0.7152527510491987</v>
+        <v>0.7992399910868982</v>
       </c>
       <c r="L4" s="3">
-        <v>0.7175917231915314</v>
+        <v>0.7992399910868982</v>
       </c>
       <c r="M4" s="3">
-        <v>0.718756829898782</v>
+        <v>0.8056276940436502</v>
       </c>
       <c r="N4" s="3">
-        <v>0.7222345336491706</v>
+        <v>0.8074241816712792</v>
       </c>
       <c r="O4" s="3">
-        <v>0.7313778578393882</v>
+        <v>0.8109791581199478</v>
       </c>
       <c r="P4" s="3">
-        <v>0.7336337024138074</v>
+        <v>0.8109791581199478</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.7659946707664889</v>
+        <v>0.8144835875047122</v>
       </c>
       <c r="R4" s="3">
-        <v>0.770096676660982</v>
+        <v>0.8288176477542757</v>
       </c>
       <c r="S4" s="3">
-        <v>0.7830774434096761</v>
+        <v>0.8368309660028946</v>
       </c>
       <c r="T4" s="3">
-        <v>0.7917488375081845</v>
+        <v>0.8376154583713974</v>
       </c>
       <c r="U4" s="3">
-        <v>0.7936407431881689</v>
+        <v>0.8430219644140362</v>
       </c>
       <c r="V4" s="3">
-        <v>0.7973863140277038</v>
+        <v>0.8533946221118819</v>
       </c>
       <c r="W4" s="3">
-        <v>0.8029091701538159</v>
+        <v>0.8541133619456244</v>
       </c>
       <c r="X4" s="3">
-        <v>0.8038185194246843</v>
+        <v>0.8555420748926974</v>
       </c>
       <c r="Y4" s="3">
-        <v>0.8074241816712792</v>
+        <v>0.8652197052285583</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1791,73 +1796,73 @@
         <v>7</v>
       </c>
       <c r="B5" s="3">
-        <v>0.3692697113837977</v>
+        <v>0.3814158779109693</v>
       </c>
       <c r="C5" s="3">
-        <v>0.4089244036850566</v>
+        <v>0.3882294992189357</v>
       </c>
       <c r="D5" s="3">
-        <v>0.4285368825916186</v>
+        <v>0.4441090388831469</v>
       </c>
       <c r="F5" s="3">
-        <v>0.5100724469274385</v>
+        <v>0.527315973006493</v>
       </c>
       <c r="G5" s="3">
-        <v>0.5215733330511455</v>
+        <v>0.6145013610085578</v>
       </c>
       <c r="H5" s="3">
-        <v>0.6090326034042396</v>
+        <v>0.626699081666732</v>
       </c>
       <c r="I5" s="3">
-        <v>0.6334077000711676</v>
+        <v>0.6712405808158318</v>
       </c>
       <c r="J5" s="3">
-        <v>0.6466688423256146</v>
+        <v>0.6850596089933503</v>
       </c>
       <c r="K5" s="3">
-        <v>0.6532171672188698</v>
+        <v>0.7607960909891424</v>
       </c>
       <c r="L5" s="3">
-        <v>0.655820505912395</v>
+        <v>0.7607960909891424</v>
       </c>
       <c r="M5" s="3">
-        <v>0.6571186864870786</v>
+        <v>0.7680520031675839</v>
       </c>
       <c r="N5" s="3">
-        <v>0.6609990912463583</v>
+        <v>0.770096676660982</v>
       </c>
       <c r="O5" s="3">
-        <v>0.6712405808158318</v>
+        <v>0.7741479777018306</v>
       </c>
       <c r="P5" s="3">
-        <v>0.6737761878883222</v>
+        <v>0.7741479777018306</v>
       </c>
       <c r="Q5" s="3">
-        <v>0.7105400123698378</v>
+        <v>0.7781484542191325</v>
       </c>
       <c r="R5" s="3">
-        <v>0.7152527510491987</v>
+        <v>0.7945819150362295</v>
       </c>
       <c r="S5" s="3">
-        <v>0.730245413297424</v>
+        <v>0.8038185194246843</v>
       </c>
       <c r="T5" s="3">
-        <v>0.7403284195148304</v>
+        <v>0.8047246934992595</v>
       </c>
       <c r="U5" s="3">
-        <v>0.7425355589430698</v>
+        <v>0.8109791581199478</v>
       </c>
       <c r="V5" s="3">
-        <v>0.7469129214289432</v>
+        <v>0.8230246289217321</v>
       </c>
       <c r="W5" s="3">
-        <v>0.7533860777856145</v>
+        <v>0.8238615285055724</v>
       </c>
       <c r="X5" s="3">
-        <v>0.7544540419421866</v>
+        <v>0.8255259873611817</v>
       </c>
       <c r="Y5" s="3">
-        <v>0.7586946201468556</v>
+        <v>0.8368309660028946</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1865,73 +1870,73 @@
         <v>8</v>
       </c>
       <c r="B6" s="3">
-        <v>0.3599350001971149</v>
+        <v>0.3559661461777073</v>
       </c>
       <c r="C6" s="3">
-        <v>0.399221754109989</v>
+        <v>0.3625916232555155</v>
       </c>
       <c r="D6" s="3">
-        <v>0.4186985216310851</v>
+        <v>0.4172981150357699</v>
       </c>
       <c r="E6" s="3">
-        <v>0.4899275530725615</v>
+        <v>0.4726840269935071</v>
       </c>
       <c r="G6" s="3">
-        <v>0.5115108912177917</v>
+        <v>0.5882899718631628</v>
       </c>
       <c r="H6" s="3">
-        <v>0.5993967967092568</v>
+        <v>0.6007782458900109</v>
       </c>
       <c r="I6" s="3">
-        <v>0.6240017586176672</v>
+        <v>0.6466688423256146</v>
       </c>
       <c r="J6" s="3">
-        <v>0.6374083767444845</v>
+        <v>0.6609990912463583</v>
       </c>
       <c r="K6" s="3">
-        <v>0.6440338538222926</v>
+        <v>0.7403284195148304</v>
       </c>
       <c r="L6" s="3">
-        <v>0.6466688423256146</v>
+        <v>0.7403284195148304</v>
       </c>
       <c r="M6" s="3">
-        <v>0.6479830132503057</v>
+        <v>0.7479995411960544</v>
       </c>
       <c r="N6" s="3">
-        <v>0.6519120398746636</v>
+        <v>0.750163481828642</v>
       </c>
       <c r="O6" s="3">
-        <v>0.6622877974308888</v>
+        <v>0.7544540419421866</v>
       </c>
       <c r="P6" s="3">
-        <v>0.6648579785547648</v>
+        <v>0.7544540419421866</v>
       </c>
       <c r="Q6" s="3">
-        <v>0.7021826020905207</v>
+        <v>0.7586946201468556</v>
       </c>
       <c r="R6" s="3">
-        <v>0.7069752948085409</v>
+        <v>0.7761545753418307</v>
       </c>
       <c r="S6" s="3">
-        <v>0.7222345336491706</v>
+        <v>0.7859966022821575</v>
       </c>
       <c r="T6" s="3">
-        <v>0.7325072897556676</v>
+        <v>0.7869632793894692</v>
       </c>
       <c r="U6" s="3">
-        <v>0.7347570893165466</v>
+        <v>0.7936407431881689</v>
       </c>
       <c r="V6" s="3">
-        <v>0.7392202541406678</v>
+        <v>0.8065275228171078</v>
       </c>
       <c r="W6" s="3">
-        <v>0.7458232083504994</v>
+        <v>0.8074241816712792</v>
       </c>
       <c r="X6" s="3">
-        <v>0.7469129214289432</v>
+        <v>0.809207997485838</v>
       </c>
       <c r="Y6" s="3">
-        <v>0.7512407935337106</v>
+        <v>0.821341471737012</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1939,73 +1944,73 @@
         <v>9</v>
       </c>
       <c r="B7" s="3">
-        <v>0.3493953720661275</v>
+        <v>0.2789217568024399</v>
       </c>
       <c r="C7" s="3">
-        <v>0.3882294992189357</v>
+        <v>0.2847472489508014</v>
       </c>
       <c r="D7" s="3">
-        <v>0.4075337694156682</v>
+        <v>0.3338605754168779</v>
       </c>
       <c r="E7" s="3">
-        <v>0.4784266669488546</v>
+        <v>0.3854986389914422</v>
       </c>
       <c r="F7" s="3">
-        <v>0.4884891087822083</v>
+        <v>0.4117100281368372</v>
       </c>
       <c r="H7" s="3">
-        <v>0.5882899718631628</v>
+        <v>0.5129491448928637</v>
       </c>
       <c r="I7" s="3">
-        <v>0.6131368201531431</v>
+        <v>0.5615679389736461</v>
       </c>
       <c r="J7" s="3">
-        <v>0.626699081666732</v>
+        <v>0.577092475825329</v>
       </c>
       <c r="K7" s="3">
-        <v>0.6334077000711676</v>
+        <v>0.6661394245831221</v>
       </c>
       <c r="L7" s="3">
-        <v>0.6360768996878818</v>
+        <v>0.6661394245831221</v>
       </c>
       <c r="M7" s="3">
-        <v>0.6374083767444845</v>
+        <v>0.6750402010402987</v>
       </c>
       <c r="N7" s="3">
-        <v>0.641390111955618</v>
+        <v>0.6775605800851006</v>
       </c>
       <c r="O7" s="3">
-        <v>0.6519120398746636</v>
+        <v>0.6825703854747719</v>
       </c>
       <c r="P7" s="3">
-        <v>0.654519994382466</v>
+        <v>0.6825703854747719</v>
       </c>
       <c r="Q7" s="3">
-        <v>0.6924633925795177</v>
+        <v>0.6875382482123418</v>
       </c>
       <c r="R7" s="3">
-        <v>0.6973450785898532</v>
+        <v>0.7081663882812006</v>
       </c>
       <c r="S7" s="3">
-        <v>0.7129021574054539</v>
+        <v>0.7199190059471519</v>
       </c>
       <c r="T7" s="3">
-        <v>0.7233878694391705</v>
+        <v>0.7210782431975601</v>
       </c>
       <c r="U7" s="3">
-        <v>0.7256856462717871</v>
+        <v>0.7291099628977525</v>
       </c>
       <c r="V7" s="3">
-        <v>0.730245413297424</v>
+        <v>0.7447304068650347</v>
       </c>
       <c r="W7" s="3">
-        <v>0.7369947605406894</v>
+        <v>0.7458232083504994</v>
       </c>
       <c r="X7" s="3">
-        <v>0.7381090325404187</v>
+        <v>0.7479995411960544</v>
       </c>
       <c r="Y7" s="3">
-        <v>0.7425355589430698</v>
+        <v>0.7628849803052542</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -2013,73 +2018,73 @@
         <v>10</v>
       </c>
       <c r="B8" s="3">
-        <v>0.2731699277232689</v>
+        <v>0.2686221421606117</v>
       </c>
       <c r="C8" s="3">
-        <v>0.3075366074204823</v>
+        <v>0.2743143537282129</v>
       </c>
       <c r="D8" s="3">
-        <v>0.3249597989597013</v>
+        <v>0.3224394199148994</v>
       </c>
       <c r="E8" s="3">
-        <v>0.3909673965957605</v>
+        <v>0.373300918333268</v>
       </c>
       <c r="F8" s="3">
-        <v>0.4006032032907432</v>
+        <v>0.399221754109989</v>
       </c>
       <c r="G8" s="3">
-        <v>0.4117100281368372</v>
+        <v>0.4870508551071362</v>
       </c>
       <c r="I8" s="3">
-        <v>0.5258809308911691</v>
+        <v>0.5487743358597419</v>
       </c>
       <c r="J8" s="3">
-        <v>0.5402082283237456</v>
+        <v>0.5644004902404213</v>
       </c>
       <c r="K8" s="3">
-        <v>0.5473485180458647</v>
+        <v>0.654519994382466</v>
       </c>
       <c r="L8" s="3">
-        <v>0.550199353253537</v>
+        <v>0.654519994382466</v>
       </c>
       <c r="M8" s="3">
-        <v>0.5516235473109605</v>
+        <v>0.6635740980412955</v>
       </c>
       <c r="N8" s="3">
-        <v>0.5558909611168531</v>
+        <v>0.6661394245831221</v>
       </c>
       <c r="O8" s="3">
-        <v>0.5672288443429522</v>
+        <v>0.6712405808158318</v>
       </c>
       <c r="P8" s="3">
-        <v>0.5700528235839882</v>
+        <v>0.6712405808158318</v>
       </c>
       <c r="Q8" s="3">
-        <v>0.6117705007810643</v>
+        <v>0.676301669492737</v>
       </c>
       <c r="R8" s="3">
-        <v>0.6172250309049463</v>
+        <v>0.6973450785898532</v>
       </c>
       <c r="S8" s="3">
-        <v>0.6347433350523167</v>
+        <v>0.7093546305987634</v>
       </c>
       <c r="T8" s="3">
-        <v>0.6466688423256146</v>
+        <v>0.7105400123698378</v>
       </c>
       <c r="U8" s="3">
-        <v>0.6492949471109635</v>
+        <v>0.718756829898782</v>
       </c>
       <c r="V8" s="3">
-        <v>0.654519994382466</v>
+        <v>0.7347570893165466</v>
       </c>
       <c r="W8" s="3">
-        <v>0.6622877974308888</v>
+        <v>0.7358774441014764</v>
       </c>
       <c r="X8" s="3">
-        <v>0.6635740980412955</v>
+        <v>0.7381090325404187</v>
       </c>
       <c r="Y8" s="3">
-        <v>0.6686949563073317</v>
+        <v>0.7533860777856145</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -2087,73 +2092,73 @@
         <v>11</v>
       </c>
       <c r="B9" s="3">
-        <v>0.2530870785710568</v>
+        <v>0.231947996832416</v>
       </c>
       <c r="C9" s="3">
-        <v>0.2859210974146497</v>
+        <v>0.2371150196947458</v>
       </c>
       <c r="D9" s="3">
-        <v>0.3026549214101468</v>
+        <v>0.2812431701012181</v>
       </c>
       <c r="E9" s="3">
-        <v>0.3665922999288324</v>
+        <v>0.3287594191841682</v>
       </c>
       <c r="F9" s="3">
-        <v>0.3759982413823328</v>
+        <v>0.3533311576743853</v>
       </c>
       <c r="G9" s="3">
-        <v>0.3868631798468569</v>
+        <v>0.438432061026354</v>
       </c>
       <c r="H9" s="3">
-        <v>0.4741190691088309</v>
+        <v>0.4512256641402582</v>
       </c>
       <c r="J9" s="3">
-        <v>0.5143871841659987</v>
+        <v>0.515824985264735</v>
       </c>
       <c r="K9" s="3">
-        <v>0.5215733330511455</v>
+        <v>0.6090326034042396</v>
       </c>
       <c r="L9" s="3">
-        <v>0.5244454611206615</v>
+        <v>0.6090326034042396</v>
       </c>
       <c r="M9" s="3">
-        <v>0.5258809308911691</v>
+        <v>0.6185841220890307</v>
       </c>
       <c r="N9" s="3">
-        <v>0.5301846800039021</v>
+        <v>0.6212967231224545</v>
       </c>
       <c r="O9" s="3">
-        <v>0.5416377027147634</v>
+        <v>0.626699081666732</v>
       </c>
       <c r="P9" s="3">
-        <v>0.544494573083008</v>
+        <v>0.626699081666732</v>
       </c>
       <c r="Q9" s="3">
-        <v>0.5868950233791</v>
+        <v>0.6320700121000735</v>
       </c>
       <c r="R9" s="3">
-        <v>0.5924662305843318</v>
+        <v>0.654519994382466</v>
       </c>
       <c r="S9" s="3">
-        <v>0.6104024220946891</v>
+        <v>0.667418421873223</v>
       </c>
       <c r="T9" s="3">
-        <v>0.6226501957872621</v>
+        <v>0.6686949563073317</v>
       </c>
       <c r="U9" s="3">
-        <v>0.6253513933075368</v>
+        <v>0.6775605800851006</v>
       </c>
       <c r="V9" s="3">
-        <v>0.6307302886162022</v>
+        <v>0.6949097127295025</v>
       </c>
       <c r="W9" s="3">
-        <v>0.6387377491117249</v>
+        <v>0.6961287704295998</v>
       </c>
       <c r="X9" s="3">
-        <v>0.6400649998028851</v>
+        <v>0.698558626418023</v>
       </c>
       <c r="Y9" s="3">
-        <v>0.6453524504393825</v>
+        <v>0.7152527510491987</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -2161,73 +2166,73 @@
         <v>12</v>
       </c>
       <c r="B10" s="3">
-        <v>0.2423608251377483</v>
+        <v>0.2208593791805304</v>
       </c>
       <c r="C10" s="3">
-        <v>0.2743143537282129</v>
+        <v>0.2258520222981694</v>
       </c>
       <c r="D10" s="3">
-        <v>0.2906453694012366</v>
+        <v>0.2686221421606117</v>
       </c>
       <c r="E10" s="3">
-        <v>0.3533311576743853</v>
+        <v>0.3149403910066497</v>
       </c>
       <c r="F10" s="3">
-        <v>0.3625916232555155</v>
+        <v>0.3390009087536417</v>
       </c>
       <c r="G10" s="3">
-        <v>0.373300918333268</v>
+        <v>0.422907524174671</v>
       </c>
       <c r="H10" s="3">
-        <v>0.4597917716762543</v>
+        <v>0.4355995097595788</v>
       </c>
       <c r="I10" s="3">
-        <v>0.4856128158340013</v>
+        <v>0.4841750147352649</v>
       </c>
       <c r="K10" s="3">
-        <v>0.5071950817090514</v>
+        <v>0.5938553852361779</v>
       </c>
       <c r="L10" s="3">
-        <v>0.5100724469274385</v>
+        <v>0.5938553852361779</v>
       </c>
       <c r="M10" s="3">
-        <v>0.5115108912177917</v>
+        <v>0.6035363185261781</v>
       </c>
       <c r="N10" s="3">
-        <v>0.515824985264735</v>
+        <v>0.6062878237854281</v>
       </c>
       <c r="O10" s="3">
-        <v>0.527315973006493</v>
+        <v>0.6117705007810643</v>
       </c>
       <c r="P10" s="3">
-        <v>0.5301846800039021</v>
+        <v>0.6117705007810643</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.5728722513945045</v>
+        <v>0.6172250309049463</v>
       </c>
       <c r="R10" s="3">
-        <v>0.5784967523447427</v>
+        <v>0.6400649998028851</v>
       </c>
       <c r="S10" s="3">
-        <v>0.596629173305774</v>
+        <v>0.6532171672188698</v>
       </c>
       <c r="T10" s="3">
-        <v>0.6090326034042396</v>
+        <v>0.654519994382466</v>
       </c>
       <c r="U10" s="3">
-        <v>0.6117705007810643</v>
+        <v>0.6635740980412955</v>
       </c>
       <c r="V10" s="3">
-        <v>0.6172250309049463</v>
+        <v>0.6813218351663937</v>
       </c>
       <c r="W10" s="3">
-        <v>0.6253513933075368</v>
+        <v>0.6825703854747719</v>
       </c>
       <c r="X10" s="3">
-        <v>0.626699081666732</v>
+        <v>0.6850596089933503</v>
       </c>
       <c r="Y10" s="3">
-        <v>0.6320700121000735</v>
+        <v>0.7021826020905207</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -2235,73 +2240,73 @@
         <v>13</v>
       </c>
       <c r="B11" s="3">
-        <v>0.2371150196947458</v>
+        <v>0.1623845416286026</v>
       </c>
       <c r="C11" s="3">
-        <v>0.2686221421606117</v>
+        <v>0.1663375308165619</v>
       </c>
       <c r="D11" s="3">
-        <v>0.2847472489508014</v>
+        <v>0.2007600089131018</v>
       </c>
       <c r="E11" s="3">
-        <v>0.3467828327811303</v>
+        <v>0.2392039090108577</v>
       </c>
       <c r="F11" s="3">
-        <v>0.3559661461777073</v>
+        <v>0.2596715804851696</v>
       </c>
       <c r="G11" s="3">
-        <v>0.3665922999288324</v>
+        <v>0.3338605754168779</v>
       </c>
       <c r="H11" s="3">
-        <v>0.4526514819541353</v>
+        <v>0.3454800056175341</v>
       </c>
       <c r="I11" s="3">
-        <v>0.4784266669488546</v>
+        <v>0.3909673965957605</v>
       </c>
       <c r="J11" s="3">
-        <v>0.4928049182909486</v>
+        <v>0.4061446147638222</v>
       </c>
       <c r="L11" s="3">
-        <v>0.5028781995748109</v>
+        <v>0.5</v>
       </c>
       <c r="M11" s="3">
-        <v>0.5043172397550598</v>
+        <v>0.5100724469274385</v>
       </c>
       <c r="N11" s="3">
-        <v>0.5086338358210827</v>
+        <v>0.5129491448928637</v>
       </c>
       <c r="O11" s="3">
-        <v>0.5201367220358165</v>
+        <v>0.5186997779295586</v>
       </c>
       <c r="P11" s="3">
-        <v>0.5230095872975623</v>
+        <v>0.5186997779295586</v>
       </c>
       <c r="Q11" s="3">
-        <v>0.5658152030692333</v>
+        <v>0.5244454611206615</v>
       </c>
       <c r="R11" s="3">
-        <v>0.5714631174083814</v>
+        <v>0.5487743358597419</v>
       </c>
       <c r="S11" s="3">
-        <v>0.5896835031399501</v>
+        <v>0.5629847281035958</v>
       </c>
       <c r="T11" s="3">
-        <v>0.6021580931747169</v>
+        <v>0.5644004902404213</v>
       </c>
       <c r="U11" s="3">
-        <v>0.6049129020079569</v>
+        <v>0.5742802036545245</v>
       </c>
       <c r="V11" s="3">
-        <v>0.6104024220946891</v>
+        <v>0.5938553852361779</v>
       </c>
       <c r="W11" s="3">
-        <v>0.6185841220890307</v>
+        <v>0.5952430396515719</v>
       </c>
       <c r="X11" s="3">
-        <v>0.6199413590445233</v>
+        <v>0.5980137657693436</v>
       </c>
       <c r="Y11" s="3">
-        <v>0.6253513933075368</v>
+        <v>0.6172250309049463</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -2309,73 +2314,73 @@
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>0.2350387364473108</v>
+        <v>0.1623845416286026</v>
       </c>
       <c r="C12" s="3">
-        <v>0.2663662975861926</v>
+        <v>0.1663375308165619</v>
       </c>
       <c r="D12" s="3">
-        <v>0.2824082768084685</v>
+        <v>0.2007600089131018</v>
       </c>
       <c r="E12" s="3">
-        <v>0.344179494087605</v>
+        <v>0.2392039090108577</v>
       </c>
       <c r="F12" s="3">
-        <v>0.3533311576743853</v>
+        <v>0.2596715804851696</v>
       </c>
       <c r="G12" s="3">
-        <v>0.3639231003121181</v>
+        <v>0.3338605754168779</v>
       </c>
       <c r="H12" s="3">
-        <v>0.449800646746463</v>
+        <v>0.3454800056175341</v>
       </c>
       <c r="I12" s="3">
-        <v>0.4755545388793386</v>
+        <v>0.3909673965957605</v>
       </c>
       <c r="J12" s="3">
-        <v>0.4899275530725615</v>
+        <v>0.4061446147638222</v>
       </c>
       <c r="K12" s="3">
-        <v>0.4971218004251891</v>
+        <v>0.5</v>
       </c>
       <c r="M12" s="3">
-        <v>0.5014391117091528</v>
+        <v>0.5100724469274385</v>
       </c>
       <c r="N12" s="3">
-        <v>0.5057562084111449</v>
+        <v>0.5129491448928637</v>
       </c>
       <c r="O12" s="3">
-        <v>0.5172625244323762</v>
+        <v>0.5186997779295586</v>
       </c>
       <c r="P12" s="3">
-        <v>0.5201367220358165</v>
+        <v>0.5186997779295586</v>
       </c>
       <c r="Q12" s="3">
+        <v>0.5244454611206615</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0.5487743358597419</v>
+      </c>
+      <c r="S12" s="3">
         <v>0.5629847281035958</v>
       </c>
-      <c r="R12" s="3">
-        <v>0.5686413918836677</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0.5868950233791</v>
-      </c>
       <c r="T12" s="3">
-        <v>0.5993967967092568</v>
+        <v>0.5644004902404213</v>
       </c>
       <c r="U12" s="3">
-        <v>0.6021580931747169</v>
+        <v>0.5742802036545245</v>
       </c>
       <c r="V12" s="3">
-        <v>0.6076610641268197</v>
+        <v>0.5938553852361779</v>
       </c>
       <c r="W12" s="3">
-        <v>0.615864104253756</v>
+        <v>0.5952430396515719</v>
       </c>
       <c r="X12" s="3">
+        <v>0.5980137657693436</v>
+      </c>
+      <c r="Y12" s="3">
         <v>0.6172250309049463</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>0.6226501957872621</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2383,73 +2388,73 @@
         <v>15</v>
       </c>
       <c r="B13" s="3">
-        <v>0.2340053292335112</v>
+        <v>0.1569780355859638</v>
       </c>
       <c r="C13" s="3">
-        <v>0.2652429106834533</v>
+        <v>0.1608246821473244</v>
       </c>
       <c r="D13" s="3">
-        <v>0.2812431701012181</v>
+        <v>0.1943723059563498</v>
       </c>
       <c r="E13" s="3">
-        <v>0.3428813135129214</v>
+        <v>0.231947996832416</v>
       </c>
       <c r="F13" s="3">
-        <v>0.3520169867496943</v>
+        <v>0.2520004588039456</v>
       </c>
       <c r="G13" s="3">
-        <v>0.3625916232555155</v>
+        <v>0.3249597989597013</v>
       </c>
       <c r="H13" s="3">
-        <v>0.4483764526890395</v>
+        <v>0.3364259019587045</v>
       </c>
       <c r="I13" s="3">
-        <v>0.4741190691088309</v>
+        <v>0.3814158779109693</v>
       </c>
       <c r="J13" s="3">
-        <v>0.4884891087822083</v>
+        <v>0.3964636814738219</v>
       </c>
       <c r="K13" s="3">
-        <v>0.4956827602449402</v>
+        <v>0.4899275530725615</v>
       </c>
       <c r="L13" s="3">
-        <v>0.4985608882908471</v>
+        <v>0.4899275530725615</v>
       </c>
       <c r="N13" s="3">
-        <v>0.5043172397550598</v>
+        <v>0.5028781995748109</v>
       </c>
       <c r="O13" s="3">
-        <v>0.515824985264735</v>
+        <v>0.5086338358210827</v>
       </c>
       <c r="P13" s="3">
-        <v>0.5186997779295586</v>
+        <v>0.5086338358210827</v>
       </c>
       <c r="Q13" s="3">
-        <v>0.5615679389736461</v>
+        <v>0.5143871841659987</v>
       </c>
       <c r="R13" s="3">
-        <v>0.5672288443429522</v>
+        <v>0.5387780920571715</v>
       </c>
       <c r="S13" s="3">
+        <v>0.5530468951694625</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0.554469374021676</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0.5644004902404213</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.584100958813678</v>
+      </c>
+      <c r="W13" s="3">
         <v>0.5854986786718095</v>
       </c>
-      <c r="T13" s="3">
-        <v>0.5980137657693436</v>
-      </c>
-      <c r="U13" s="3">
-        <v>0.6007782458900109</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0.6062878237854281</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0.6145013610085578</v>
-      </c>
       <c r="X13" s="3">
-        <v>0.615864104253756</v>
+        <v>0.5882899718631628</v>
       </c>
       <c r="Y13" s="3">
-        <v>0.6212967231224545</v>
+        <v>0.6076610641268197</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2457,73 +2462,73 @@
         <v>16</v>
       </c>
       <c r="B14" s="3">
-        <v>0.2309240765666072</v>
+        <v>0.1554604717699649</v>
       </c>
       <c r="C14" s="3">
-        <v>0.2618909674595814</v>
+        <v>0.159276957338385</v>
       </c>
       <c r="D14" s="3">
-        <v>0.2777654663508294</v>
+        <v>0.1925758183287208</v>
       </c>
       <c r="E14" s="3">
-        <v>0.3390009087536417</v>
+        <v>0.229903323339018</v>
       </c>
       <c r="F14" s="3">
-        <v>0.3480879601253363</v>
+        <v>0.249836518171358</v>
       </c>
       <c r="G14" s="3">
-        <v>0.358609888044382</v>
+        <v>0.3224394199148994</v>
       </c>
       <c r="H14" s="3">
-        <v>0.4441090388831469</v>
+        <v>0.3338605754168779</v>
       </c>
       <c r="I14" s="3">
-        <v>0.469815319996098</v>
+        <v>0.3787032768775454</v>
       </c>
       <c r="J14" s="3">
-        <v>0.4841750147352649</v>
+        <v>0.3937121762145718</v>
       </c>
       <c r="K14" s="3">
-        <v>0.4913661641789174</v>
+        <v>0.4870508551071362</v>
       </c>
       <c r="L14" s="3">
-        <v>0.4942437915888551</v>
+        <v>0.4870508551071362</v>
       </c>
       <c r="M14" s="3">
-        <v>0.4956827602449402</v>
+        <v>0.4971218004251891</v>
       </c>
       <c r="O14" s="3">
+        <v>0.5057562084111449</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0.5057562084111449</v>
+      </c>
+      <c r="Q14" s="3">
         <v>0.5115108912177917</v>
       </c>
-      <c r="P14" s="3">
-        <v>0.5143871841659987</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0.5573116337622928</v>
-      </c>
       <c r="R14" s="3">
-        <v>0.5629847281035958</v>
+        <v>0.5359159269451023</v>
       </c>
       <c r="S14" s="3">
+        <v>0.550199353253537</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0.5516235473109605</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0.5615679389736461</v>
+      </c>
+      <c r="V14" s="3">
         <v>0.581301478368915</v>
       </c>
-      <c r="T14" s="3">
-        <v>0.5938553852361779</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0.596629173305774</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0.6021580931747169</v>
-      </c>
       <c r="W14" s="3">
-        <v>0.6104024220946891</v>
+        <v>0.5827018849642301</v>
       </c>
       <c r="X14" s="3">
-        <v>0.6117705007810643</v>
+        <v>0.5854986786718095</v>
       </c>
       <c r="Y14" s="3">
-        <v>0.6172250309049463</v>
+        <v>0.6049129020079569</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2531,73 +2536,73 @@
         <v>17</v>
       </c>
       <c r="B15" s="3">
-        <v>0.222846894685274</v>
+        <v>0.15246127600415</v>
       </c>
       <c r="C15" s="3">
-        <v>0.2530870785710568</v>
+        <v>0.1562177520757074</v>
       </c>
       <c r="D15" s="3">
-        <v>0.2686221421606117</v>
+        <v>0.1890208418800522</v>
       </c>
       <c r="E15" s="3">
+        <v>0.2258520222981694</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.2455459580578135</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.3174296145252281</v>
+      </c>
+      <c r="H15" s="3">
         <v>0.3287594191841682</v>
       </c>
-      <c r="F15" s="3">
-        <v>0.3377122025691112</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0.3480879601253363</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.4327711556570478</v>
-      </c>
       <c r="I15" s="3">
-        <v>0.4583622972852365</v>
+        <v>0.373300918333268</v>
       </c>
       <c r="J15" s="3">
-        <v>0.4726840269935071</v>
+        <v>0.3882294992189357</v>
       </c>
       <c r="K15" s="3">
-        <v>0.4798632779641835</v>
+        <v>0.4813002220704414</v>
       </c>
       <c r="L15" s="3">
-        <v>0.4827374755676238</v>
+        <v>0.4813002220704414</v>
       </c>
       <c r="M15" s="3">
-        <v>0.4841750147352649</v>
+        <v>0.4913661641789174</v>
       </c>
       <c r="N15" s="3">
-        <v>0.4884891087822083</v>
+        <v>0.4942437915888551</v>
       </c>
       <c r="P15" s="3">
-        <v>0.5028781995748109</v>
+        <v>0.5</v>
       </c>
       <c r="Q15" s="3">
+        <v>0.5057562084111449</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0.5301846800039021</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0.544494573083008</v>
+      </c>
+      <c r="T15" s="3">
         <v>0.5459219227804837</v>
       </c>
-      <c r="R15" s="3">
-        <v>0.5516235473109605</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0.5700528235839882</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0.5827018849642301</v>
-      </c>
       <c r="U15" s="3">
-        <v>0.5854986786718095</v>
+        <v>0.5558909611168531</v>
       </c>
       <c r="V15" s="3">
-        <v>0.5910755963149433</v>
+        <v>0.5756869523764296</v>
       </c>
       <c r="W15" s="3">
+        <v>0.577092475825329</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0.5798997603578815</v>
+      </c>
+      <c r="Y15" s="3">
         <v>0.5993967967092568</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0.6007782458900109</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0.6062878237854281</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2605,73 +2610,73 @@
         <v>18</v>
       </c>
       <c r="B16" s="3">
-        <v>0.2208593791805304</v>
+        <v>0.15246127600415</v>
       </c>
       <c r="C16" s="3">
-        <v>0.2509169371224644</v>
+        <v>0.1562177520757074</v>
       </c>
       <c r="D16" s="3">
-        <v>0.2663662975861926</v>
+        <v>0.1890208418800522</v>
       </c>
       <c r="E16" s="3">
-        <v>0.3262238121116778</v>
+        <v>0.2258520222981694</v>
       </c>
       <c r="F16" s="3">
-        <v>0.3351420214452352</v>
+        <v>0.2455459580578135</v>
       </c>
       <c r="G16" s="3">
-        <v>0.3454800056175341</v>
+        <v>0.3174296145252281</v>
       </c>
       <c r="H16" s="3">
-        <v>0.4299471764160118</v>
+        <v>0.3287594191841682</v>
       </c>
       <c r="I16" s="3">
-        <v>0.4555054269169921</v>
+        <v>0.373300918333268</v>
       </c>
       <c r="J16" s="3">
-        <v>0.469815319996098</v>
+        <v>0.3882294992189357</v>
       </c>
       <c r="K16" s="3">
-        <v>0.4769904127024377</v>
+        <v>0.4813002220704414</v>
       </c>
       <c r="L16" s="3">
-        <v>0.4798632779641835</v>
+        <v>0.4813002220704414</v>
       </c>
       <c r="M16" s="3">
-        <v>0.4813002220704414</v>
+        <v>0.4913661641789174</v>
       </c>
       <c r="N16" s="3">
-        <v>0.4856128158340013</v>
+        <v>0.4942437915888551</v>
       </c>
       <c r="O16" s="3">
-        <v>0.4971218004251891</v>
+        <v>0.5</v>
       </c>
       <c r="Q16" s="3">
-        <v>0.5430664920222119</v>
+        <v>0.5057562084111449</v>
       </c>
       <c r="R16" s="3">
-        <v>0.5487743358597419</v>
+        <v>0.5301846800039021</v>
       </c>
       <c r="S16" s="3">
-        <v>0.5672288443429522</v>
+        <v>0.544494573083008</v>
       </c>
       <c r="T16" s="3">
+        <v>0.5459219227804837</v>
+      </c>
+      <c r="U16" s="3">
+        <v>0.5558909611168531</v>
+      </c>
+      <c r="V16" s="3">
+        <v>0.5756869523764296</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0.577092475825329</v>
+      </c>
+      <c r="X16" s="3">
         <v>0.5798997603578815</v>
       </c>
-      <c r="U16" s="3">
-        <v>0.5827018849642301</v>
-      </c>
-      <c r="V16" s="3">
-        <v>0.5882899718631628</v>
-      </c>
-      <c r="W16" s="3">
-        <v>0.596629173305774</v>
-      </c>
-      <c r="X16" s="3">
-        <v>0.5980137657693436</v>
-      </c>
       <c r="Y16" s="3">
-        <v>0.6035363185261781</v>
+        <v>0.5993967967092568</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2679,73 +2684,73 @@
         <v>19</v>
       </c>
       <c r="B17" s="3">
-        <v>0.1925758183287208</v>
+        <v>0.1495096984531974</v>
       </c>
       <c r="C17" s="3">
-        <v>0.2198703960068415</v>
+        <v>0.1532065969273193</v>
       </c>
       <c r="D17" s="3">
-        <v>0.2340053292335112</v>
+        <v>0.1855164124952878</v>
       </c>
       <c r="E17" s="3">
-        <v>0.2894599876301622</v>
+        <v>0.2218515457808675</v>
       </c>
       <c r="F17" s="3">
-        <v>0.2978173979094794</v>
+        <v>0.2413053798531443</v>
       </c>
       <c r="G17" s="3">
-        <v>0.3075366074204823</v>
+        <v>0.3124617517876582</v>
       </c>
       <c r="H17" s="3">
-        <v>0.3882294992189357</v>
+        <v>0.3236983305072631</v>
       </c>
       <c r="I17" s="3">
-        <v>0.4131049766209</v>
+        <v>0.3679299878999264</v>
       </c>
       <c r="J17" s="3">
-        <v>0.4271277486054956</v>
+        <v>0.3827749690950537</v>
       </c>
       <c r="K17" s="3">
-        <v>0.4341847969307668</v>
+        <v>0.4755545388793386</v>
       </c>
       <c r="L17" s="3">
-        <v>0.4370152718964042</v>
+        <v>0.4755545388793386</v>
       </c>
       <c r="M17" s="3">
-        <v>0.438432061026354</v>
+        <v>0.4856128158340013</v>
       </c>
       <c r="N17" s="3">
-        <v>0.4426883662377072</v>
+        <v>0.4884891087822083</v>
       </c>
       <c r="O17" s="3">
-        <v>0.4540780772195163</v>
+        <v>0.4942437915888551</v>
       </c>
       <c r="P17" s="3">
-        <v>0.4569335079777882</v>
+        <v>0.4942437915888551</v>
       </c>
       <c r="R17" s="3">
-        <v>0.5057562084111449</v>
+        <v>0.5244454611206615</v>
       </c>
       <c r="S17" s="3">
-        <v>0.5244454611206615</v>
+        <v>0.5387780920571715</v>
       </c>
       <c r="T17" s="3">
-        <v>0.5373473171664928</v>
+        <v>0.5402082283237456</v>
       </c>
       <c r="U17" s="3">
-        <v>0.5402082283237456</v>
+        <v>0.550199353253537</v>
       </c>
       <c r="V17" s="3">
-        <v>0.5459219227804837</v>
+        <v>0.5700528235839882</v>
       </c>
       <c r="W17" s="3">
-        <v>0.554469374021676</v>
+        <v>0.5714631174083814</v>
       </c>
       <c r="X17" s="3">
-        <v>0.5558909611168531</v>
+        <v>0.5742802036545245</v>
       </c>
       <c r="Y17" s="3">
-        <v>0.5615679389736461</v>
+        <v>0.5938553852361779</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2753,73 +2758,73 @@
         <v>20</v>
       </c>
       <c r="B18" s="3">
-        <v>0.1890208418800522</v>
+        <v>0.1374880960086889</v>
       </c>
       <c r="C18" s="3">
-        <v>0.2159463161121849</v>
+        <v>0.1409369976233262</v>
       </c>
       <c r="D18" s="3">
-        <v>0.229903323339018</v>
+        <v>0.1711823522457242</v>
       </c>
       <c r="E18" s="3">
-        <v>0.2847472489508014</v>
+        <v>0.2054180849637705</v>
       </c>
       <c r="F18" s="3">
-        <v>0.293024705191459</v>
+        <v>0.2238454246581693</v>
       </c>
       <c r="G18" s="3">
+        <v>0.2918336117187994</v>
+      </c>
+      <c r="H18" s="3">
         <v>0.3026549214101468</v>
       </c>
-      <c r="H18" s="3">
-        <v>0.3827749690950537</v>
-      </c>
       <c r="I18" s="3">
-        <v>0.4075337694156682</v>
+        <v>0.3454800056175341</v>
       </c>
       <c r="J18" s="3">
-        <v>0.4215032476552573</v>
+        <v>0.3599350001971149</v>
       </c>
       <c r="K18" s="3">
-        <v>0.4285368825916186</v>
+        <v>0.4512256641402582</v>
       </c>
       <c r="L18" s="3">
-        <v>0.4313586081163324</v>
+        <v>0.4512256641402582</v>
       </c>
       <c r="M18" s="3">
-        <v>0.4327711556570478</v>
+        <v>0.4612219079428285</v>
       </c>
       <c r="N18" s="3">
-        <v>0.4370152718964042</v>
+        <v>0.4640840730548977</v>
       </c>
       <c r="O18" s="3">
-        <v>0.4483764526890395</v>
+        <v>0.469815319996098</v>
       </c>
       <c r="P18" s="3">
-        <v>0.4512256641402582</v>
+        <v>0.469815319996098</v>
       </c>
       <c r="Q18" s="3">
-        <v>0.4942437915888551</v>
+        <v>0.4755545388793386</v>
       </c>
       <c r="S18" s="3">
-        <v>0.5186997779295586</v>
+        <v>0.5143871841659987</v>
       </c>
       <c r="T18" s="3">
-        <v>0.5316182978281073</v>
+        <v>0.515824985264735</v>
       </c>
       <c r="U18" s="3">
-        <v>0.5344839447268315</v>
+        <v>0.5258809308911691</v>
       </c>
       <c r="V18" s="3">
-        <v>0.5402082283237456</v>
+        <v>0.5459219227804837</v>
       </c>
       <c r="W18" s="3">
-        <v>0.5487743358597419</v>
+        <v>0.5473485180458647</v>
       </c>
       <c r="X18" s="3">
         <v>0.550199353253537</v>
       </c>
       <c r="Y18" s="3">
-        <v>0.5558909611168531</v>
+        <v>0.5700528235839882</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2827,73 +2832,73 @@
         <v>21</v>
       </c>
       <c r="B19" s="3">
-        <v>0.1778153888464977</v>
+        <v>0.1308031345449462</v>
       </c>
       <c r="C19" s="3">
-        <v>0.2035453002882742</v>
+        <v>0.1341104175449561</v>
       </c>
       <c r="D19" s="3">
-        <v>0.2169225565903239</v>
+        <v>0.1631690339971053</v>
       </c>
       <c r="E19" s="3">
-        <v>0.269754586702576</v>
+        <v>0.1961814805753157</v>
       </c>
       <c r="F19" s="3">
-        <v>0.2777654663508294</v>
+        <v>0.2140033977178425</v>
       </c>
       <c r="G19" s="3">
-        <v>0.287097842594546</v>
+        <v>0.2800809940528481</v>
       </c>
       <c r="H19" s="3">
-        <v>0.3652566649476832</v>
+        <v>0.2906453694012366</v>
       </c>
       <c r="I19" s="3">
-        <v>0.389597577905311</v>
+        <v>0.332581578126777</v>
       </c>
       <c r="J19" s="3">
-        <v>0.403370826694226</v>
+        <v>0.3467828327811303</v>
       </c>
       <c r="K19" s="3">
-        <v>0.41031649686005</v>
+        <v>0.4370152718964042</v>
       </c>
       <c r="L19" s="3">
-        <v>0.4131049766209</v>
+        <v>0.4370152718964042</v>
       </c>
       <c r="M19" s="3">
-        <v>0.4145013213281905</v>
+        <v>0.4469531048305375</v>
       </c>
       <c r="N19" s="3">
-        <v>0.4186985216310851</v>
+        <v>0.449800646746463</v>
       </c>
       <c r="O19" s="3">
-        <v>0.4299471764160118</v>
+        <v>0.4555054269169921</v>
       </c>
       <c r="P19" s="3">
-        <v>0.4327711556570478</v>
+        <v>0.4555054269169921</v>
       </c>
       <c r="Q19" s="3">
-        <v>0.4755545388793386</v>
+        <v>0.4612219079428285</v>
       </c>
       <c r="R19" s="3">
-        <v>0.4813002220704414</v>
+        <v>0.4856128158340013</v>
       </c>
       <c r="T19" s="3">
-        <v>0.5129491448928637</v>
+        <v>0.5014391117091528</v>
       </c>
       <c r="U19" s="3">
-        <v>0.515824985264735</v>
+        <v>0.5115108912177917</v>
       </c>
       <c r="V19" s="3">
-        <v>0.5215733330511455</v>
+        <v>0.5316182978281073</v>
       </c>
       <c r="W19" s="3">
-        <v>0.5301846800039021</v>
+        <v>0.5330513938844411</v>
       </c>
       <c r="X19" s="3">
-        <v>0.5316182978281073</v>
+        <v>0.5359159269451023</v>
       </c>
       <c r="Y19" s="3">
-        <v>0.5373473171664928</v>
+        <v>0.5558909611168531</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2901,73 +2906,73 @@
         <v>22</v>
       </c>
       <c r="B20" s="3">
-        <v>0.1703671765686566</v>
+        <v>0.1301500509256908</v>
       </c>
       <c r="C20" s="3">
+        <v>0.1334433562104599</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.1623845416286026</v>
+      </c>
+      <c r="E20" s="3">
         <v>0.1952753065007406</v>
       </c>
-      <c r="D20" s="3">
-        <v>0.2082511624918156</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0.2596715804851696</v>
-      </c>
       <c r="F20" s="3">
-        <v>0.2674927102443324</v>
+        <v>0.2130367206105308</v>
       </c>
       <c r="G20" s="3">
-        <v>0.2766121305608295</v>
+        <v>0.2789217568024399</v>
       </c>
       <c r="H20" s="3">
-        <v>0.3533311576743853</v>
+        <v>0.2894599876301622</v>
       </c>
       <c r="I20" s="3">
-        <v>0.3773498042127379</v>
+        <v>0.3313050436926683</v>
       </c>
       <c r="J20" s="3">
-        <v>0.3909673965957605</v>
+        <v>0.3454800056175341</v>
       </c>
       <c r="K20" s="3">
-        <v>0.397841906825283</v>
+        <v>0.4355995097595788</v>
       </c>
       <c r="L20" s="3">
-        <v>0.4006032032907432</v>
+        <v>0.4355995097595788</v>
       </c>
       <c r="M20" s="3">
-        <v>0.4019862342306564</v>
+        <v>0.4455306259783239</v>
       </c>
       <c r="N20" s="3">
-        <v>0.4061446147638222</v>
+        <v>0.4483764526890395</v>
       </c>
       <c r="O20" s="3">
-        <v>0.4172981150357699</v>
+        <v>0.4540780772195163</v>
       </c>
       <c r="P20" s="3">
-        <v>0.4201002396421186</v>
+        <v>0.4540780772195163</v>
       </c>
       <c r="Q20" s="3">
-        <v>0.4626526828335072</v>
+        <v>0.4597917716762543</v>
       </c>
       <c r="R20" s="3">
-        <v>0.4683817021718927</v>
+        <v>0.4841750147352649</v>
       </c>
       <c r="S20" s="3">
-        <v>0.4870508551071362</v>
+        <v>0.4985608882908471</v>
       </c>
       <c r="U20" s="3">
-        <v>0.5028781995748109</v>
+        <v>0.5100724469274385</v>
       </c>
       <c r="V20" s="3">
-        <v>0.5086338358210827</v>
+        <v>0.5301846800039021</v>
       </c>
       <c r="W20" s="3">
-        <v>0.5172625244323762</v>
+        <v>0.5316182978281073</v>
       </c>
       <c r="X20" s="3">
-        <v>0.5186997779295586</v>
+        <v>0.5344839447268315</v>
       </c>
       <c r="Y20" s="3">
-        <v>0.5244454611206615</v>
+        <v>0.554469374021676</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2975,73 +2980,73 @@
         <v>23</v>
       </c>
       <c r="B21" s="3">
-        <v>0.1687460843479534</v>
+        <v>0.1256557731814538</v>
       </c>
       <c r="C21" s="3">
-        <v>0.1934724771828921</v>
+        <v>0.1288522015954445</v>
       </c>
       <c r="D21" s="3">
+        <v>0.1569780355859638</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.1890208418800522</v>
+      </c>
+      <c r="F21" s="3">
         <v>0.2063592568118311</v>
       </c>
-      <c r="E21" s="3">
-        <v>0.2574644410569302</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0.2652429106834533</v>
-      </c>
       <c r="G21" s="3">
-        <v>0.2743143537282129</v>
+        <v>0.2708900371022475</v>
       </c>
       <c r="H21" s="3">
-        <v>0.3507050528890364</v>
+        <v>0.2812431701012181</v>
       </c>
       <c r="I21" s="3">
-        <v>0.3746486066924632</v>
+        <v>0.3224394199148994</v>
       </c>
       <c r="J21" s="3">
-        <v>0.3882294992189357</v>
+        <v>0.3364259019587045</v>
       </c>
       <c r="K21" s="3">
-        <v>0.3950870979920432</v>
+        <v>0.4257197963454756</v>
       </c>
       <c r="L21" s="3">
-        <v>0.397841906825283</v>
+        <v>0.4257197963454756</v>
       </c>
       <c r="M21" s="3">
-        <v>0.399221754109989</v>
+        <v>0.4355995097595788</v>
       </c>
       <c r="N21" s="3">
-        <v>0.403370826694226</v>
+        <v>0.438432061026354</v>
       </c>
       <c r="O21" s="3">
-        <v>0.4145013213281905</v>
+        <v>0.4441090388831469</v>
       </c>
       <c r="P21" s="3">
-        <v>0.4172981150357699</v>
+        <v>0.4441090388831469</v>
       </c>
       <c r="Q21" s="3">
-        <v>0.4597917716762543</v>
+        <v>0.449800646746463</v>
       </c>
       <c r="R21" s="3">
-        <v>0.4655160552731685</v>
+        <v>0.4741190691088309</v>
       </c>
       <c r="S21" s="3">
-        <v>0.4841750147352649</v>
+        <v>0.4884891087822083</v>
       </c>
       <c r="T21" s="3">
-        <v>0.4971218004251891</v>
+        <v>0.4899275530725615</v>
       </c>
       <c r="V21" s="3">
-        <v>0.5057562084111449</v>
+        <v>0.5201367220358165</v>
       </c>
       <c r="W21" s="3">
-        <v>0.5143871841659987</v>
+        <v>0.5215733330511455</v>
       </c>
       <c r="X21" s="3">
-        <v>0.515824985264735</v>
+        <v>0.5244454611206615</v>
       </c>
       <c r="Y21" s="3">
-        <v>0.5215733330511455</v>
+        <v>0.544494573083008</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -3049,73 +3054,73 @@
         <v>24</v>
       </c>
       <c r="B22" s="3">
-        <v>0.1655408182910169</v>
+        <v>0.1170653958743179</v>
       </c>
       <c r="C22" s="3">
-        <v>0.1899048413952433</v>
+        <v>0.1200733119893831</v>
       </c>
       <c r="D22" s="3">
-        <v>0.2026136859722963</v>
+        <v>0.1466053778881182</v>
       </c>
       <c r="E22" s="3">
-        <v>0.2530870785710568</v>
+        <v>0.1769753710782679</v>
       </c>
       <c r="F22" s="3">
-        <v>0.2607797458593321</v>
+        <v>0.1934724771828921</v>
       </c>
       <c r="G22" s="3">
-        <v>0.269754586702576</v>
+        <v>0.2552695931349653</v>
       </c>
       <c r="H22" s="3">
-        <v>0.3454800056175341</v>
+        <v>0.2652429106834533</v>
       </c>
       <c r="I22" s="3">
-        <v>0.3692697113837977</v>
+        <v>0.3050902872704974</v>
       </c>
       <c r="J22" s="3">
-        <v>0.3827749690950537</v>
+        <v>0.3186781648336063</v>
       </c>
       <c r="K22" s="3">
-        <v>0.389597577905311</v>
+        <v>0.4061446147638222</v>
       </c>
       <c r="L22" s="3">
-        <v>0.3923389358731801</v>
+        <v>0.4061446147638222</v>
       </c>
       <c r="M22" s="3">
-        <v>0.3937121762145718</v>
+        <v>0.415899041186322</v>
       </c>
       <c r="N22" s="3">
-        <v>0.397841906825283</v>
+        <v>0.4186985216310851</v>
       </c>
       <c r="O22" s="3">
-        <v>0.4089244036850566</v>
+        <v>0.4243130476235704</v>
       </c>
       <c r="P22" s="3">
-        <v>0.4117100281368372</v>
+        <v>0.4243130476235704</v>
       </c>
       <c r="Q22" s="3">
+        <v>0.4299471764160118</v>
+      </c>
+      <c r="R22" s="3">
         <v>0.4540780772195163</v>
       </c>
-      <c r="R22" s="3">
-        <v>0.4597917716762543</v>
-      </c>
       <c r="S22" s="3">
-        <v>0.4784266669488546</v>
+        <v>0.4683817021718927</v>
       </c>
       <c r="T22" s="3">
-        <v>0.4913661641789174</v>
+        <v>0.469815319996098</v>
       </c>
       <c r="U22" s="3">
-        <v>0.4942437915888551</v>
+        <v>0.4798632779641835</v>
       </c>
       <c r="W22" s="3">
-        <v>0.5086338358210827</v>
+        <v>0.5014391117091528</v>
       </c>
       <c r="X22" s="3">
-        <v>0.5100724469274385</v>
+        <v>0.5043172397550598</v>
       </c>
       <c r="Y22" s="3">
-        <v>0.515824985264735</v>
+        <v>0.5244454611206615</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -3123,73 +3128,73 @@
         <v>25</v>
       </c>
       <c r="B23" s="3">
-        <v>0.1608246821473244</v>
+        <v>0.1164717119435607</v>
       </c>
       <c r="C23" s="3">
-        <v>0.1846481847166994</v>
+        <v>0.1194664377525988</v>
       </c>
       <c r="D23" s="3">
-        <v>0.1970908298461841</v>
+        <v>0.1458866380543756</v>
       </c>
       <c r="E23" s="3">
-        <v>0.2466139222143855</v>
+        <v>0.1761384714944276</v>
       </c>
       <c r="F23" s="3">
+        <v>0.1925758183287208</v>
+      </c>
+      <c r="G23" s="3">
         <v>0.2541767916495005</v>
       </c>
-      <c r="G23" s="3">
-        <v>0.2630052394593107</v>
-      </c>
       <c r="H23" s="3">
-        <v>0.3377122025691112</v>
+        <v>0.2641225558985236</v>
       </c>
       <c r="I23" s="3">
-        <v>0.3612622508882752</v>
+        <v>0.3038712295704002</v>
       </c>
       <c r="J23" s="3">
-        <v>0.3746486066924632</v>
+        <v>0.3174296145252281</v>
       </c>
       <c r="K23" s="3">
-        <v>0.3814158779109693</v>
+        <v>0.4047569603484281</v>
       </c>
       <c r="L23" s="3">
-        <v>0.384135895746244</v>
+        <v>0.4047569603484281</v>
       </c>
       <c r="M23" s="3">
-        <v>0.3854986389914422</v>
+        <v>0.4145013213281905</v>
       </c>
       <c r="N23" s="3">
-        <v>0.389597577905311</v>
+        <v>0.4172981150357699</v>
       </c>
       <c r="O23" s="3">
-        <v>0.4006032032907432</v>
+        <v>0.422907524174671</v>
       </c>
       <c r="P23" s="3">
-        <v>0.403370826694226</v>
+        <v>0.422907524174671</v>
       </c>
       <c r="Q23" s="3">
-        <v>0.4455306259783239</v>
+        <v>0.4285368825916186</v>
       </c>
       <c r="R23" s="3">
-        <v>0.4512256641402582</v>
+        <v>0.4526514819541353</v>
       </c>
       <c r="S23" s="3">
-        <v>0.469815319996098</v>
+        <v>0.4669486061155589</v>
       </c>
       <c r="T23" s="3">
-        <v>0.4827374755676238</v>
+        <v>0.4683817021718927</v>
       </c>
       <c r="U23" s="3">
-        <v>0.4856128158340013</v>
+        <v>0.4784266669488546</v>
       </c>
       <c r="V23" s="3">
-        <v>0.4913661641789174</v>
+        <v>0.4985608882908471</v>
       </c>
       <c r="X23" s="3">
-        <v>0.5014391117091528</v>
+        <v>0.5028781995748109</v>
       </c>
       <c r="Y23" s="3">
-        <v>0.5071950817090514</v>
+        <v>0.5230095872975623</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -3197,73 +3202,73 @@
         <v>26</v>
       </c>
       <c r="B24" s="3">
-        <v>0.1600493053652466</v>
+        <v>0.1152921835088358</v>
       </c>
       <c r="C24" s="3">
-        <v>0.1837831034243972</v>
+        <v>0.1182606406580926</v>
       </c>
       <c r="D24" s="3">
-        <v>0.1961814805753157</v>
+        <v>0.1444579251073025</v>
       </c>
       <c r="E24" s="3">
-        <v>0.2455459580578135</v>
+        <v>0.1744740126388183</v>
       </c>
       <c r="F24" s="3">
-        <v>0.2530870785710568</v>
+        <v>0.1907920025141619</v>
       </c>
       <c r="G24" s="3">
+        <v>0.2520004588039456</v>
+      </c>
+      <c r="H24" s="3">
         <v>0.2618909674595814</v>
       </c>
-      <c r="H24" s="3">
-        <v>0.3364259019587045</v>
-      </c>
       <c r="I24" s="3">
-        <v>0.3599350001971149</v>
+        <v>0.301441373581977</v>
       </c>
       <c r="J24" s="3">
-        <v>0.373300918333268</v>
+        <v>0.3149403910066497</v>
       </c>
       <c r="K24" s="3">
-        <v>0.3800586409554767</v>
+        <v>0.4019862342306564</v>
       </c>
       <c r="L24" s="3">
-        <v>0.3827749690950537</v>
+        <v>0.4019862342306564</v>
       </c>
       <c r="M24" s="3">
-        <v>0.384135895746244</v>
+        <v>0.4117100281368372</v>
       </c>
       <c r="N24" s="3">
-        <v>0.3882294992189357</v>
+        <v>0.4145013213281905</v>
       </c>
       <c r="O24" s="3">
-        <v>0.399221754109989</v>
+        <v>0.4201002396421186</v>
       </c>
       <c r="P24" s="3">
-        <v>0.4019862342306564</v>
+        <v>0.4201002396421186</v>
       </c>
       <c r="Q24" s="3">
-        <v>0.4441090388831469</v>
+        <v>0.4257197963454756</v>
       </c>
       <c r="R24" s="3">
         <v>0.449800646746463</v>
       </c>
       <c r="S24" s="3">
-        <v>0.4683817021718927</v>
+        <v>0.4640840730548977</v>
       </c>
       <c r="T24" s="3">
-        <v>0.4813002220704414</v>
+        <v>0.4655160552731685</v>
       </c>
       <c r="U24" s="3">
-        <v>0.4841750147352649</v>
+        <v>0.4755545388793386</v>
       </c>
       <c r="V24" s="3">
-        <v>0.4899275530725615</v>
+        <v>0.4956827602449402</v>
       </c>
       <c r="W24" s="3">
-        <v>0.4985608882908471</v>
+        <v>0.4971218004251891</v>
       </c>
       <c r="Y24" s="3">
-        <v>0.5057562084111449</v>
+        <v>0.5201367220358165</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -3271,73 +3276,73 @@
         <v>27</v>
       </c>
       <c r="B25" s="3">
-        <v>0.1569780355859638</v>
+        <v>0.1073233399938459</v>
       </c>
       <c r="C25" s="3">
-        <v>0.1803541855053107</v>
+        <v>0.1101121578188672</v>
       </c>
       <c r="D25" s="3">
-        <v>0.1925758183287208</v>
+        <v>0.1347802947714417</v>
       </c>
       <c r="E25" s="3">
-        <v>0.2413053798531443</v>
+        <v>0.1631690339971053</v>
       </c>
       <c r="F25" s="3">
-        <v>0.2487592064662893</v>
+        <v>0.178658528262988</v>
       </c>
       <c r="G25" s="3">
-        <v>0.2574644410569302</v>
+        <v>0.2371150196947458</v>
       </c>
       <c r="H25" s="3">
-        <v>0.3313050436926683</v>
+        <v>0.2466139222143855</v>
       </c>
       <c r="I25" s="3">
-        <v>0.3546475495606176</v>
+        <v>0.2847472489508014</v>
       </c>
       <c r="J25" s="3">
-        <v>0.3679299878999264</v>
+        <v>0.2978173979094794</v>
       </c>
       <c r="K25" s="3">
-        <v>0.3746486066924632</v>
+        <v>0.3827749690950537</v>
       </c>
       <c r="L25" s="3">
-        <v>0.3773498042127379</v>
+        <v>0.3827749690950537</v>
       </c>
       <c r="M25" s="3">
-        <v>0.3787032768775454</v>
+        <v>0.3923389358731801</v>
       </c>
       <c r="N25" s="3">
-        <v>0.3827749690950537</v>
+        <v>0.3950870979920432</v>
       </c>
       <c r="O25" s="3">
-        <v>0.3937121762145718</v>
+        <v>0.4006032032907432</v>
       </c>
       <c r="P25" s="3">
-        <v>0.3964636814738219</v>
+        <v>0.4006032032907432</v>
       </c>
       <c r="Q25" s="3">
-        <v>0.438432061026354</v>
+        <v>0.4061446147638222</v>
       </c>
       <c r="R25" s="3">
+        <v>0.4299471764160118</v>
+      </c>
+      <c r="S25" s="3">
         <v>0.4441090388831469</v>
       </c>
-      <c r="S25" s="3">
-        <v>0.4626526828335072</v>
-      </c>
       <c r="T25" s="3">
+        <v>0.4455306259783239</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0.4555054269169921</v>
+      </c>
+      <c r="V25" s="3">
         <v>0.4755545388793386</v>
       </c>
-      <c r="U25" s="3">
-        <v>0.4784266669488546</v>
-      </c>
-      <c r="V25" s="3">
-        <v>0.4841750147352649</v>
-      </c>
       <c r="W25" s="3">
-        <v>0.4928049182909486</v>
+        <v>0.4769904127024377</v>
       </c>
       <c r="X25" s="3">
-        <v>0.4942437915888551</v>
+        <v>0.4798632779641835</v>
       </c>
     </row>
   </sheetData>
@@ -3389,19 +3394,19 @@
         <v>4</v>
       </c>
       <c r="C2" s="1">
-        <v>2121</v>
+        <v>2200</v>
       </c>
       <c r="D2">
         <v>23</v>
       </c>
       <c r="E2" s="1">
-        <v>17.33328013943989</v>
+        <v>18.26197274582883</v>
       </c>
       <c r="F2" s="1">
-        <v>34.66656027887977</v>
+        <v>36.52394549165766</v>
       </c>
       <c r="G2" s="1">
-        <v>1.507241751255642</v>
+        <v>1.587997630072072</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3412,19 +3417,19 @@
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>2092</v>
+        <v>2195</v>
       </c>
       <c r="D3">
         <v>23</v>
       </c>
       <c r="E3" s="1">
-        <v>16.58142485902778</v>
+        <v>18.15359246151616</v>
       </c>
       <c r="F3" s="1">
-        <v>33.16284971805556</v>
+        <v>36.30718492303232</v>
       </c>
       <c r="G3" s="1">
-        <v>1.441863031219807</v>
+        <v>1.578573257523145</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3435,19 +3440,19 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>2078</v>
+        <v>2155</v>
       </c>
       <c r="D4">
         <v>23</v>
       </c>
       <c r="E4" s="1">
-        <v>16.20021003043394</v>
+        <v>17.23324497683946</v>
       </c>
       <c r="F4" s="1">
-        <v>32.40042006086788</v>
+        <v>34.46648995367892</v>
       </c>
       <c r="G4" s="1">
-        <v>1.408713915689908</v>
+        <v>1.498543041464301</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3458,19 +3463,19 @@
         <v>7</v>
       </c>
       <c r="C5" s="1">
-        <v>2028</v>
+        <v>2116</v>
       </c>
       <c r="D5">
         <v>23</v>
       </c>
       <c r="E5" s="1">
-        <v>14.7520079594869</v>
+        <v>16.24810368980516</v>
       </c>
       <c r="F5" s="1">
-        <v>29.50401591897379</v>
+        <v>32.49620737961033</v>
       </c>
       <c r="G5" s="1">
-        <v>1.282783300824947</v>
+        <v>1.412878581722188</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3481,19 +3486,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="1">
-        <v>2021</v>
+        <v>2097</v>
       </c>
       <c r="D6">
         <v>23</v>
       </c>
       <c r="E6" s="1">
-        <v>14.53969816463275</v>
+        <v>15.7389550027861</v>
       </c>
       <c r="F6" s="1">
-        <v>29.0793963292655</v>
+        <v>31.47791000557219</v>
       </c>
       <c r="G6" s="1">
-        <v>1.264321579533283</v>
+        <v>1.368604782850965</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3504,19 +3509,19 @@
         <v>9</v>
       </c>
       <c r="C7" s="1">
-        <v>2013</v>
+        <v>2035</v>
       </c>
       <c r="D7">
         <v>23</v>
       </c>
       <c r="E7" s="1">
-        <v>14.2945843224385</v>
+        <v>13.96361819448427</v>
       </c>
       <c r="F7" s="1">
-        <v>28.58916864487699</v>
+        <v>27.92723638896855</v>
       </c>
       <c r="G7" s="1">
-        <v>1.243007332385956</v>
+        <v>1.214227669085589</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3527,19 +3532,19 @@
         <v>10</v>
       </c>
       <c r="C8" s="1">
-        <v>1951</v>
+        <v>2026</v>
       </c>
       <c r="D8">
         <v>23</v>
       </c>
       <c r="E8" s="1">
-        <v>12.32615967133275</v>
+        <v>13.69378680716932</v>
       </c>
       <c r="F8" s="1">
-        <v>24.6523193426655</v>
+        <v>27.38757361433865</v>
       </c>
       <c r="G8" s="1">
-        <v>1.071839971420239</v>
+        <v>1.190764070188637</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3550,19 +3555,19 @@
         <v>11</v>
       </c>
       <c r="C9" s="1">
-        <v>1933</v>
+        <v>1992</v>
       </c>
       <c r="D9">
         <v>23</v>
       </c>
       <c r="E9" s="1">
-        <v>11.74049050581647</v>
+        <v>12.65433751464623</v>
       </c>
       <c r="F9" s="1">
-        <v>23.48098101163294</v>
+        <v>25.30867502929246</v>
       </c>
       <c r="G9" s="1">
-        <v>1.020912217897084</v>
+        <v>1.100377175186628</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3573,19 +3578,19 @@
         <v>12</v>
       </c>
       <c r="C10" s="1">
-        <v>1923</v>
+        <v>1981</v>
       </c>
       <c r="D10">
         <v>23</v>
       </c>
       <c r="E10" s="1">
-        <v>11.41419969237965</v>
+        <v>12.31276852849071</v>
       </c>
       <c r="F10" s="1">
-        <v>22.82839938475929</v>
+        <v>24.62553705698141</v>
       </c>
       <c r="G10" s="1">
-        <v>0.9925391036851867</v>
+        <v>1.070675524216583</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3596,19 +3601,19 @@
         <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="D11">
         <v>23</v>
       </c>
       <c r="E11" s="1">
-        <v>11.25099645670812</v>
+        <v>10.24445375146869</v>
       </c>
       <c r="F11" s="1">
-        <v>22.50199291341623</v>
+        <v>20.48890750293739</v>
       </c>
       <c r="G11" s="1">
-        <v>0.9783475179746187</v>
+        <v>0.8908220653451038</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3619,19 +3624,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="1">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D12">
         <v>23</v>
       </c>
       <c r="E12" s="1">
-        <v>11.18572259695124</v>
+        <v>10.24445375146869</v>
       </c>
       <c r="F12" s="1">
-        <v>22.37144519390249</v>
+        <v>20.48890750293739</v>
       </c>
       <c r="G12" s="1">
-        <v>0.9726715301696734</v>
+        <v>0.8908220653451038</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3642,19 +3647,19 @@
         <v>15</v>
       </c>
       <c r="C13" s="1">
-        <v>1915</v>
+        <v>1908</v>
       </c>
       <c r="D13">
         <v>23</v>
       </c>
       <c r="E13" s="1">
-        <v>11.15308910141949</v>
+        <v>10.0260224261215</v>
       </c>
       <c r="F13" s="1">
-        <v>22.30617820283898</v>
+        <v>20.05204485224299</v>
       </c>
       <c r="G13" s="1">
-        <v>0.9698338349060427</v>
+        <v>0.8718280370540432</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3665,19 +3670,19 @@
         <v>16</v>
       </c>
       <c r="C14" s="1">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="D14">
         <v>23</v>
       </c>
       <c r="E14" s="1">
-        <v>11.05520787804356</v>
+        <v>9.963737066547042</v>
       </c>
       <c r="F14" s="1">
-        <v>22.11041575608713</v>
+        <v>19.92747413309408</v>
       </c>
       <c r="G14" s="1">
-        <v>0.9613224241777011</v>
+        <v>0.8664119188301775</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3688,19 +3693,19 @@
         <v>17</v>
       </c>
       <c r="C15" s="1">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="D15">
         <v>23</v>
       </c>
       <c r="E15" s="1">
-        <v>10.79441357386655</v>
+        <v>9.839352032150439</v>
       </c>
       <c r="F15" s="1">
-        <v>21.58882714773311</v>
+        <v>19.67870406430088</v>
       </c>
       <c r="G15" s="1">
-        <v>0.9386446585970916</v>
+        <v>0.8555958288826468</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3717,13 +3722,13 @@
         <v>23</v>
       </c>
       <c r="E16" s="1">
-        <v>10.72928545240046</v>
+        <v>9.839352032150439</v>
       </c>
       <c r="F16" s="1">
-        <v>21.45857090480093</v>
+        <v>19.67870406430088</v>
       </c>
       <c r="G16" s="1">
-        <v>0.9329813436869968</v>
+        <v>0.8555958288826468</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3734,19 +3739,19 @@
         <v>19</v>
       </c>
       <c r="C17" s="1">
-        <v>1872</v>
+        <v>1898</v>
       </c>
       <c r="D17">
         <v>23</v>
       </c>
       <c r="E17" s="1">
-        <v>9.758667254177768</v>
+        <v>9.715235922990503</v>
       </c>
       <c r="F17" s="1">
-        <v>19.51733450835554</v>
+        <v>19.43047184598101</v>
       </c>
       <c r="G17" s="1">
-        <v>0.8485797612328494</v>
+        <v>0.8448031237383047</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3757,19 +3762,19 @@
         <v>20</v>
       </c>
       <c r="C18" s="1">
-        <v>1868</v>
+        <v>1881</v>
       </c>
       <c r="D18">
         <v>23</v>
       </c>
       <c r="E18" s="1">
-        <v>9.630512068767572</v>
+        <v>9.19133270057883</v>
       </c>
       <c r="F18" s="1">
-        <v>19.26102413753514</v>
+        <v>18.38266540115766</v>
       </c>
       <c r="G18" s="1">
-        <v>0.8374358320667454</v>
+        <v>0.7992463217894634</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3780,19 +3785,19 @@
         <v>21</v>
       </c>
       <c r="C19" s="1">
-        <v>1855</v>
+        <v>1871</v>
       </c>
       <c r="D19">
         <v>23</v>
       </c>
       <c r="E19" s="1">
-        <v>9.216818378590578</v>
+        <v>8.886414694424229</v>
       </c>
       <c r="F19" s="1">
-        <v>18.43363675718116</v>
+        <v>17.77282938884846</v>
       </c>
       <c r="G19" s="1">
-        <v>0.8014624677035285</v>
+        <v>0.7727317125586286</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3803,19 +3808,19 @@
         <v>22</v>
       </c>
       <c r="C20" s="1">
-        <v>1846</v>
+        <v>1870</v>
       </c>
       <c r="D20">
         <v>23</v>
       </c>
       <c r="E20" s="1">
-        <v>8.933297778113847</v>
+        <v>8.856075440454706</v>
       </c>
       <c r="F20" s="1">
-        <v>17.86659555622769</v>
+        <v>17.71215088090941</v>
       </c>
       <c r="G20" s="1">
-        <v>0.7768085024446824</v>
+        <v>0.7700935165612788</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3826,19 +3831,19 @@
         <v>23</v>
       </c>
       <c r="C21" s="1">
-        <v>1844</v>
+        <v>1863</v>
       </c>
       <c r="D21">
         <v>23</v>
       </c>
       <c r="E21" s="1">
-        <v>8.870650057600111</v>
+        <v>8.644540346375688</v>
       </c>
       <c r="F21" s="1">
-        <v>17.74130011520022</v>
+        <v>17.28908069275138</v>
       </c>
       <c r="G21" s="1">
-        <v>0.7713608745739227</v>
+        <v>0.7516991605544077</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3849,19 +3854,19 @@
         <v>24</v>
       </c>
       <c r="C22" s="1">
-        <v>1840</v>
+        <v>1849</v>
       </c>
       <c r="D22">
         <v>23</v>
       </c>
       <c r="E22" s="1">
-        <v>8.745768211153798</v>
+        <v>8.226273143880269</v>
       </c>
       <c r="F22" s="1">
-        <v>17.4915364223076</v>
+        <v>16.45254628776054</v>
       </c>
       <c r="G22" s="1">
-        <v>0.7605015835785912</v>
+        <v>0.7153280994678495</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3872,19 +3877,19 @@
         <v>25</v>
       </c>
       <c r="C23" s="1">
-        <v>1834</v>
+        <v>1848</v>
       </c>
       <c r="D23">
         <v>23</v>
       </c>
       <c r="E23" s="1">
-        <v>8.559526989835616</v>
+        <v>8.196661689572776</v>
       </c>
       <c r="F23" s="1">
-        <v>17.11905397967123</v>
+        <v>16.39332337914555</v>
       </c>
       <c r="G23" s="1">
-        <v>0.7443066947683145</v>
+        <v>0.7127531903976327</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3895,19 +3900,19 @@
         <v>26</v>
       </c>
       <c r="C24" s="1">
-        <v>1833</v>
+        <v>1846</v>
       </c>
       <c r="D24">
         <v>23</v>
       </c>
       <c r="E24" s="1">
-        <v>8.528617981680616</v>
+        <v>8.137550645495232</v>
       </c>
       <c r="F24" s="1">
-        <v>17.05723596336123</v>
+        <v>16.27510129099046</v>
       </c>
       <c r="G24" s="1">
-        <v>0.7416189549287493</v>
+        <v>0.707613099608281</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3918,19 +3923,19 @@
         <v>27</v>
       </c>
       <c r="C25" s="1">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="D25">
         <v>23</v>
       </c>
       <c r="E25" s="1">
-        <v>8.405370875702035</v>
+        <v>7.728164434754732</v>
       </c>
       <c r="F25" s="1">
-        <v>16.81074175140407</v>
+        <v>15.45632886950946</v>
       </c>
       <c r="G25" s="1">
-        <v>0.7309018152784378</v>
+        <v>0.6720142986743245</v>
       </c>
     </row>
   </sheetData>
@@ -3949,7 +3954,9 @@
     <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
     <col min="5" max="28" width="7.7109375" style="3" customWidth="1"/>
     <col min="29" max="29" width="8.7109375" style="3" customWidth="1"/>
-    <col min="30" max="34" width="22.7109375" style="3" customWidth="1"/>
+    <col min="30" max="30" width="21.7109375" style="3" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" style="3" customWidth="1"/>
+    <col min="32" max="34" width="22.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -4061,58 +4068,58 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>2121</v>
+        <v>2200</v>
       </c>
       <c r="C2" s="1">
-        <v>34.772</v>
+        <v>36.562</v>
       </c>
       <c r="D2" s="1">
-        <v>17.386</v>
+        <v>18.281</v>
       </c>
       <c r="E2" s="3">
-        <v>0.474</v>
+        <v>0.444</v>
       </c>
       <c r="F2" s="3">
-        <v>0.238</v>
+        <v>0.24</v>
       </c>
       <c r="G2" s="3">
-        <v>0.12</v>
+        <v>0.168</v>
       </c>
       <c r="H2" s="3">
-        <v>0.073</v>
+        <v>0.077</v>
       </c>
       <c r="I2" s="3">
-        <v>0.045</v>
+        <v>0.038</v>
       </c>
       <c r="J2" s="3">
-        <v>0.018</v>
+        <v>0.024</v>
       </c>
       <c r="K2" s="3">
         <v>0.007</v>
       </c>
       <c r="L2" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="M2" s="3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="P2" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="R2" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="S2" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="T2" s="3">
         <v>0</v>
@@ -4142,22 +4149,22 @@
         <v>0</v>
       </c>
       <c r="AC2" s="3">
-        <v>0.474</v>
+        <v>0.444</v>
       </c>
       <c r="AD2" s="3">
-        <v>0.712</v>
+        <v>0.6839999999999999</v>
       </c>
       <c r="AE2" s="3">
-        <v>0.832</v>
+        <v>0.852</v>
       </c>
       <c r="AF2" s="3">
-        <v>0.9049999999999999</v>
+        <v>0.9289999999999999</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.95</v>
+        <v>0.967</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.984</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -4165,61 +4172,61 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>2092</v>
+        <v>2195</v>
       </c>
       <c r="C3" s="1">
-        <v>33.18</v>
+        <v>36.41</v>
       </c>
       <c r="D3" s="1">
-        <v>16.59</v>
+        <v>18.205</v>
       </c>
       <c r="E3" s="3">
-        <v>0.236</v>
+        <v>0.318</v>
       </c>
       <c r="F3" s="3">
-        <v>0.282</v>
+        <v>0.322</v>
       </c>
       <c r="G3" s="3">
-        <v>0.176</v>
+        <v>0.181</v>
       </c>
       <c r="H3" s="3">
-        <v>0.115</v>
+        <v>0.093</v>
       </c>
       <c r="I3" s="3">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="J3" s="3">
-        <v>0.043</v>
+        <v>0.023</v>
       </c>
       <c r="K3" s="3">
-        <v>0.034</v>
+        <v>0.006</v>
       </c>
       <c r="L3" s="3">
-        <v>0.022</v>
+        <v>0.005</v>
       </c>
       <c r="M3" s="3">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="N3" s="3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="O3" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="P3" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
       </c>
       <c r="S3" s="3">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="T3" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="U3" s="3">
         <v>0</v>
@@ -4246,22 +4253,22 @@
         <v>0</v>
       </c>
       <c r="AC3" s="3">
-        <v>0.236</v>
+        <v>0.318</v>
       </c>
       <c r="AD3" s="3">
-        <v>0.518</v>
+        <v>0.64</v>
       </c>
       <c r="AE3" s="3">
-        <v>0.694</v>
+        <v>0.821</v>
       </c>
       <c r="AF3" s="3">
-        <v>0.8089999999999999</v>
+        <v>0.9139999999999999</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.879</v>
+        <v>0.965</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.9780000000000001</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -4269,70 +4276,70 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>2078</v>
+        <v>2155</v>
       </c>
       <c r="C4" s="1">
-        <v>32.182</v>
+        <v>34.334</v>
       </c>
       <c r="D4" s="1">
-        <v>16.091</v>
+        <v>17.167</v>
       </c>
       <c r="E4" s="3">
-        <v>0.149</v>
+        <v>0.147</v>
       </c>
       <c r="F4" s="3">
+        <v>0.204</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.234</v>
+      </c>
+      <c r="H4" s="3">
         <v>0.198</v>
       </c>
-      <c r="G4" s="3">
-        <v>0.227</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.151</v>
-      </c>
       <c r="I4" s="3">
-        <v>0.109</v>
+        <v>0.103</v>
       </c>
       <c r="J4" s="3">
-        <v>0.047</v>
+        <v>0.057</v>
       </c>
       <c r="K4" s="3">
-        <v>0.038</v>
+        <v>0.025</v>
       </c>
       <c r="L4" s="3">
-        <v>0.024</v>
+        <v>0.013</v>
       </c>
       <c r="M4" s="3">
-        <v>0.021</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="N4" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.003</v>
       </c>
       <c r="O4" s="3">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="P4" s="3">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="R4" s="3">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="S4" s="3">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3">
         <v>0.001</v>
       </c>
-      <c r="T4" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0</v>
-      </c>
       <c r="V4" s="3">
         <v>0</v>
       </c>
       <c r="W4" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="X4" s="3">
         <v>0</v>
@@ -4350,22 +4357,22 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3">
-        <v>0.149</v>
+        <v>0.147</v>
       </c>
       <c r="AD4" s="3">
-        <v>0.347</v>
+        <v>0.351</v>
       </c>
       <c r="AE4" s="3">
-        <v>0.574</v>
+        <v>0.585</v>
       </c>
       <c r="AF4" s="3">
-        <v>0.725</v>
+        <v>0.7829999999999999</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.834</v>
+        <v>0.8859999999999999</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.9430000000000001</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -4373,79 +4380,79 @@
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>2028</v>
+        <v>2116</v>
       </c>
       <c r="C5" s="1">
-        <v>29.56</v>
+        <v>32.458</v>
       </c>
       <c r="D5" s="1">
-        <v>14.78</v>
+        <v>16.229</v>
       </c>
       <c r="E5" s="3">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="F5" s="3">
-        <v>0.106</v>
+        <v>0.121</v>
       </c>
       <c r="G5" s="3">
-        <v>0.127</v>
+        <v>0.183</v>
       </c>
       <c r="H5" s="3">
-        <v>0.179</v>
+        <v>0.239</v>
       </c>
       <c r="I5" s="3">
-        <v>0.13</v>
+        <v>0.158</v>
       </c>
       <c r="J5" s="3">
-        <v>0.125</v>
+        <v>0.111</v>
       </c>
       <c r="K5" s="3">
-        <v>0.076</v>
+        <v>0.067</v>
       </c>
       <c r="L5" s="3">
-        <v>0.043</v>
+        <v>0.024</v>
       </c>
       <c r="M5" s="3">
-        <v>0.042</v>
+        <v>0.019</v>
       </c>
       <c r="N5" s="3">
-        <v>0.029</v>
+        <v>0.015</v>
       </c>
       <c r="O5" s="3">
-        <v>0.036</v>
+        <v>0.006</v>
       </c>
       <c r="P5" s="3">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="Q5" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="R5" s="3">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="T5" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="U5" s="3">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="V5" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="X5" s="3">
         <v>0</v>
       </c>
       <c r="Y5" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AA5" s="3">
         <v>0</v>
@@ -4454,22 +4461,22 @@
         <v>0</v>
       </c>
       <c r="AC5" s="3">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="AD5" s="3">
-        <v>0.158</v>
+        <v>0.171</v>
       </c>
       <c r="AE5" s="3">
-        <v>0.285</v>
+        <v>0.354</v>
       </c>
       <c r="AF5" s="3">
-        <v>0.464</v>
+        <v>0.593</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.5940000000000001</v>
+        <v>0.751</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.8380000000000001</v>
+        <v>0.9530000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -4477,70 +4484,70 @@
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>2021</v>
+        <v>2097</v>
       </c>
       <c r="C6" s="1">
-        <v>29.09</v>
+        <v>31.398</v>
       </c>
       <c r="D6" s="1">
-        <v>14.545</v>
+        <v>15.699</v>
       </c>
       <c r="E6" s="3">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="F6" s="3">
-        <v>0.073</v>
+        <v>0.076</v>
       </c>
       <c r="G6" s="3">
-        <v>0.127</v>
+        <v>0.137</v>
       </c>
       <c r="H6" s="3">
-        <v>0.148</v>
+        <v>0.194</v>
       </c>
       <c r="I6" s="3">
-        <v>0.151</v>
+        <v>0.229</v>
       </c>
       <c r="J6" s="3">
-        <v>0.12</v>
+        <v>0.124</v>
       </c>
       <c r="K6" s="3">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="L6" s="3">
-        <v>0.073</v>
+        <v>0.052</v>
       </c>
       <c r="M6" s="3">
-        <v>0.049</v>
+        <v>0.023</v>
       </c>
       <c r="N6" s="3">
-        <v>0.03</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O6" s="3">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="P6" s="3">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
       <c r="Q6" s="3">
-        <v>0.011</v>
+        <v>0.002</v>
       </c>
       <c r="R6" s="3">
-        <v>0.011</v>
+        <v>0.001</v>
       </c>
       <c r="S6" s="3">
-        <v>0.008</v>
+        <v>0.002</v>
       </c>
       <c r="T6" s="3">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="U6" s="3">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="V6" s="3">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="W6" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="X6" s="3">
         <v>0</v>
@@ -4549,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="3">
         <v>0</v>
@@ -4558,22 +4565,22 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3">
-        <v>0.04</v>
+        <v>0.028</v>
       </c>
       <c r="AD6" s="3">
-        <v>0.113</v>
+        <v>0.104</v>
       </c>
       <c r="AE6" s="3">
-        <v>0.24</v>
+        <v>0.241</v>
       </c>
       <c r="AF6" s="3">
-        <v>0.388</v>
+        <v>0.435</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.539</v>
+        <v>0.664</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.841</v>
+        <v>0.9470000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -4581,73 +4588,73 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>2013</v>
+        <v>2035</v>
       </c>
       <c r="C7" s="1">
-        <v>28.506</v>
+        <v>27.91</v>
       </c>
       <c r="D7" s="1">
-        <v>14.253</v>
+        <v>13.955</v>
       </c>
       <c r="E7" s="3">
-        <v>0.033</v>
+        <v>0.007</v>
       </c>
       <c r="F7" s="3">
-        <v>0.058</v>
+        <v>0.019</v>
       </c>
       <c r="G7" s="3">
-        <v>0.099</v>
+        <v>0.037</v>
       </c>
       <c r="H7" s="3">
-        <v>0.13</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="I7" s="3">
-        <v>0.144</v>
+        <v>0.137</v>
       </c>
       <c r="J7" s="3">
-        <v>0.134</v>
+        <v>0.187</v>
       </c>
       <c r="K7" s="3">
+        <v>0.161</v>
+      </c>
+      <c r="L7" s="3">
         <v>0.102</v>
       </c>
-      <c r="L7" s="3">
-        <v>0.082</v>
-      </c>
       <c r="M7" s="3">
-        <v>0.061</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="N7" s="3">
-        <v>0.034</v>
+        <v>0.064</v>
       </c>
       <c r="O7" s="3">
-        <v>0.032</v>
+        <v>0.037</v>
       </c>
       <c r="P7" s="3">
+        <v>0.018</v>
+      </c>
+      <c r="Q7" s="3">
         <v>0.023</v>
       </c>
-      <c r="Q7" s="3">
-        <v>0.019</v>
-      </c>
       <c r="R7" s="3">
-        <v>0.008</v>
+        <v>0.011</v>
       </c>
       <c r="S7" s="3">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="T7" s="3">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="U7" s="3">
         <v>0.006</v>
       </c>
       <c r="V7" s="3">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="W7" s="3">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="X7" s="3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="Y7" s="3">
         <v>0.001</v>
@@ -4662,22 +4669,22 @@
         <v>0</v>
       </c>
       <c r="AC7" s="3">
-        <v>0.033</v>
+        <v>0.007</v>
       </c>
       <c r="AD7" s="3">
-        <v>0.091</v>
+        <v>0.026</v>
       </c>
       <c r="AE7" s="3">
-        <v>0.19</v>
+        <v>0.063</v>
       </c>
       <c r="AF7" s="3">
-        <v>0.32</v>
+        <v>0.148</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.464</v>
+        <v>0.285</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.7819999999999999</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -4685,415 +4692,415 @@
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>1951</v>
+        <v>2026</v>
       </c>
       <c r="C8" s="1">
-        <v>24.688</v>
+        <v>27.432</v>
       </c>
       <c r="D8" s="1">
-        <v>12.344</v>
+        <v>13.716</v>
       </c>
       <c r="E8" s="3">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="F8" s="3">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="G8" s="3">
         <v>0.033</v>
       </c>
       <c r="H8" s="3">
-        <v>0.043</v>
+        <v>0.053</v>
       </c>
       <c r="I8" s="3">
-        <v>0.074</v>
+        <v>0.128</v>
       </c>
       <c r="J8" s="3">
-        <v>0.097</v>
+        <v>0.171</v>
       </c>
       <c r="K8" s="3">
+        <v>0.181</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0.054</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.041</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0.031</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.031</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0.014</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0.017</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0.006</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0.003</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0.004</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0.016</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0.049</v>
+      </c>
+      <c r="AF8" s="3">
         <v>0.102</v>
       </c>
-      <c r="L8" s="3">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0.064</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0.051</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0.036</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0.037</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0.024</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0.025</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0.023</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0.013</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0.012</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0.011</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>0.012</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>0.003</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>0.005</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>0.017</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>0.093</v>
-      </c>
       <c r="AG8" s="3">
-        <v>0.167</v>
+        <v>0.23</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.45</v>
+        <v>0.7070000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:34">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1">
-        <v>1915</v>
+        <v>1992</v>
       </c>
       <c r="C9" s="1">
-        <v>22.396</v>
+        <v>25.184</v>
       </c>
       <c r="D9" s="1">
-        <v>11.198</v>
+        <v>12.592</v>
       </c>
       <c r="E9" s="3">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="F9" s="3">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="G9" s="3">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="H9" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.053</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.106</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0.148</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0.124</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0.099</v>
+      </c>
+      <c r="O9" s="3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="P9" s="3">
+        <v>0.054</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="R9" s="3">
+        <v>0.033</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0.022</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0.017</v>
+      </c>
+      <c r="U9" s="3">
         <v>0.016</v>
       </c>
-      <c r="I9" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.044</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0.043</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0.073</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0.075</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="O9" s="3">
-        <v>0.064</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0.079</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0.076</v>
-      </c>
-      <c r="R9" s="3">
-        <v>0.055</v>
-      </c>
-      <c r="S9" s="3">
-        <v>0.067</v>
-      </c>
-      <c r="T9" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="U9" s="3">
-        <v>0.058</v>
-      </c>
       <c r="V9" s="3">
-        <v>0.033</v>
+        <v>0.016</v>
       </c>
       <c r="W9" s="3">
-        <v>0.039</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="X9" s="3">
-        <v>0.023</v>
+        <v>0.006</v>
       </c>
       <c r="Y9" s="3">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="Z9" s="3">
-        <v>0.027</v>
+        <v>0.005</v>
       </c>
       <c r="AA9" s="3">
-        <v>0.023</v>
+        <v>0.001</v>
       </c>
       <c r="AB9" s="3">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="AC9" s="3">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="AD9" s="3">
-        <v>0.006</v>
+        <v>0.004</v>
       </c>
       <c r="AE9" s="3">
-        <v>0.016</v>
+        <v>0.019</v>
       </c>
       <c r="AF9" s="3">
-        <v>0.032</v>
+        <v>0.045</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.062</v>
+        <v>0.098</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.222</v>
+        <v>0.482</v>
       </c>
     </row>
     <row r="10" spans="1:34">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1">
-        <v>1933</v>
+        <v>1981</v>
       </c>
       <c r="C10" s="1">
-        <v>23.396</v>
+        <v>24.474</v>
       </c>
       <c r="D10" s="1">
-        <v>11.698</v>
+        <v>12.237</v>
       </c>
       <c r="E10" s="3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F10" s="3">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="G10" s="3">
-        <v>0.017</v>
+        <v>0.008</v>
       </c>
       <c r="H10" s="3">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="I10" s="3">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="J10" s="3">
-        <v>0.062</v>
+        <v>0.068</v>
       </c>
       <c r="K10" s="3">
-        <v>0.081</v>
+        <v>0.108</v>
       </c>
       <c r="L10" s="3">
-        <v>0.08799999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="M10" s="3">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="N10" s="3">
-        <v>0.08500000000000001</v>
+        <v>0.143</v>
       </c>
       <c r="O10" s="3">
-        <v>0.06900000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="P10" s="3">
-        <v>0.07000000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.056</v>
+        <v>0.043</v>
       </c>
       <c r="R10" s="3">
         <v>0.05</v>
       </c>
       <c r="S10" s="3">
-        <v>0.043</v>
+        <v>0.027</v>
       </c>
       <c r="T10" s="3">
-        <v>0.047</v>
+        <v>0.019</v>
       </c>
       <c r="U10" s="3">
-        <v>0.033</v>
+        <v>0.021</v>
       </c>
       <c r="V10" s="3">
-        <v>0.037</v>
+        <v>0.019</v>
       </c>
       <c r="W10" s="3">
-        <v>0.033</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="X10" s="3">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="Y10" s="3">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="Z10" s="3">
-        <v>0.016</v>
+        <v>0.004</v>
       </c>
       <c r="AA10" s="3">
         <v>0.003</v>
       </c>
       <c r="AB10" s="3">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="AC10" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AD10" s="3">
         <v>0.002</v>
       </c>
-      <c r="AD10" s="3">
-        <v>0.009000000000000001</v>
-      </c>
       <c r="AE10" s="3">
-        <v>0.026</v>
+        <v>0.01</v>
       </c>
       <c r="AF10" s="3">
-        <v>0.05500000000000001</v>
+        <v>0.029</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.104</v>
+        <v>0.07999999999999999</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.335</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1">
-        <v>1923</v>
+        <v>1908</v>
       </c>
       <c r="C11" s="1">
-        <v>22.734</v>
+        <v>20.212</v>
       </c>
       <c r="D11" s="1">
-        <v>11.367</v>
+        <v>10.106</v>
       </c>
       <c r="E11" s="3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F11" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0.003</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.008</v>
+      </c>
+      <c r="J11" s="3">
         <v>0.013</v>
       </c>
-      <c r="H11" s="3">
-        <v>0.028</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0.025</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0.048</v>
-      </c>
       <c r="K11" s="3">
-        <v>0.056</v>
+        <v>0.029</v>
       </c>
       <c r="L11" s="3">
-        <v>0.06900000000000001</v>
+        <v>0.044</v>
       </c>
       <c r="M11" s="3">
-        <v>0.081</v>
+        <v>0.062</v>
       </c>
       <c r="N11" s="3">
-        <v>0.095</v>
+        <v>0.073</v>
       </c>
       <c r="O11" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="P11" s="3">
         <v>0.08699999999999999</v>
       </c>
-      <c r="P11" s="3">
-        <v>0.075</v>
-      </c>
       <c r="Q11" s="3">
-        <v>0.068</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="R11" s="3">
-        <v>0.068</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="S11" s="3">
-        <v>0.048</v>
+        <v>0.076</v>
       </c>
       <c r="T11" s="3">
+        <v>0.061</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0.065</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0.049</v>
+      </c>
+      <c r="W11" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="X11" s="3">
         <v>0.044</v>
       </c>
-      <c r="U11" s="3">
-        <v>0.049</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0.041</v>
-      </c>
-      <c r="W11" s="3">
+      <c r="Y11" s="3">
+        <v>0.027</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>0.039</v>
+      </c>
+      <c r="AA11" s="3">
         <v>0.031</v>
       </c>
-      <c r="X11" s="3">
-        <v>0.018</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0.023</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="AA11" s="3">
+      <c r="AB11" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0.004</v>
+      </c>
+      <c r="AG11" s="3">
         <v>0.012</v>
       </c>
-      <c r="AB11" s="3">
-        <v>0.007</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="AD11" s="3">
-        <v>0.004</v>
-      </c>
-      <c r="AE11" s="3">
-        <v>0.017</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>0.045</v>
-      </c>
-      <c r="AG11" s="3">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="AH11" s="3">
-        <v>0.243</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -5101,103 +5108,103 @@
         <v>13</v>
       </c>
       <c r="B12" s="1">
-        <v>1918</v>
+        <v>1915</v>
       </c>
       <c r="C12" s="1">
-        <v>22.448</v>
+        <v>20.428</v>
       </c>
       <c r="D12" s="1">
-        <v>11.224</v>
+        <v>10.214</v>
       </c>
       <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
         <v>0.001</v>
       </c>
-      <c r="F12" s="3">
-        <v>0.004</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="H12" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.006</v>
+      </c>
+      <c r="J12" s="3">
         <v>0.025</v>
       </c>
-      <c r="I12" s="3">
-        <v>0.035</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0.045</v>
-      </c>
       <c r="K12" s="3">
-        <v>0.062</v>
+        <v>0.025</v>
       </c>
       <c r="L12" s="3">
-        <v>0.081</v>
+        <v>0.047</v>
       </c>
       <c r="M12" s="3">
-        <v>0.063</v>
+        <v>0.083</v>
       </c>
       <c r="N12" s="3">
-        <v>0.07000000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="O12" s="3">
-        <v>0.073</v>
+        <v>0.09</v>
       </c>
       <c r="P12" s="3">
-        <v>0.07199999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="Q12" s="3">
-        <v>0.077</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="R12" s="3">
-        <v>0.053</v>
+        <v>0.061</v>
       </c>
       <c r="S12" s="3">
-        <v>0.053</v>
+        <v>0.059</v>
       </c>
       <c r="T12" s="3">
-        <v>0.046</v>
+        <v>0.054</v>
       </c>
       <c r="U12" s="3">
-        <v>0.04</v>
+        <v>0.061</v>
       </c>
       <c r="V12" s="3">
-        <v>0.044</v>
+        <v>0.057</v>
       </c>
       <c r="W12" s="3">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="X12" s="3">
-        <v>0.027</v>
+        <v>0.037</v>
       </c>
       <c r="Y12" s="3">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
       <c r="Z12" s="3">
-        <v>0.025</v>
+        <v>0.031</v>
       </c>
       <c r="AA12" s="3">
-        <v>0.013</v>
+        <v>0.022</v>
       </c>
       <c r="AB12" s="3">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="AC12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3">
         <v>0.001</v>
       </c>
-      <c r="AD12" s="3">
-        <v>0.005</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>0.014</v>
-      </c>
       <c r="AF12" s="3">
-        <v>0.039</v>
+        <v>0.003</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.07400000000000001</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.262</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="13" spans="1:34">
@@ -5205,103 +5212,103 @@
         <v>14</v>
       </c>
       <c r="B13" s="1">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="C13" s="1">
-        <v>22.272</v>
+        <v>20.292</v>
       </c>
       <c r="D13" s="1">
-        <v>11.136</v>
+        <v>10.146</v>
       </c>
       <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="H13" s="3">
         <v>0.001</v>
       </c>
-      <c r="F13" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0.011</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.02</v>
-      </c>
       <c r="I13" s="3">
-        <v>0.037</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J13" s="3">
+        <v>0.018</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.031</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.052</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.057</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0.068</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0.076</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0.067</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.049</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.024</v>
+      </c>
+      <c r="Y13" s="3">
         <v>0.044</v>
       </c>
-      <c r="K13" s="3">
-        <v>0.065</v>
-      </c>
-      <c r="L13" s="3">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0.067</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0.054</v>
-      </c>
-      <c r="O13" s="3">
-        <v>0.073</v>
-      </c>
-      <c r="P13" s="3">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>0.064</v>
-      </c>
-      <c r="R13" s="3">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="S13" s="3">
-        <v>0.054</v>
-      </c>
-      <c r="T13" s="3">
-        <v>0.065</v>
-      </c>
-      <c r="U13" s="3">
-        <v>0.051</v>
-      </c>
-      <c r="V13" s="3">
+      <c r="Z13" s="3">
         <v>0.038</v>
       </c>
-      <c r="W13" s="3">
-        <v>0.033</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>0.031</v>
-      </c>
       <c r="AA13" s="3">
-        <v>0.014</v>
+        <v>0.024</v>
       </c>
       <c r="AB13" s="3">
         <v>0.016</v>
       </c>
       <c r="AC13" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="AF13" s="3">
         <v>0.003</v>
       </c>
-      <c r="AE13" s="3">
-        <v>0.014</v>
-      </c>
-      <c r="AF13" s="3">
-        <v>0.034</v>
-      </c>
       <c r="AG13" s="3">
-        <v>0.07100000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.249</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -5309,311 +5316,311 @@
         <v>16</v>
       </c>
       <c r="B14" s="1">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="C14" s="1">
-        <v>22.058</v>
+        <v>19.946</v>
       </c>
       <c r="D14" s="1">
-        <v>11.029</v>
+        <v>9.973000000000001</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>0.001</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>0.002</v>
       </c>
-      <c r="G14" s="3">
-        <v>0.008</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="I14" s="3">
-        <v>0.027</v>
+        <v>0.002</v>
       </c>
       <c r="J14" s="3">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="K14" s="3">
-        <v>0.057</v>
+        <v>0.026</v>
       </c>
       <c r="L14" s="3">
-        <v>0.053</v>
+        <v>0.042</v>
       </c>
       <c r="M14" s="3">
-        <v>0.065</v>
+        <v>0.05</v>
       </c>
       <c r="N14" s="3">
-        <v>0.077</v>
+        <v>0.045</v>
       </c>
       <c r="O14" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="S14" s="3">
         <v>0.073</v>
       </c>
-      <c r="P14" s="3">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0.073</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0.073</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0.07199999999999999</v>
-      </c>
       <c r="T14" s="3">
-        <v>0.065</v>
+        <v>0.074</v>
       </c>
       <c r="U14" s="3">
-        <v>0.039</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="V14" s="3">
-        <v>0.051</v>
+        <v>0.055</v>
       </c>
       <c r="W14" s="3">
-        <v>0.032</v>
+        <v>0.056</v>
       </c>
       <c r="X14" s="3">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
       <c r="Y14" s="3">
-        <v>0.034</v>
+        <v>0.048</v>
       </c>
       <c r="Z14" s="3">
         <v>0.028</v>
       </c>
       <c r="AA14" s="3">
-        <v>0.015</v>
+        <v>0.025</v>
       </c>
       <c r="AB14" s="3">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>0.001</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AF14" s="3">
         <v>0.003</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0.011</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0.02</v>
-      </c>
       <c r="AG14" s="3">
-        <v>0.047</v>
+        <v>0.005</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.19</v>
+        <v>0.08299999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1">
         <v>1902</v>
       </c>
       <c r="C15" s="1">
-        <v>21.418</v>
+        <v>19.772</v>
       </c>
       <c r="D15" s="1">
-        <v>10.709</v>
+        <v>9.885999999999999</v>
       </c>
       <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
         <v>0.001</v>
       </c>
-      <c r="F15" s="3">
-        <v>0.003</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0.007</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.008</v>
-      </c>
       <c r="I15" s="3">
-        <v>0.017</v>
+        <v>0.004</v>
       </c>
       <c r="J15" s="3">
-        <v>0.039</v>
+        <v>0.019</v>
       </c>
       <c r="K15" s="3">
-        <v>0.036</v>
+        <v>0.025</v>
       </c>
       <c r="L15" s="3">
-        <v>0.055</v>
+        <v>0.032</v>
       </c>
       <c r="M15" s="3">
-        <v>0.061</v>
+        <v>0.054</v>
       </c>
       <c r="N15" s="3">
-        <v>0.063</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="O15" s="3">
-        <v>0.05</v>
+        <v>0.056</v>
       </c>
       <c r="P15" s="3">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0.062</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0.066</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0.066</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="V15" s="3">
         <v>0.067</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0.067</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="W15" s="3">
+        <v>0.059</v>
+      </c>
+      <c r="X15" s="3">
         <v>0.048</v>
       </c>
-      <c r="T15" s="3">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0.063</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0.055</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0.041</v>
-      </c>
       <c r="Y15" s="3">
-        <v>0.047</v>
+        <v>0.045</v>
       </c>
       <c r="Z15" s="3">
-        <v>0.026</v>
+        <v>0.037</v>
       </c>
       <c r="AA15" s="3">
+        <v>0.035</v>
+      </c>
+      <c r="AB15" s="3">
         <v>0.025</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0.012</v>
-      </c>
       <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
         <v>0.001</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0.004</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>0.011</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>0.019</v>
-      </c>
       <c r="AG15" s="3">
-        <v>0.036</v>
+        <v>0.005</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.166</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="C16" s="1">
-        <v>21.734</v>
+        <v>19.718</v>
       </c>
       <c r="D16" s="1">
-        <v>10.867</v>
+        <v>9.859</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="H16" s="3">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3">
-        <v>0.025</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J16" s="3">
-        <v>0.036</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K16" s="3">
+        <v>0.014</v>
+      </c>
+      <c r="L16" s="3">
         <v>0.04</v>
       </c>
-      <c r="L16" s="3">
+      <c r="M16" s="3">
+        <v>0.058</v>
+      </c>
+      <c r="N16" s="3">
         <v>0.049</v>
       </c>
-      <c r="M16" s="3">
-        <v>0.055</v>
-      </c>
-      <c r="N16" s="3">
+      <c r="O16" s="3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="P16" s="3">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.076</v>
+      </c>
+      <c r="R16" s="3">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="S16" s="3">
+        <v>0.059</v>
+      </c>
+      <c r="T16" s="3">
         <v>0.073</v>
       </c>
-      <c r="O16" s="3">
-        <v>0.078</v>
-      </c>
-      <c r="P16" s="3">
-        <v>0.066</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>0.077</v>
-      </c>
-      <c r="R16" s="3">
-        <v>0.057</v>
-      </c>
-      <c r="S16" s="3">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="T16" s="3">
-        <v>0.06900000000000001</v>
-      </c>
       <c r="U16" s="3">
-        <v>0.051</v>
+        <v>0.067</v>
       </c>
       <c r="V16" s="3">
-        <v>0.053</v>
+        <v>0.068</v>
       </c>
       <c r="W16" s="3">
-        <v>0.036</v>
+        <v>0.056</v>
       </c>
       <c r="X16" s="3">
-        <v>0.039</v>
+        <v>0.059</v>
       </c>
       <c r="Y16" s="3">
+        <v>0.045</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>0.043</v>
+      </c>
+      <c r="AA16" s="3">
         <v>0.034</v>
       </c>
-      <c r="Z16" s="3">
-        <v>0.031</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>0.024</v>
-      </c>
       <c r="AB16" s="3">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="AC16" s="3">
         <v>0</v>
       </c>
       <c r="AD16" s="3">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AE16" s="3">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="3">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.047</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.172</v>
+        <v>0.07200000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:34">
@@ -5621,28 +5628,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="1">
-        <v>1872</v>
+        <v>1898</v>
       </c>
       <c r="C17" s="1">
-        <v>19.444</v>
+        <v>19.316</v>
       </c>
       <c r="D17" s="1">
-        <v>9.722</v>
+        <v>9.657999999999999</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
         <v>0.001</v>
       </c>
-      <c r="G17" s="3">
-        <v>0.003</v>
-      </c>
       <c r="H17" s="3">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="I17" s="3">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="J17" s="3">
         <v>0.012</v>
@@ -5651,73 +5658,73 @@
         <v>0.021</v>
       </c>
       <c r="L17" s="3">
-        <v>0.027</v>
+        <v>0.031</v>
       </c>
       <c r="M17" s="3">
-        <v>0.037</v>
+        <v>0.036</v>
       </c>
       <c r="N17" s="3">
-        <v>0.037</v>
+        <v>0.043</v>
       </c>
       <c r="O17" s="3">
-        <v>0.046</v>
+        <v>0.056</v>
       </c>
       <c r="P17" s="3">
-        <v>0.061</v>
+        <v>0.077</v>
       </c>
       <c r="Q17" s="3">
-        <v>0.054</v>
+        <v>0.064</v>
       </c>
       <c r="R17" s="3">
+        <v>0.079</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0.065</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0.065</v>
+      </c>
+      <c r="X17" s="3">
         <v>0.056</v>
       </c>
-      <c r="S17" s="3">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="T17" s="3">
-        <v>0.057</v>
-      </c>
-      <c r="U17" s="3">
-        <v>0.081</v>
-      </c>
-      <c r="V17" s="3">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="W17" s="3">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="X17" s="3">
-        <v>0.066</v>
-      </c>
       <c r="Y17" s="3">
-        <v>0.064</v>
+        <v>0.048</v>
       </c>
       <c r="Z17" s="3">
-        <v>0.062</v>
+        <v>0.047</v>
       </c>
       <c r="AA17" s="3">
-        <v>0.053</v>
+        <v>0.042</v>
       </c>
       <c r="AB17" s="3">
-        <v>0.036</v>
+        <v>0.029</v>
       </c>
       <c r="AC17" s="3">
         <v>0</v>
       </c>
       <c r="AD17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="3">
         <v>0.001</v>
       </c>
-      <c r="AE17" s="3">
-        <v>0.004</v>
-      </c>
       <c r="AF17" s="3">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.017</v>
+        <v>0.008</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.077</v>
+        <v>0.07200000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -5725,103 +5732,103 @@
         <v>20</v>
       </c>
       <c r="B18" s="1">
-        <v>1868</v>
+        <v>1881</v>
       </c>
       <c r="C18" s="1">
-        <v>19.426</v>
+        <v>18.518</v>
       </c>
       <c r="D18" s="1">
-        <v>9.712999999999999</v>
+        <v>9.259</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
       </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="I18" s="3">
         <v>0.002</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.004</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0.006</v>
-      </c>
       <c r="J18" s="3">
-        <v>0.016</v>
+        <v>0.008</v>
       </c>
       <c r="K18" s="3">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="L18" s="3">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="M18" s="3">
-        <v>0.018</v>
+        <v>0.031</v>
       </c>
       <c r="N18" s="3">
-        <v>0.047</v>
+        <v>0.041</v>
       </c>
       <c r="O18" s="3">
-        <v>0.048</v>
+        <v>0.038</v>
       </c>
       <c r="P18" s="3">
-        <v>0.048</v>
+        <v>0.056</v>
       </c>
       <c r="Q18" s="3">
-        <v>0.052</v>
+        <v>0.061</v>
       </c>
       <c r="R18" s="3">
-        <v>0.073</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="S18" s="3">
-        <v>0.059</v>
+        <v>0.076</v>
       </c>
       <c r="T18" s="3">
-        <v>0.074</v>
+        <v>0.065</v>
       </c>
       <c r="U18" s="3">
-        <v>0.07099999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="V18" s="3">
-        <v>0.083</v>
+        <v>0.068</v>
       </c>
       <c r="W18" s="3">
-        <v>0.07000000000000001</v>
+        <v>0.092</v>
       </c>
       <c r="X18" s="3">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Y18" s="3">
-        <v>0.068</v>
+        <v>0.062</v>
       </c>
       <c r="Z18" s="3">
-        <v>0.067</v>
+        <v>0.049</v>
       </c>
       <c r="AA18" s="3">
-        <v>0.044</v>
+        <v>0.055</v>
       </c>
       <c r="AB18" s="3">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="AC18" s="3">
         <v>0</v>
       </c>
       <c r="AD18" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AE18" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AF18" s="3">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.012</v>
+        <v>0.003</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.067</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="19" spans="1:34">
@@ -5829,13 +5836,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="1">
-        <v>1855</v>
+        <v>1871</v>
       </c>
       <c r="C19" s="1">
-        <v>18.566</v>
+        <v>17.808</v>
       </c>
       <c r="D19" s="1">
-        <v>9.282999999999999</v>
+        <v>8.904</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
@@ -5844,70 +5851,70 @@
         <v>0</v>
       </c>
       <c r="G19" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H19" s="3">
         <v>0.001</v>
       </c>
       <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
         <v>0.003</v>
       </c>
-      <c r="J19" s="3">
-        <v>0.008999999999999999</v>
-      </c>
       <c r="K19" s="3">
-        <v>0.015</v>
+        <v>0.007</v>
       </c>
       <c r="L19" s="3">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="M19" s="3">
-        <v>0.025</v>
+        <v>0.021</v>
       </c>
       <c r="N19" s="3">
-        <v>0.019</v>
+        <v>0.029</v>
       </c>
       <c r="O19" s="3">
-        <v>0.035</v>
+        <v>0.031</v>
       </c>
       <c r="P19" s="3">
-        <v>0.037</v>
+        <v>0.042</v>
       </c>
       <c r="Q19" s="3">
-        <v>0.048</v>
+        <v>0.053</v>
       </c>
       <c r="R19" s="3">
-        <v>0.07199999999999999</v>
+        <v>0.056</v>
       </c>
       <c r="S19" s="3">
+        <v>0.082</v>
+      </c>
+      <c r="T19" s="3">
+        <v>0.074</v>
+      </c>
+      <c r="U19" s="3">
         <v>0.059</v>
       </c>
-      <c r="T19" s="3">
-        <v>0.076</v>
-      </c>
-      <c r="U19" s="3">
-        <v>0.063</v>
-      </c>
       <c r="V19" s="3">
-        <v>0.082</v>
+        <v>0.075</v>
       </c>
       <c r="W19" s="3">
-        <v>0.073</v>
+        <v>0.08</v>
       </c>
       <c r="X19" s="3">
-        <v>0.08699999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="Y19" s="3">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="Z19" s="3">
+        <v>0.075</v>
+      </c>
+      <c r="AA19" s="3">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AA19" s="3">
-        <v>0.073</v>
-      </c>
       <c r="AB19" s="3">
-        <v>0.061</v>
+        <v>0.056</v>
       </c>
       <c r="AC19" s="3">
         <v>0</v>
@@ -5916,16 +5923,16 @@
         <v>0</v>
       </c>
       <c r="AE19" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="3">
         <v>0.001</v>
       </c>
-      <c r="AF19" s="3">
-        <v>0.002</v>
-      </c>
       <c r="AG19" s="3">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.03999999999999999</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -5933,13 +5940,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="1">
-        <v>1846</v>
+        <v>1870</v>
       </c>
       <c r="C20" s="1">
-        <v>17.892</v>
+        <v>17.756</v>
       </c>
       <c r="D20" s="1">
-        <v>8.946</v>
+        <v>8.878</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -5948,71 +5955,71 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0.001</v>
       </c>
       <c r="I20" s="3">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J20" s="3">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="K20" s="3">
         <v>0.007</v>
       </c>
       <c r="L20" s="3">
-        <v>0.012</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M20" s="3">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="N20" s="3">
-        <v>0.028</v>
+        <v>0.037</v>
       </c>
       <c r="O20" s="3">
-        <v>0.032</v>
+        <v>0.047</v>
       </c>
       <c r="P20" s="3">
-        <v>0.03</v>
+        <v>0.031</v>
       </c>
       <c r="Q20" s="3">
-        <v>0.048</v>
+        <v>0.057</v>
       </c>
       <c r="R20" s="3">
-        <v>0.038</v>
+        <v>0.054</v>
       </c>
       <c r="S20" s="3">
-        <v>0.055</v>
+        <v>0.064</v>
       </c>
       <c r="T20" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0.068</v>
+      </c>
+      <c r="V20" s="3">
+        <v>0.065</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0.079</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AB20" s="3">
         <v>0.061</v>
       </c>
-      <c r="U20" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0.061</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0.103</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0.097</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0.076</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -6020,16 +6027,16 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -6037,13 +6044,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>1844</v>
+        <v>1863</v>
       </c>
       <c r="C21" s="1">
-        <v>17.736</v>
+        <v>17.28</v>
       </c>
       <c r="D21" s="1">
-        <v>8.868</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -6055,67 +6062,67 @@
         <v>0</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>0.002</v>
       </c>
-      <c r="I21" s="3">
-        <v>0.001</v>
-      </c>
       <c r="J21" s="3">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="K21" s="3">
-        <v>0.014</v>
+        <v>0.003</v>
       </c>
       <c r="L21" s="3">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="M21" s="3">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="N21" s="3">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="O21" s="3">
-        <v>0.021</v>
+        <v>0.024</v>
       </c>
       <c r="P21" s="3">
-        <v>0.031</v>
+        <v>0.046</v>
       </c>
       <c r="Q21" s="3">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="R21" s="3">
-        <v>0.046</v>
+        <v>0.04</v>
       </c>
       <c r="S21" s="3">
-        <v>0.042</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T21" s="3">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
       <c r="U21" s="3">
-        <v>0.078</v>
+        <v>0.068</v>
       </c>
       <c r="V21" s="3">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W21" s="3">
-        <v>0.078</v>
+        <v>0.073</v>
       </c>
       <c r="X21" s="3">
+        <v>0.097</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>0.083</v>
+      </c>
+      <c r="Z21" s="3">
         <v>0.08599999999999999</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>0.096</v>
-      </c>
       <c r="AA21" s="3">
-        <v>0.1</v>
+        <v>0.094</v>
       </c>
       <c r="AB21" s="3">
-        <v>0.096</v>
+        <v>0.079</v>
       </c>
       <c r="AC21" s="3">
         <v>0</v>
@@ -6127,131 +6134,131 @@
         <v>0</v>
       </c>
       <c r="AF21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3">
         <v>0.002</v>
       </c>
-      <c r="AG21" s="3">
-        <v>0.003</v>
-      </c>
       <c r="AH21" s="3">
-        <v>0.03700000000000001</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="1">
-        <v>1840</v>
+        <v>1848</v>
       </c>
       <c r="C22" s="1">
-        <v>17.372</v>
+        <v>16.646</v>
       </c>
       <c r="D22" s="1">
-        <v>8.686</v>
+        <v>8.323</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="K22" s="3">
         <v>0.001</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0.003</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0.005</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0.006</v>
-      </c>
       <c r="L22" s="3">
+        <v>0.004</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0.017</v>
+      </c>
+      <c r="N22" s="3">
         <v>0.011</v>
       </c>
-      <c r="M22" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0.016</v>
-      </c>
       <c r="O22" s="3">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="P22" s="3">
-        <v>0.029</v>
+        <v>0.037</v>
       </c>
       <c r="Q22" s="3">
-        <v>0.031</v>
+        <v>0.036</v>
       </c>
       <c r="R22" s="3">
+        <v>0.047</v>
+      </c>
+      <c r="S22" s="3">
         <v>0.041</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0.042</v>
       </c>
       <c r="T22" s="3">
         <v>0.058</v>
       </c>
       <c r="U22" s="3">
-        <v>0.061</v>
+        <v>0.055</v>
       </c>
       <c r="V22" s="3">
-        <v>0.07099999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="W22" s="3">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="X22" s="3">
-        <v>0.108</v>
+        <v>0.083</v>
       </c>
       <c r="Y22" s="3">
         <v>0.102</v>
       </c>
       <c r="Z22" s="3">
-        <v>0.093</v>
+        <v>0.117</v>
       </c>
       <c r="AA22" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="AB22" s="3">
         <v>0.114</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0.108</v>
-      </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
       <c r="AD22" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1">
-        <v>1834</v>
+        <v>1849</v>
       </c>
       <c r="C23" s="1">
-        <v>17.352</v>
+        <v>16.36</v>
       </c>
       <c r="D23" s="1">
-        <v>8.676</v>
+        <v>8.18</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -6263,64 +6270,64 @@
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="I23" s="3">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="K23" s="3">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="L23" s="3">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="M23" s="3">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="N23" s="3">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="O23" s="3">
         <v>0.021</v>
       </c>
       <c r="P23" s="3">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="Q23" s="3">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="R23" s="3">
-        <v>0.048</v>
+        <v>0.033</v>
       </c>
       <c r="S23" s="3">
-        <v>0.053</v>
+        <v>0.044</v>
       </c>
       <c r="T23" s="3">
-        <v>0.044</v>
+        <v>0.073</v>
       </c>
       <c r="U23" s="3">
-        <v>0.057</v>
+        <v>0.062</v>
       </c>
       <c r="V23" s="3">
-        <v>0.05</v>
+        <v>0.063</v>
       </c>
       <c r="W23" s="3">
-        <v>0.067</v>
+        <v>0.076</v>
       </c>
       <c r="X23" s="3">
-        <v>0.101</v>
+        <v>0.092</v>
       </c>
       <c r="Y23" s="3">
-        <v>0.095</v>
+        <v>0.118</v>
       </c>
       <c r="Z23" s="3">
-        <v>0.114</v>
+        <v>0.096</v>
       </c>
       <c r="AA23" s="3">
-        <v>0.125</v>
+        <v>0.108</v>
       </c>
       <c r="AB23" s="3">
         <v>0.123</v>
@@ -6335,13 +6342,13 @@
         <v>0</v>
       </c>
       <c r="AF23" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG23" s="3">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AH23" s="3">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -6349,103 +6356,103 @@
         <v>26</v>
       </c>
       <c r="B24" s="1">
-        <v>1833</v>
+        <v>1846</v>
       </c>
       <c r="C24" s="1">
-        <v>17.066</v>
+        <v>16.282</v>
       </c>
       <c r="D24" s="1">
-        <v>8.532999999999999</v>
+        <v>8.141</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>0.001</v>
       </c>
-      <c r="G24" s="3">
+      <c r="J24" s="3">
         <v>0.001</v>
       </c>
-      <c r="H24" s="3">
+      <c r="K24" s="3">
         <v>0.003</v>
       </c>
-      <c r="I24" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0.005</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0.008</v>
-      </c>
       <c r="L24" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.013</v>
       </c>
       <c r="M24" s="3">
         <v>0.013</v>
       </c>
       <c r="N24" s="3">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="O24" s="3">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="P24" s="3">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="Q24" s="3">
-        <v>0.019</v>
+        <v>0.026</v>
       </c>
       <c r="R24" s="3">
-        <v>0.035</v>
+        <v>0.047</v>
       </c>
       <c r="S24" s="3">
-        <v>0.045</v>
+        <v>0.04</v>
       </c>
       <c r="T24" s="3">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="U24" s="3">
-        <v>0.061</v>
+        <v>0.052</v>
       </c>
       <c r="V24" s="3">
-        <v>0.056</v>
+        <v>0.067</v>
       </c>
       <c r="W24" s="3">
-        <v>0.07199999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="X24" s="3">
-        <v>0.06</v>
+        <v>0.081</v>
       </c>
       <c r="Y24" s="3">
-        <v>0.11</v>
+        <v>0.089</v>
       </c>
       <c r="Z24" s="3">
-        <v>0.096</v>
+        <v>0.115</v>
       </c>
       <c r="AA24" s="3">
-        <v>0.123</v>
+        <v>0.117</v>
       </c>
       <c r="AB24" s="3">
-        <v>0.177</v>
+        <v>0.17</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>0.001</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>0.005</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>0.007</v>
-      </c>
       <c r="AH24" s="3">
-        <v>0.029</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -6453,13 +6460,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="1">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="C25" s="1">
-        <v>16.712</v>
+        <v>15.504</v>
       </c>
       <c r="D25" s="1">
-        <v>8.356</v>
+        <v>7.752</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
@@ -6468,70 +6475,70 @@
         <v>0</v>
       </c>
       <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
         <v>0.001</v>
       </c>
-      <c r="H25" s="3">
-        <v>0.002</v>
-      </c>
       <c r="I25" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3">
         <v>0.004</v>
       </c>
       <c r="L25" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="M25" s="3">
+        <v>0.011</v>
+      </c>
+      <c r="N25" s="3">
         <v>0.012</v>
       </c>
-      <c r="N25" s="3">
-        <v>0.01</v>
-      </c>
       <c r="O25" s="3">
-        <v>0.026</v>
+        <v>0.015</v>
       </c>
       <c r="P25" s="3">
         <v>0.02</v>
       </c>
       <c r="Q25" s="3">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="R25" s="3">
-        <v>0.025</v>
+        <v>0.018</v>
       </c>
       <c r="S25" s="3">
-        <v>0.045</v>
+        <v>0.036</v>
       </c>
       <c r="T25" s="3">
-        <v>0.035</v>
+        <v>0.049</v>
       </c>
       <c r="U25" s="3">
-        <v>0.044</v>
+        <v>0.047</v>
       </c>
       <c r="V25" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="W25" s="3">
         <v>0.059</v>
       </c>
-      <c r="W25" s="3">
-        <v>0.055</v>
-      </c>
       <c r="X25" s="3">
-        <v>0.08500000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="Y25" s="3">
-        <v>0.082</v>
+        <v>0.096</v>
       </c>
       <c r="Z25" s="3">
-        <v>0.109</v>
+        <v>0.106</v>
       </c>
       <c r="AA25" s="3">
         <v>0.139</v>
       </c>
       <c r="AB25" s="3">
-        <v>0.208</v>
+        <v>0.227</v>
       </c>
       <c r="AC25" s="3">
         <v>0</v>
@@ -6540,16 +6547,16 @@
         <v>0</v>
       </c>
       <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
         <v>0.001</v>
       </c>
-      <c r="AF25" s="3">
-        <v>0.003</v>
-      </c>
       <c r="AG25" s="3">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="AH25" s="3">
-        <v>0.019</v>
+        <v>0.006</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/excel/pronostics_tournoi.xlsx
+++ b/outputs/excel/pronostics_tournoi.xlsx
@@ -32,76 +32,76 @@
     <t>inactivity</t>
   </si>
   <si>
-    <t>CROSNIER Stéphane</t>
-  </si>
-  <si>
     <t>SUYS Olivier</t>
   </si>
   <si>
+    <t>DUMAS Emmanuel</t>
+  </si>
+  <si>
+    <t>LANDEMAINE Thierry</t>
+  </si>
+  <si>
     <t>BLAYE Arnaud</t>
   </si>
   <si>
-    <t>DUMAS Emmanuel</t>
-  </si>
-  <si>
-    <t>LANDEMAINE Thierry</t>
+    <t>PINEL Florian</t>
+  </si>
+  <si>
+    <t>MERRHEIM Philippe</t>
+  </si>
+  <si>
+    <t>DURAND Jean-Marc</t>
   </si>
   <si>
     <t>LECLÈRE Christophe</t>
   </si>
   <si>
-    <t>PINEL Florian</t>
-  </si>
-  <si>
-    <t>MERRHEIM Philippe</t>
-  </si>
-  <si>
-    <t>DURAND Jean-Marc</t>
+    <t>COSTE Denis</t>
+  </si>
+  <si>
+    <t>BROSSEAU Dany</t>
+  </si>
+  <si>
+    <t>TRUCCHI Sébastien</t>
   </si>
   <si>
     <t>CAMBLONCQ Thierry</t>
   </si>
   <si>
+    <t>BERNARD Pierre</t>
+  </si>
+  <si>
     <t>OLIVIER Philippe</t>
   </si>
   <si>
+    <t>RODRIGUES Marvin</t>
+  </si>
+  <si>
+    <t>BAKAYOKO Ahmed</t>
+  </si>
+  <si>
+    <t>DUCHAINE Laurent</t>
+  </si>
+  <si>
+    <t>ROUX Pierre-Damien</t>
+  </si>
+  <si>
+    <t>ROCCHIA Philippe</t>
+  </si>
+  <si>
+    <t>KERBIRIOU Jean-Luc</t>
+  </si>
+  <si>
     <t>BARCET Vincent</t>
   </si>
   <si>
-    <t>BROSSEAU Dany</t>
-  </si>
-  <si>
-    <t>RODRIGUES Marvin</t>
-  </si>
-  <si>
-    <t>TRUCCHI Sébastien</t>
-  </si>
-  <si>
-    <t>BERNARD Pierre</t>
-  </si>
-  <si>
-    <t>COSTE Denis</t>
-  </si>
-  <si>
-    <t>ROUX Pierre-Damien</t>
-  </si>
-  <si>
-    <t>BAKAYOKO Ahmed</t>
-  </si>
-  <si>
-    <t>KERBIRIOU Jean-Luc</t>
+    <t>BARBET Catherine</t>
+  </si>
+  <si>
+    <t>CALAIS Jean-Manuel</t>
   </si>
   <si>
     <t>BONTHOUX Julien</t>
-  </si>
-  <si>
-    <t>SUYS Alain</t>
-  </si>
-  <si>
-    <t>ROCCHIA Philippe</t>
-  </si>
-  <si>
-    <t>FOURY Christian</t>
   </si>
   <si>
     <t>elo_original</t>
@@ -619,13 +619,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>2200</v>
+        <v>2121</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -633,13 +633,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>2195</v>
+        <v>2092</v>
       </c>
       <c r="C3">
-        <v>219</v>
+        <v>354</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -647,10 +647,10 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>2155</v>
+        <v>2078</v>
       </c>
       <c r="C4">
-        <v>526</v>
+        <v>391</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -661,10 +661,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>2116</v>
+        <v>2028</v>
       </c>
       <c r="C5">
-        <v>418</v>
+        <v>464</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -675,13 +675,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>2097</v>
+        <v>2021</v>
       </c>
       <c r="C6">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -689,13 +689,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>2035</v>
+        <v>2013</v>
       </c>
       <c r="C7">
-        <v>449</v>
+        <v>200</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -703,13 +703,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>2026</v>
+        <v>1951</v>
       </c>
       <c r="C8">
-        <v>426</v>
+        <v>199</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -717,13 +717,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="1">
-        <v>1992</v>
+        <v>1933</v>
       </c>
       <c r="C9">
-        <v>220</v>
+        <v>396</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -731,13 +731,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="1">
-        <v>1981</v>
+        <v>1923</v>
       </c>
       <c r="C10">
-        <v>245</v>
+        <v>122</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -745,13 +745,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="1">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="C11">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -759,10 +759,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="1">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="C12">
-        <v>333</v>
+        <v>286</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -773,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="B13" s="1">
-        <v>1908</v>
+        <v>1915</v>
       </c>
       <c r="C13">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>16</v>
       </c>
       <c r="B14" s="1">
-        <v>1906</v>
+        <v>1912</v>
       </c>
       <c r="C14">
-        <v>297</v>
+        <v>200</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -801,13 +801,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="1">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C15">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -818,10 +818,10 @@
         <v>1902</v>
       </c>
       <c r="C16">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -829,10 +829,10 @@
         <v>19</v>
       </c>
       <c r="B17" s="1">
-        <v>1898</v>
+        <v>1872</v>
       </c>
       <c r="C17">
-        <v>230</v>
+        <v>361</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>20</v>
       </c>
       <c r="B18" s="1">
-        <v>1881</v>
+        <v>1868</v>
       </c>
       <c r="C18">
-        <v>151</v>
+        <v>264</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -857,13 +857,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="1">
-        <v>1871</v>
+        <v>1855</v>
       </c>
       <c r="C19">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -871,13 +871,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="1">
-        <v>1870</v>
+        <v>1846</v>
       </c>
       <c r="C20">
-        <v>406</v>
+        <v>35</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -885,13 +885,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>1863</v>
+        <v>1844</v>
       </c>
       <c r="C21">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -899,13 +899,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="1">
-        <v>1849</v>
+        <v>1840</v>
       </c>
       <c r="C22">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -913,13 +913,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="1">
-        <v>1848</v>
+        <v>1834</v>
       </c>
       <c r="C23">
-        <v>128</v>
+        <v>314</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -927,13 +927,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="1">
-        <v>1846</v>
+        <v>1833</v>
       </c>
       <c r="C24">
-        <v>35</v>
+        <v>215</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -941,13 +941,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="1">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="C25">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +962,7 @@
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="7.7109375" customWidth="1"/>
@@ -997,22 +997,19 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>2200</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2200</v>
+        <v>2121</v>
       </c>
       <c r="D2" s="1">
-        <v>2200</v>
+        <v>2121</v>
       </c>
       <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>184</v>
+      </c>
+      <c r="G2">
         <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1020,19 +1017,19 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>2195</v>
+        <v>2092</v>
       </c>
       <c r="D3" s="1">
-        <v>2195</v>
+        <v>2092</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>219</v>
+        <v>354</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1040,16 +1037,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>2155</v>
+        <v>2078</v>
       </c>
       <c r="D4" s="1">
-        <v>2155</v>
+        <v>2078</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>526</v>
+        <v>391</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1060,16 +1057,16 @@
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>2116</v>
+        <v>2028</v>
       </c>
       <c r="D5" s="1">
-        <v>2116</v>
+        <v>2028</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>418</v>
+        <v>464</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1080,19 +1077,19 @@
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>2097</v>
+        <v>2021</v>
       </c>
       <c r="D6" s="1">
-        <v>2097</v>
+        <v>2021</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1100,19 +1097,19 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>2035</v>
+        <v>2013</v>
       </c>
       <c r="D7" s="1">
-        <v>2035</v>
+        <v>2013</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>449</v>
+        <v>200</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1120,19 +1117,19 @@
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>2026</v>
+        <v>1951</v>
       </c>
       <c r="D8" s="1">
-        <v>2026</v>
+        <v>1951</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>426</v>
+        <v>199</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1140,19 +1137,19 @@
         <v>11</v>
       </c>
       <c r="B9" s="1">
-        <v>1992</v>
+        <v>1933</v>
       </c>
       <c r="D9" s="1">
-        <v>1992</v>
+        <v>1933</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>220</v>
+        <v>396</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1160,19 +1157,19 @@
         <v>12</v>
       </c>
       <c r="B10" s="1">
-        <v>1981</v>
+        <v>1923</v>
       </c>
       <c r="D10" s="1">
-        <v>1981</v>
+        <v>1923</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>245</v>
+        <v>122</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1180,19 +1177,19 @@
         <v>13</v>
       </c>
       <c r="B11" s="1">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="D11" s="1">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1200,16 +1197,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="1">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="D12" s="1">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>333</v>
+        <v>286</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1220,16 +1217,16 @@
         <v>15</v>
       </c>
       <c r="B13" s="1">
-        <v>1908</v>
+        <v>1915</v>
       </c>
       <c r="D13" s="1">
-        <v>1908</v>
+        <v>1915</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1240,16 +1237,16 @@
         <v>16</v>
       </c>
       <c r="B14" s="1">
-        <v>1906</v>
+        <v>1912</v>
       </c>
       <c r="D14" s="1">
-        <v>1906</v>
+        <v>1912</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>297</v>
+        <v>200</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1260,19 +1257,19 @@
         <v>17</v>
       </c>
       <c r="B15" s="1">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="D15" s="1">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1289,10 +1286,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1300,16 +1297,16 @@
         <v>19</v>
       </c>
       <c r="B17" s="1">
-        <v>1898</v>
+        <v>1872</v>
       </c>
       <c r="D17" s="1">
-        <v>1898</v>
+        <v>1872</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>230</v>
+        <v>361</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -1320,16 +1317,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="1">
-        <v>1881</v>
+        <v>1868</v>
       </c>
       <c r="D18" s="1">
-        <v>1881</v>
+        <v>1868</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>151</v>
+        <v>264</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1340,19 +1337,19 @@
         <v>21</v>
       </c>
       <c r="B19" s="1">
-        <v>1871</v>
+        <v>1855</v>
       </c>
       <c r="D19" s="1">
-        <v>1871</v>
+        <v>1855</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1360,19 +1357,19 @@
         <v>22</v>
       </c>
       <c r="B20" s="1">
-        <v>1870</v>
+        <v>1846</v>
       </c>
       <c r="D20" s="1">
-        <v>1870</v>
+        <v>1846</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>406</v>
+        <v>35</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1380,19 +1377,19 @@
         <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>1863</v>
+        <v>1844</v>
       </c>
       <c r="D21" s="1">
-        <v>1863</v>
+        <v>1844</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1400,19 +1397,19 @@
         <v>24</v>
       </c>
       <c r="B22" s="1">
-        <v>1849</v>
+        <v>1840</v>
       </c>
       <c r="D22" s="1">
-        <v>1849</v>
+        <v>1840</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1420,19 +1417,19 @@
         <v>25</v>
       </c>
       <c r="B23" s="1">
-        <v>1848</v>
+        <v>1834</v>
       </c>
       <c r="D23" s="1">
-        <v>1848</v>
+        <v>1834</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>128</v>
+        <v>314</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1440,19 +1437,19 @@
         <v>26</v>
       </c>
       <c r="B24" s="1">
-        <v>1846</v>
+        <v>1833</v>
       </c>
       <c r="D24" s="1">
-        <v>1846</v>
+        <v>1833</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>35</v>
+        <v>215</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1460,19 +1457,19 @@
         <v>27</v>
       </c>
       <c r="B25" s="1">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="D25" s="1">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
       <c r="F25">
-        <v>225</v>
+        <v>138</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1486,9 +1483,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="22" width="21.7109375" style="3" customWidth="1"/>
-    <col min="23" max="23" width="20.7109375" style="3" customWidth="1"/>
-    <col min="24" max="24" width="21.7109375" style="3" customWidth="1"/>
+    <col min="2" max="24" width="21.7109375" style="3" customWidth="1"/>
     <col min="25" max="25" width="20.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1574,73 +1569,73 @@
         <v>4</v>
       </c>
       <c r="C2" s="3">
-        <v>0.5071950817090514</v>
+        <v>0.5416377027147634</v>
       </c>
       <c r="D2" s="3">
-        <v>0.5644004902404213</v>
+        <v>0.5615679389736461</v>
       </c>
       <c r="E2" s="3">
-        <v>0.6185841220890307</v>
+        <v>0.6307302886162022</v>
       </c>
       <c r="F2" s="3">
-        <v>0.6440338538222926</v>
+        <v>0.6400649998028851</v>
       </c>
       <c r="G2" s="3">
-        <v>0.7210782431975601</v>
+        <v>0.6506046279338725</v>
       </c>
       <c r="H2" s="3">
-        <v>0.7313778578393882</v>
+        <v>0.726830072276731</v>
       </c>
       <c r="I2" s="3">
-        <v>0.7680520031675839</v>
+        <v>0.7469129214289432</v>
       </c>
       <c r="J2" s="3">
+        <v>0.7576391748622517</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0.7628849803052542</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0.7649612635526892</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0.7659946707664889</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0.7690759234333929</v>
+      </c>
+      <c r="O2" s="3">
+        <v>0.777153105314726</v>
+      </c>
+      <c r="P2" s="3">
         <v>0.7791406208194696</v>
       </c>
-      <c r="K2" s="3">
-        <v>0.8376154583713974</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.8376154583713974</v>
-      </c>
-      <c r="M2" s="3">
+      <c r="Q2" s="3">
+        <v>0.8074241816712792</v>
+      </c>
+      <c r="R2" s="3">
+        <v>0.8109791581199478</v>
+      </c>
+      <c r="S2" s="3">
+        <v>0.8221846111535023</v>
+      </c>
+      <c r="T2" s="3">
+        <v>0.8296328234313434</v>
+      </c>
+      <c r="U2" s="3">
+        <v>0.8312539156520465</v>
+      </c>
+      <c r="V2" s="3">
+        <v>0.834459181708983</v>
+      </c>
+      <c r="W2" s="3">
+        <v>0.8391753178526756</v>
+      </c>
+      <c r="X2" s="3">
+        <v>0.8399506946347535</v>
+      </c>
+      <c r="Y2" s="3">
         <v>0.8430219644140362</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0.8445395282300351</v>
-      </c>
-      <c r="O2" s="3">
-        <v>0.8475387239958501</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.8475387239958501</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0.8504903015468027</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.8625119039913111</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0.8691968654550538</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0.8698499490743091</v>
-      </c>
-      <c r="U2" s="3">
-        <v>0.8743442268185462</v>
-      </c>
-      <c r="V2" s="3">
-        <v>0.8829346041256821</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0.8835282880564392</v>
-      </c>
-      <c r="X2" s="3">
-        <v>0.8847078164911643</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>0.8926766600061541</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -1648,73 +1643,73 @@
         <v>5</v>
       </c>
       <c r="B3" s="3">
-        <v>0.4928049182909486</v>
+        <v>0.4583622972852365</v>
       </c>
       <c r="D3" s="3">
-        <v>0.5573116337622928</v>
+        <v>0.5201367220358165</v>
       </c>
       <c r="E3" s="3">
+        <v>0.5910755963149433</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.6007782458900109</v>
+      </c>
+      <c r="G3" s="3">
         <v>0.6117705007810643</v>
       </c>
-      <c r="F3" s="3">
-        <v>0.6374083767444845</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.7152527510491987</v>
-      </c>
       <c r="H3" s="3">
+        <v>0.6924633925795177</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.7140789025853503</v>
+      </c>
+      <c r="J3" s="3">
         <v>0.7256856462717871</v>
       </c>
-      <c r="I3" s="3">
-        <v>0.7628849803052542</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0.7741479777018306</v>
-      </c>
       <c r="K3" s="3">
-        <v>0.8336624691834381</v>
+        <v>0.7313778578393882</v>
       </c>
       <c r="L3" s="3">
-        <v>0.8336624691834381</v>
+        <v>0.7336337024138074</v>
       </c>
       <c r="M3" s="3">
-        <v>0.8391753178526756</v>
+        <v>0.7347570893165466</v>
       </c>
       <c r="N3" s="3">
-        <v>0.840723042661615</v>
+        <v>0.7381090325404187</v>
       </c>
       <c r="O3" s="3">
-        <v>0.8437822479242926</v>
+        <v>0.7469129214289432</v>
       </c>
       <c r="P3" s="3">
-        <v>0.8437822479242926</v>
+        <v>0.7490830628775357</v>
       </c>
       <c r="Q3" s="3">
-        <v>0.8467934030726807</v>
+        <v>0.7801296039931584</v>
       </c>
       <c r="R3" s="3">
-        <v>0.8590630023766738</v>
+        <v>0.784053683887815</v>
       </c>
       <c r="S3" s="3">
-        <v>0.8658895824550439</v>
+        <v>0.7964546997117258</v>
       </c>
       <c r="T3" s="3">
-        <v>0.8665566437895401</v>
+        <v>0.8047246934992595</v>
       </c>
       <c r="U3" s="3">
-        <v>0.8711477984045555</v>
+        <v>0.8065275228171078</v>
       </c>
       <c r="V3" s="3">
-        <v>0.8799266880106169</v>
+        <v>0.8100951586047567</v>
       </c>
       <c r="W3" s="3">
-        <v>0.8805335622474012</v>
+        <v>0.8153518152833006</v>
       </c>
       <c r="X3" s="3">
-        <v>0.8817393593419074</v>
+        <v>0.8162168965756028</v>
       </c>
       <c r="Y3" s="3">
-        <v>0.8898878421811328</v>
+        <v>0.8196458144946892</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -1722,73 +1717,73 @@
         <v>6</v>
       </c>
       <c r="B4" s="3">
-        <v>0.4355995097595788</v>
+        <v>0.438432061026354</v>
       </c>
       <c r="C4" s="3">
-        <v>0.4426883662377072</v>
+        <v>0.4798632779641835</v>
       </c>
       <c r="E4" s="3">
-        <v>0.5558909611168531</v>
+        <v>0.5714631174083814</v>
       </c>
       <c r="F4" s="3">
-        <v>0.5827018849642301</v>
+        <v>0.581301478368915</v>
       </c>
       <c r="G4" s="3">
-        <v>0.6661394245831221</v>
+        <v>0.5924662305843318</v>
       </c>
       <c r="H4" s="3">
-        <v>0.6775605800851006</v>
+        <v>0.6750402010402987</v>
       </c>
       <c r="I4" s="3">
+        <v>0.6973450785898532</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.7093546305987634</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.7152527510491987</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0.7175917231915314</v>
+      </c>
+      <c r="M4" s="3">
         <v>0.718756829898782</v>
       </c>
-      <c r="J4" s="3">
+      <c r="N4" s="3">
+        <v>0.7222345336491706</v>
+      </c>
+      <c r="O4" s="3">
         <v>0.7313778578393882</v>
       </c>
-      <c r="K4" s="3">
-        <v>0.7992399910868982</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0.7992399910868982</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0.8056276940436502</v>
-      </c>
-      <c r="N4" s="3">
+      <c r="P4" s="3">
+        <v>0.7336337024138074</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.7659946707664889</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0.770096676660982</v>
+      </c>
+      <c r="S4" s="3">
+        <v>0.7830774434096761</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0.7917488375081845</v>
+      </c>
+      <c r="U4" s="3">
+        <v>0.7936407431881689</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0.7973863140277038</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0.8029091701538159</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0.8038185194246843</v>
+      </c>
+      <c r="Y4" s="3">
         <v>0.8074241816712792</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0.8109791581199478</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.8109791581199478</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0.8144835875047122</v>
-      </c>
-      <c r="R4" s="3">
-        <v>0.8288176477542757</v>
-      </c>
-      <c r="S4" s="3">
-        <v>0.8368309660028946</v>
-      </c>
-      <c r="T4" s="3">
-        <v>0.8376154583713974</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0.8430219644140362</v>
-      </c>
-      <c r="V4" s="3">
-        <v>0.8533946221118819</v>
-      </c>
-      <c r="W4" s="3">
-        <v>0.8541133619456244</v>
-      </c>
-      <c r="X4" s="3">
-        <v>0.8555420748926974</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>0.8652197052285583</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1796,73 +1791,73 @@
         <v>7</v>
       </c>
       <c r="B5" s="3">
-        <v>0.3814158779109693</v>
+        <v>0.3692697113837977</v>
       </c>
       <c r="C5" s="3">
-        <v>0.3882294992189357</v>
+        <v>0.4089244036850566</v>
       </c>
       <c r="D5" s="3">
-        <v>0.4441090388831469</v>
+        <v>0.4285368825916186</v>
       </c>
       <c r="F5" s="3">
-        <v>0.527315973006493</v>
+        <v>0.5100724469274385</v>
       </c>
       <c r="G5" s="3">
-        <v>0.6145013610085578</v>
+        <v>0.5215733330511455</v>
       </c>
       <c r="H5" s="3">
-        <v>0.626699081666732</v>
+        <v>0.6090326034042396</v>
       </c>
       <c r="I5" s="3">
+        <v>0.6334077000711676</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.6466688423256146</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.6532171672188698</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.655820505912395</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.6571186864870786</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0.6609990912463583</v>
+      </c>
+      <c r="O5" s="3">
         <v>0.6712405808158318</v>
       </c>
-      <c r="J5" s="3">
-        <v>0.6850596089933503</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0.7607960909891424</v>
-      </c>
-      <c r="L5" s="3">
-        <v>0.7607960909891424</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0.7680520031675839</v>
-      </c>
-      <c r="N5" s="3">
-        <v>0.770096676660982</v>
-      </c>
-      <c r="O5" s="3">
-        <v>0.7741479777018306</v>
-      </c>
       <c r="P5" s="3">
-        <v>0.7741479777018306</v>
+        <v>0.6737761878883222</v>
       </c>
       <c r="Q5" s="3">
-        <v>0.7781484542191325</v>
+        <v>0.7105400123698378</v>
       </c>
       <c r="R5" s="3">
-        <v>0.7945819150362295</v>
+        <v>0.7152527510491987</v>
       </c>
       <c r="S5" s="3">
-        <v>0.8038185194246843</v>
+        <v>0.730245413297424</v>
       </c>
       <c r="T5" s="3">
-        <v>0.8047246934992595</v>
+        <v>0.7403284195148304</v>
       </c>
       <c r="U5" s="3">
-        <v>0.8109791581199478</v>
+        <v>0.7425355589430698</v>
       </c>
       <c r="V5" s="3">
-        <v>0.8230246289217321</v>
+        <v>0.7469129214289432</v>
       </c>
       <c r="W5" s="3">
-        <v>0.8238615285055724</v>
+        <v>0.7533860777856145</v>
       </c>
       <c r="X5" s="3">
-        <v>0.8255259873611817</v>
+        <v>0.7544540419421866</v>
       </c>
       <c r="Y5" s="3">
-        <v>0.8368309660028946</v>
+        <v>0.7586946201468556</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1870,73 +1865,73 @@
         <v>8</v>
       </c>
       <c r="B6" s="3">
-        <v>0.3559661461777073</v>
+        <v>0.3599350001971149</v>
       </c>
       <c r="C6" s="3">
-        <v>0.3625916232555155</v>
+        <v>0.399221754109989</v>
       </c>
       <c r="D6" s="3">
-        <v>0.4172981150357699</v>
+        <v>0.4186985216310851</v>
       </c>
       <c r="E6" s="3">
-        <v>0.4726840269935071</v>
+        <v>0.4899275530725615</v>
       </c>
       <c r="G6" s="3">
-        <v>0.5882899718631628</v>
+        <v>0.5115108912177917</v>
       </c>
       <c r="H6" s="3">
-        <v>0.6007782458900109</v>
+        <v>0.5993967967092568</v>
       </c>
       <c r="I6" s="3">
+        <v>0.6240017586176672</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.6374083767444845</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0.6440338538222926</v>
+      </c>
+      <c r="L6" s="3">
         <v>0.6466688423256146</v>
       </c>
-      <c r="J6" s="3">
-        <v>0.6609990912463583</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0.7403284195148304</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0.7403284195148304</v>
-      </c>
       <c r="M6" s="3">
-        <v>0.7479995411960544</v>
+        <v>0.6479830132503057</v>
       </c>
       <c r="N6" s="3">
-        <v>0.750163481828642</v>
+        <v>0.6519120398746636</v>
       </c>
       <c r="O6" s="3">
-        <v>0.7544540419421866</v>
+        <v>0.6622877974308888</v>
       </c>
       <c r="P6" s="3">
-        <v>0.7544540419421866</v>
+        <v>0.6648579785547648</v>
       </c>
       <c r="Q6" s="3">
-        <v>0.7586946201468556</v>
+        <v>0.7021826020905207</v>
       </c>
       <c r="R6" s="3">
-        <v>0.7761545753418307</v>
+        <v>0.7069752948085409</v>
       </c>
       <c r="S6" s="3">
-        <v>0.7859966022821575</v>
+        <v>0.7222345336491706</v>
       </c>
       <c r="T6" s="3">
-        <v>0.7869632793894692</v>
+        <v>0.7325072897556676</v>
       </c>
       <c r="U6" s="3">
-        <v>0.7936407431881689</v>
+        <v>0.7347570893165466</v>
       </c>
       <c r="V6" s="3">
-        <v>0.8065275228171078</v>
+        <v>0.7392202541406678</v>
       </c>
       <c r="W6" s="3">
-        <v>0.8074241816712792</v>
+        <v>0.7458232083504994</v>
       </c>
       <c r="X6" s="3">
-        <v>0.809207997485838</v>
+        <v>0.7469129214289432</v>
       </c>
       <c r="Y6" s="3">
-        <v>0.821341471737012</v>
+        <v>0.7512407935337106</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1944,73 +1939,73 @@
         <v>9</v>
       </c>
       <c r="B7" s="3">
-        <v>0.2789217568024399</v>
+        <v>0.3493953720661275</v>
       </c>
       <c r="C7" s="3">
-        <v>0.2847472489508014</v>
+        <v>0.3882294992189357</v>
       </c>
       <c r="D7" s="3">
-        <v>0.3338605754168779</v>
+        <v>0.4075337694156682</v>
       </c>
       <c r="E7" s="3">
-        <v>0.3854986389914422</v>
+        <v>0.4784266669488546</v>
       </c>
       <c r="F7" s="3">
-        <v>0.4117100281368372</v>
+        <v>0.4884891087822083</v>
       </c>
       <c r="H7" s="3">
-        <v>0.5129491448928637</v>
+        <v>0.5882899718631628</v>
       </c>
       <c r="I7" s="3">
-        <v>0.5615679389736461</v>
+        <v>0.6131368201531431</v>
       </c>
       <c r="J7" s="3">
-        <v>0.577092475825329</v>
+        <v>0.626699081666732</v>
       </c>
       <c r="K7" s="3">
-        <v>0.6661394245831221</v>
+        <v>0.6334077000711676</v>
       </c>
       <c r="L7" s="3">
-        <v>0.6661394245831221</v>
+        <v>0.6360768996878818</v>
       </c>
       <c r="M7" s="3">
-        <v>0.6750402010402987</v>
+        <v>0.6374083767444845</v>
       </c>
       <c r="N7" s="3">
-        <v>0.6775605800851006</v>
+        <v>0.641390111955618</v>
       </c>
       <c r="O7" s="3">
-        <v>0.6825703854747719</v>
+        <v>0.6519120398746636</v>
       </c>
       <c r="P7" s="3">
-        <v>0.6825703854747719</v>
+        <v>0.654519994382466</v>
       </c>
       <c r="Q7" s="3">
-        <v>0.6875382482123418</v>
+        <v>0.6924633925795177</v>
       </c>
       <c r="R7" s="3">
-        <v>0.7081663882812006</v>
+        <v>0.6973450785898532</v>
       </c>
       <c r="S7" s="3">
-        <v>0.7199190059471519</v>
+        <v>0.7129021574054539</v>
       </c>
       <c r="T7" s="3">
-        <v>0.7210782431975601</v>
+        <v>0.7233878694391705</v>
       </c>
       <c r="U7" s="3">
-        <v>0.7291099628977525</v>
+        <v>0.7256856462717871</v>
       </c>
       <c r="V7" s="3">
-        <v>0.7447304068650347</v>
+        <v>0.730245413297424</v>
       </c>
       <c r="W7" s="3">
-        <v>0.7458232083504994</v>
+        <v>0.7369947605406894</v>
       </c>
       <c r="X7" s="3">
-        <v>0.7479995411960544</v>
+        <v>0.7381090325404187</v>
       </c>
       <c r="Y7" s="3">
-        <v>0.7628849803052542</v>
+        <v>0.7425355589430698</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -2018,73 +2013,73 @@
         <v>10</v>
       </c>
       <c r="B8" s="3">
-        <v>0.2686221421606117</v>
+        <v>0.2731699277232689</v>
       </c>
       <c r="C8" s="3">
-        <v>0.2743143537282129</v>
+        <v>0.3075366074204823</v>
       </c>
       <c r="D8" s="3">
-        <v>0.3224394199148994</v>
+        <v>0.3249597989597013</v>
       </c>
       <c r="E8" s="3">
-        <v>0.373300918333268</v>
+        <v>0.3909673965957605</v>
       </c>
       <c r="F8" s="3">
-        <v>0.399221754109989</v>
+        <v>0.4006032032907432</v>
       </c>
       <c r="G8" s="3">
-        <v>0.4870508551071362</v>
+        <v>0.4117100281368372</v>
       </c>
       <c r="I8" s="3">
-        <v>0.5487743358597419</v>
+        <v>0.5258809308911691</v>
       </c>
       <c r="J8" s="3">
-        <v>0.5644004902404213</v>
+        <v>0.5402082283237456</v>
       </c>
       <c r="K8" s="3">
+        <v>0.5473485180458647</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0.550199353253537</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.5516235473109605</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0.5558909611168531</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.5672288443429522</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0.5700528235839882</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.6117705007810643</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0.6172250309049463</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0.6347433350523167</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0.6466688423256146</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0.6492949471109635</v>
+      </c>
+      <c r="V8" s="3">
         <v>0.654519994382466</v>
       </c>
-      <c r="L8" s="3">
-        <v>0.654519994382466</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="W8" s="3">
+        <v>0.6622877974308888</v>
+      </c>
+      <c r="X8" s="3">
         <v>0.6635740980412955</v>
       </c>
-      <c r="N8" s="3">
-        <v>0.6661394245831221</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0.6712405808158318</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0.6712405808158318</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0.676301669492737</v>
-      </c>
-      <c r="R8" s="3">
-        <v>0.6973450785898532</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0.7093546305987634</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0.7105400123698378</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0.718756829898782</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0.7347570893165466</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0.7358774441014764</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0.7381090325404187</v>
-      </c>
       <c r="Y8" s="3">
-        <v>0.7533860777856145</v>
+        <v>0.6686949563073317</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -2092,73 +2087,73 @@
         <v>11</v>
       </c>
       <c r="B9" s="3">
-        <v>0.231947996832416</v>
+        <v>0.2530870785710568</v>
       </c>
       <c r="C9" s="3">
-        <v>0.2371150196947458</v>
+        <v>0.2859210974146497</v>
       </c>
       <c r="D9" s="3">
-        <v>0.2812431701012181</v>
+        <v>0.3026549214101468</v>
       </c>
       <c r="E9" s="3">
-        <v>0.3287594191841682</v>
+        <v>0.3665922999288324</v>
       </c>
       <c r="F9" s="3">
-        <v>0.3533311576743853</v>
+        <v>0.3759982413823328</v>
       </c>
       <c r="G9" s="3">
-        <v>0.438432061026354</v>
+        <v>0.3868631798468569</v>
       </c>
       <c r="H9" s="3">
-        <v>0.4512256641402582</v>
+        <v>0.4741190691088309</v>
       </c>
       <c r="J9" s="3">
-        <v>0.515824985264735</v>
+        <v>0.5143871841659987</v>
       </c>
       <c r="K9" s="3">
-        <v>0.6090326034042396</v>
+        <v>0.5215733330511455</v>
       </c>
       <c r="L9" s="3">
-        <v>0.6090326034042396</v>
+        <v>0.5244454611206615</v>
       </c>
       <c r="M9" s="3">
-        <v>0.6185841220890307</v>
+        <v>0.5258809308911691</v>
       </c>
       <c r="N9" s="3">
-        <v>0.6212967231224545</v>
+        <v>0.5301846800039021</v>
       </c>
       <c r="O9" s="3">
-        <v>0.626699081666732</v>
+        <v>0.5416377027147634</v>
       </c>
       <c r="P9" s="3">
-        <v>0.626699081666732</v>
+        <v>0.544494573083008</v>
       </c>
       <c r="Q9" s="3">
-        <v>0.6320700121000735</v>
+        <v>0.5868950233791</v>
       </c>
       <c r="R9" s="3">
-        <v>0.654519994382466</v>
+        <v>0.5924662305843318</v>
       </c>
       <c r="S9" s="3">
-        <v>0.667418421873223</v>
+        <v>0.6104024220946891</v>
       </c>
       <c r="T9" s="3">
-        <v>0.6686949563073317</v>
+        <v>0.6226501957872621</v>
       </c>
       <c r="U9" s="3">
-        <v>0.6775605800851006</v>
+        <v>0.6253513933075368</v>
       </c>
       <c r="V9" s="3">
-        <v>0.6949097127295025</v>
+        <v>0.6307302886162022</v>
       </c>
       <c r="W9" s="3">
-        <v>0.6961287704295998</v>
+        <v>0.6387377491117249</v>
       </c>
       <c r="X9" s="3">
-        <v>0.698558626418023</v>
+        <v>0.6400649998028851</v>
       </c>
       <c r="Y9" s="3">
-        <v>0.7152527510491987</v>
+        <v>0.6453524504393825</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -2166,73 +2161,73 @@
         <v>12</v>
       </c>
       <c r="B10" s="3">
-        <v>0.2208593791805304</v>
+        <v>0.2423608251377483</v>
       </c>
       <c r="C10" s="3">
-        <v>0.2258520222981694</v>
+        <v>0.2743143537282129</v>
       </c>
       <c r="D10" s="3">
-        <v>0.2686221421606117</v>
+        <v>0.2906453694012366</v>
       </c>
       <c r="E10" s="3">
-        <v>0.3149403910066497</v>
+        <v>0.3533311576743853</v>
       </c>
       <c r="F10" s="3">
-        <v>0.3390009087536417</v>
+        <v>0.3625916232555155</v>
       </c>
       <c r="G10" s="3">
-        <v>0.422907524174671</v>
+        <v>0.373300918333268</v>
       </c>
       <c r="H10" s="3">
-        <v>0.4355995097595788</v>
+        <v>0.4597917716762543</v>
       </c>
       <c r="I10" s="3">
-        <v>0.4841750147352649</v>
+        <v>0.4856128158340013</v>
       </c>
       <c r="K10" s="3">
-        <v>0.5938553852361779</v>
+        <v>0.5071950817090514</v>
       </c>
       <c r="L10" s="3">
-        <v>0.5938553852361779</v>
+        <v>0.5100724469274385</v>
       </c>
       <c r="M10" s="3">
-        <v>0.6035363185261781</v>
+        <v>0.5115108912177917</v>
       </c>
       <c r="N10" s="3">
-        <v>0.6062878237854281</v>
+        <v>0.515824985264735</v>
       </c>
       <c r="O10" s="3">
+        <v>0.527315973006493</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0.5301846800039021</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0.5728722513945045</v>
+      </c>
+      <c r="R10" s="3">
+        <v>0.5784967523447427</v>
+      </c>
+      <c r="S10" s="3">
+        <v>0.596629173305774</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0.6090326034042396</v>
+      </c>
+      <c r="U10" s="3">
         <v>0.6117705007810643</v>
       </c>
-      <c r="P10" s="3">
-        <v>0.6117705007810643</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="V10" s="3">
         <v>0.6172250309049463</v>
       </c>
-      <c r="R10" s="3">
-        <v>0.6400649998028851</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0.6532171672188698</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0.654519994382466</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0.6635740980412955</v>
-      </c>
-      <c r="V10" s="3">
-        <v>0.6813218351663937</v>
-      </c>
       <c r="W10" s="3">
-        <v>0.6825703854747719</v>
+        <v>0.6253513933075368</v>
       </c>
       <c r="X10" s="3">
-        <v>0.6850596089933503</v>
+        <v>0.626699081666732</v>
       </c>
       <c r="Y10" s="3">
-        <v>0.7021826020905207</v>
+        <v>0.6320700121000735</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -2240,73 +2235,73 @@
         <v>13</v>
       </c>
       <c r="B11" s="3">
-        <v>0.1623845416286026</v>
+        <v>0.2371150196947458</v>
       </c>
       <c r="C11" s="3">
-        <v>0.1663375308165619</v>
+        <v>0.2686221421606117</v>
       </c>
       <c r="D11" s="3">
-        <v>0.2007600089131018</v>
+        <v>0.2847472489508014</v>
       </c>
       <c r="E11" s="3">
-        <v>0.2392039090108577</v>
+        <v>0.3467828327811303</v>
       </c>
       <c r="F11" s="3">
-        <v>0.2596715804851696</v>
+        <v>0.3559661461777073</v>
       </c>
       <c r="G11" s="3">
-        <v>0.3338605754168779</v>
+        <v>0.3665922999288324</v>
       </c>
       <c r="H11" s="3">
-        <v>0.3454800056175341</v>
+        <v>0.4526514819541353</v>
       </c>
       <c r="I11" s="3">
-        <v>0.3909673965957605</v>
+        <v>0.4784266669488546</v>
       </c>
       <c r="J11" s="3">
-        <v>0.4061446147638222</v>
+        <v>0.4928049182909486</v>
       </c>
       <c r="L11" s="3">
-        <v>0.5</v>
+        <v>0.5028781995748109</v>
       </c>
       <c r="M11" s="3">
-        <v>0.5100724469274385</v>
+        <v>0.5043172397550598</v>
       </c>
       <c r="N11" s="3">
-        <v>0.5129491448928637</v>
+        <v>0.5086338358210827</v>
       </c>
       <c r="O11" s="3">
-        <v>0.5186997779295586</v>
+        <v>0.5201367220358165</v>
       </c>
       <c r="P11" s="3">
-        <v>0.5186997779295586</v>
+        <v>0.5230095872975623</v>
       </c>
       <c r="Q11" s="3">
-        <v>0.5244454611206615</v>
+        <v>0.5658152030692333</v>
       </c>
       <c r="R11" s="3">
-        <v>0.5487743358597419</v>
+        <v>0.5714631174083814</v>
       </c>
       <c r="S11" s="3">
-        <v>0.5629847281035958</v>
+        <v>0.5896835031399501</v>
       </c>
       <c r="T11" s="3">
-        <v>0.5644004902404213</v>
+        <v>0.6021580931747169</v>
       </c>
       <c r="U11" s="3">
-        <v>0.5742802036545245</v>
+        <v>0.6049129020079569</v>
       </c>
       <c r="V11" s="3">
-        <v>0.5938553852361779</v>
+        <v>0.6104024220946891</v>
       </c>
       <c r="W11" s="3">
-        <v>0.5952430396515719</v>
+        <v>0.6185841220890307</v>
       </c>
       <c r="X11" s="3">
-        <v>0.5980137657693436</v>
+        <v>0.6199413590445233</v>
       </c>
       <c r="Y11" s="3">
-        <v>0.6172250309049463</v>
+        <v>0.6253513933075368</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -2314,73 +2309,73 @@
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>0.1623845416286026</v>
+        <v>0.2350387364473108</v>
       </c>
       <c r="C12" s="3">
-        <v>0.1663375308165619</v>
+        <v>0.2663662975861926</v>
       </c>
       <c r="D12" s="3">
-        <v>0.2007600089131018</v>
+        <v>0.2824082768084685</v>
       </c>
       <c r="E12" s="3">
-        <v>0.2392039090108577</v>
+        <v>0.344179494087605</v>
       </c>
       <c r="F12" s="3">
-        <v>0.2596715804851696</v>
+        <v>0.3533311576743853</v>
       </c>
       <c r="G12" s="3">
-        <v>0.3338605754168779</v>
+        <v>0.3639231003121181</v>
       </c>
       <c r="H12" s="3">
-        <v>0.3454800056175341</v>
+        <v>0.449800646746463</v>
       </c>
       <c r="I12" s="3">
-        <v>0.3909673965957605</v>
+        <v>0.4755545388793386</v>
       </c>
       <c r="J12" s="3">
-        <v>0.4061446147638222</v>
+        <v>0.4899275530725615</v>
       </c>
       <c r="K12" s="3">
-        <v>0.5</v>
+        <v>0.4971218004251891</v>
       </c>
       <c r="M12" s="3">
-        <v>0.5100724469274385</v>
+        <v>0.5014391117091528</v>
       </c>
       <c r="N12" s="3">
-        <v>0.5129491448928637</v>
+        <v>0.5057562084111449</v>
       </c>
       <c r="O12" s="3">
-        <v>0.5186997779295586</v>
+        <v>0.5172625244323762</v>
       </c>
       <c r="P12" s="3">
-        <v>0.5186997779295586</v>
+        <v>0.5201367220358165</v>
       </c>
       <c r="Q12" s="3">
-        <v>0.5244454611206615</v>
+        <v>0.5629847281035958</v>
       </c>
       <c r="R12" s="3">
-        <v>0.5487743358597419</v>
+        <v>0.5686413918836677</v>
       </c>
       <c r="S12" s="3">
-        <v>0.5629847281035958</v>
+        <v>0.5868950233791</v>
       </c>
       <c r="T12" s="3">
-        <v>0.5644004902404213</v>
+        <v>0.5993967967092568</v>
       </c>
       <c r="U12" s="3">
-        <v>0.5742802036545245</v>
+        <v>0.6021580931747169</v>
       </c>
       <c r="V12" s="3">
-        <v>0.5938553852361779</v>
+        <v>0.6076610641268197</v>
       </c>
       <c r="W12" s="3">
-        <v>0.5952430396515719</v>
+        <v>0.615864104253756</v>
       </c>
       <c r="X12" s="3">
-        <v>0.5980137657693436</v>
+        <v>0.6172250309049463</v>
       </c>
       <c r="Y12" s="3">
-        <v>0.6172250309049463</v>
+        <v>0.6226501957872621</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -2388,73 +2383,73 @@
         <v>15</v>
       </c>
       <c r="B13" s="3">
-        <v>0.1569780355859638</v>
+        <v>0.2340053292335112</v>
       </c>
       <c r="C13" s="3">
-        <v>0.1608246821473244</v>
+        <v>0.2652429106834533</v>
       </c>
       <c r="D13" s="3">
-        <v>0.1943723059563498</v>
+        <v>0.2812431701012181</v>
       </c>
       <c r="E13" s="3">
-        <v>0.231947996832416</v>
+        <v>0.3428813135129214</v>
       </c>
       <c r="F13" s="3">
-        <v>0.2520004588039456</v>
+        <v>0.3520169867496943</v>
       </c>
       <c r="G13" s="3">
-        <v>0.3249597989597013</v>
+        <v>0.3625916232555155</v>
       </c>
       <c r="H13" s="3">
-        <v>0.3364259019587045</v>
+        <v>0.4483764526890395</v>
       </c>
       <c r="I13" s="3">
-        <v>0.3814158779109693</v>
+        <v>0.4741190691088309</v>
       </c>
       <c r="J13" s="3">
-        <v>0.3964636814738219</v>
+        <v>0.4884891087822083</v>
       </c>
       <c r="K13" s="3">
-        <v>0.4899275530725615</v>
+        <v>0.4956827602449402</v>
       </c>
       <c r="L13" s="3">
-        <v>0.4899275530725615</v>
+        <v>0.4985608882908471</v>
       </c>
       <c r="N13" s="3">
-        <v>0.5028781995748109</v>
+        <v>0.5043172397550598</v>
       </c>
       <c r="O13" s="3">
-        <v>0.5086338358210827</v>
+        <v>0.515824985264735</v>
       </c>
       <c r="P13" s="3">
-        <v>0.5086338358210827</v>
+        <v>0.5186997779295586</v>
       </c>
       <c r="Q13" s="3">
-        <v>0.5143871841659987</v>
+        <v>0.5615679389736461</v>
       </c>
       <c r="R13" s="3">
-        <v>0.5387780920571715</v>
+        <v>0.5672288443429522</v>
       </c>
       <c r="S13" s="3">
-        <v>0.5530468951694625</v>
+        <v>0.5854986786718095</v>
       </c>
       <c r="T13" s="3">
-        <v>0.554469374021676</v>
+        <v>0.5980137657693436</v>
       </c>
       <c r="U13" s="3">
-        <v>0.5644004902404213</v>
+        <v>0.6007782458900109</v>
       </c>
       <c r="V13" s="3">
-        <v>0.584100958813678</v>
+        <v>0.6062878237854281</v>
       </c>
       <c r="W13" s="3">
-        <v>0.5854986786718095</v>
+        <v>0.6145013610085578</v>
       </c>
       <c r="X13" s="3">
-        <v>0.5882899718631628</v>
+        <v>0.615864104253756</v>
       </c>
       <c r="Y13" s="3">
-        <v>0.6076610641268197</v>
+        <v>0.6212967231224545</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -2462,73 +2457,73 @@
         <v>16</v>
       </c>
       <c r="B14" s="3">
-        <v>0.1554604717699649</v>
+        <v>0.2309240765666072</v>
       </c>
       <c r="C14" s="3">
-        <v>0.159276957338385</v>
+        <v>0.2618909674595814</v>
       </c>
       <c r="D14" s="3">
-        <v>0.1925758183287208</v>
+        <v>0.2777654663508294</v>
       </c>
       <c r="E14" s="3">
-        <v>0.229903323339018</v>
+        <v>0.3390009087536417</v>
       </c>
       <c r="F14" s="3">
-        <v>0.249836518171358</v>
+        <v>0.3480879601253363</v>
       </c>
       <c r="G14" s="3">
-        <v>0.3224394199148994</v>
+        <v>0.358609888044382</v>
       </c>
       <c r="H14" s="3">
-        <v>0.3338605754168779</v>
+        <v>0.4441090388831469</v>
       </c>
       <c r="I14" s="3">
-        <v>0.3787032768775454</v>
+        <v>0.469815319996098</v>
       </c>
       <c r="J14" s="3">
-        <v>0.3937121762145718</v>
+        <v>0.4841750147352649</v>
       </c>
       <c r="K14" s="3">
-        <v>0.4870508551071362</v>
+        <v>0.4913661641789174</v>
       </c>
       <c r="L14" s="3">
-        <v>0.4870508551071362</v>
+        <v>0.4942437915888551</v>
       </c>
       <c r="M14" s="3">
-        <v>0.4971218004251891</v>
+        <v>0.4956827602449402</v>
       </c>
       <c r="O14" s="3">
-        <v>0.5057562084111449</v>
+        <v>0.5115108912177917</v>
       </c>
       <c r="P14" s="3">
-        <v>0.5057562084111449</v>
+        <v>0.5143871841659987</v>
       </c>
       <c r="Q14" s="3">
-        <v>0.5115108912177917</v>
+        <v>0.5573116337622928</v>
       </c>
       <c r="R14" s="3">
-        <v>0.5359159269451023</v>
+        <v>0.5629847281035958</v>
       </c>
       <c r="S14" s="3">
-        <v>0.550199353253537</v>
+        <v>0.581301478368915</v>
       </c>
       <c r="T14" s="3">
-        <v>0.5516235473109605</v>
+        <v>0.5938553852361779</v>
       </c>
       <c r="U14" s="3">
-        <v>0.5615679389736461</v>
+        <v>0.596629173305774</v>
       </c>
       <c r="V14" s="3">
-        <v>0.581301478368915</v>
+        <v>0.6021580931747169</v>
       </c>
       <c r="W14" s="3">
-        <v>0.5827018849642301</v>
+        <v>0.6104024220946891</v>
       </c>
       <c r="X14" s="3">
-        <v>0.5854986786718095</v>
+        <v>0.6117705007810643</v>
       </c>
       <c r="Y14" s="3">
-        <v>0.6049129020079569</v>
+        <v>0.6172250309049463</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -2536,73 +2531,73 @@
         <v>17</v>
       </c>
       <c r="B15" s="3">
-        <v>0.15246127600415</v>
+        <v>0.222846894685274</v>
       </c>
       <c r="C15" s="3">
-        <v>0.1562177520757074</v>
+        <v>0.2530870785710568</v>
       </c>
       <c r="D15" s="3">
-        <v>0.1890208418800522</v>
+        <v>0.2686221421606117</v>
       </c>
       <c r="E15" s="3">
-        <v>0.2258520222981694</v>
+        <v>0.3287594191841682</v>
       </c>
       <c r="F15" s="3">
-        <v>0.2455459580578135</v>
+        <v>0.3377122025691112</v>
       </c>
       <c r="G15" s="3">
-        <v>0.3174296145252281</v>
+        <v>0.3480879601253363</v>
       </c>
       <c r="H15" s="3">
-        <v>0.3287594191841682</v>
+        <v>0.4327711556570478</v>
       </c>
       <c r="I15" s="3">
-        <v>0.373300918333268</v>
+        <v>0.4583622972852365</v>
       </c>
       <c r="J15" s="3">
-        <v>0.3882294992189357</v>
+        <v>0.4726840269935071</v>
       </c>
       <c r="K15" s="3">
-        <v>0.4813002220704414</v>
+        <v>0.4798632779641835</v>
       </c>
       <c r="L15" s="3">
-        <v>0.4813002220704414</v>
+        <v>0.4827374755676238</v>
       </c>
       <c r="M15" s="3">
-        <v>0.4913661641789174</v>
+        <v>0.4841750147352649</v>
       </c>
       <c r="N15" s="3">
-        <v>0.4942437915888551</v>
+        <v>0.4884891087822083</v>
       </c>
       <c r="P15" s="3">
-        <v>0.5</v>
+        <v>0.5028781995748109</v>
       </c>
       <c r="Q15" s="3">
-        <v>0.5057562084111449</v>
+        <v>0.5459219227804837</v>
       </c>
       <c r="R15" s="3">
-        <v>0.5301846800039021</v>
+        <v>0.5516235473109605</v>
       </c>
       <c r="S15" s="3">
-        <v>0.544494573083008</v>
+        <v>0.5700528235839882</v>
       </c>
       <c r="T15" s="3">
-        <v>0.5459219227804837</v>
+        <v>0.5827018849642301</v>
       </c>
       <c r="U15" s="3">
-        <v>0.5558909611168531</v>
+        <v>0.5854986786718095</v>
       </c>
       <c r="V15" s="3">
-        <v>0.5756869523764296</v>
+        <v>0.5910755963149433</v>
       </c>
       <c r="W15" s="3">
-        <v>0.577092475825329</v>
+        <v>0.5993967967092568</v>
       </c>
       <c r="X15" s="3">
-        <v>0.5798997603578815</v>
+        <v>0.6007782458900109</v>
       </c>
       <c r="Y15" s="3">
-        <v>0.5993967967092568</v>
+        <v>0.6062878237854281</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2610,73 +2605,73 @@
         <v>18</v>
       </c>
       <c r="B16" s="3">
-        <v>0.15246127600415</v>
+        <v>0.2208593791805304</v>
       </c>
       <c r="C16" s="3">
-        <v>0.1562177520757074</v>
+        <v>0.2509169371224644</v>
       </c>
       <c r="D16" s="3">
-        <v>0.1890208418800522</v>
+        <v>0.2663662975861926</v>
       </c>
       <c r="E16" s="3">
-        <v>0.2258520222981694</v>
+        <v>0.3262238121116778</v>
       </c>
       <c r="F16" s="3">
-        <v>0.2455459580578135</v>
+        <v>0.3351420214452352</v>
       </c>
       <c r="G16" s="3">
-        <v>0.3174296145252281</v>
+        <v>0.3454800056175341</v>
       </c>
       <c r="H16" s="3">
-        <v>0.3287594191841682</v>
+        <v>0.4299471764160118</v>
       </c>
       <c r="I16" s="3">
-        <v>0.373300918333268</v>
+        <v>0.4555054269169921</v>
       </c>
       <c r="J16" s="3">
-        <v>0.3882294992189357</v>
+        <v>0.469815319996098</v>
       </c>
       <c r="K16" s="3">
+        <v>0.4769904127024377</v>
+      </c>
+      <c r="L16" s="3">
+        <v>0.4798632779641835</v>
+      </c>
+      <c r="M16" s="3">
         <v>0.4813002220704414</v>
       </c>
-      <c r="L16" s="3">
-        <v>0.4813002220704414</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0.4913661641789174</v>
-      </c>
       <c r="N16" s="3">
-        <v>0.4942437915888551</v>
+        <v>0.4856128158340013</v>
       </c>
       <c r="O16" s="3">
-        <v>0.5</v>
+        <v>0.4971218004251891</v>
       </c>
       <c r="Q16" s="3">
-        <v>0.5057562084111449</v>
+        <v>0.5430664920222119</v>
       </c>
       <c r="R16" s="3">
-        <v>0.5301846800039021</v>
+        <v>0.5487743358597419</v>
       </c>
       <c r="S16" s="3">
-        <v>0.544494573083008</v>
+        <v>0.5672288443429522</v>
       </c>
       <c r="T16" s="3">
-        <v>0.5459219227804837</v>
+        <v>0.5798997603578815</v>
       </c>
       <c r="U16" s="3">
-        <v>0.5558909611168531</v>
+        <v>0.5827018849642301</v>
       </c>
       <c r="V16" s="3">
-        <v>0.5756869523764296</v>
+        <v>0.5882899718631628</v>
       </c>
       <c r="W16" s="3">
-        <v>0.577092475825329</v>
+        <v>0.596629173305774</v>
       </c>
       <c r="X16" s="3">
-        <v>0.5798997603578815</v>
+        <v>0.5980137657693436</v>
       </c>
       <c r="Y16" s="3">
-        <v>0.5993967967092568</v>
+        <v>0.6035363185261781</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2684,73 +2679,73 @@
         <v>19</v>
       </c>
       <c r="B17" s="3">
-        <v>0.1495096984531974</v>
+        <v>0.1925758183287208</v>
       </c>
       <c r="C17" s="3">
-        <v>0.1532065969273193</v>
+        <v>0.2198703960068415</v>
       </c>
       <c r="D17" s="3">
-        <v>0.1855164124952878</v>
+        <v>0.2340053292335112</v>
       </c>
       <c r="E17" s="3">
-        <v>0.2218515457808675</v>
+        <v>0.2894599876301622</v>
       </c>
       <c r="F17" s="3">
-        <v>0.2413053798531443</v>
+        <v>0.2978173979094794</v>
       </c>
       <c r="G17" s="3">
-        <v>0.3124617517876582</v>
+        <v>0.3075366074204823</v>
       </c>
       <c r="H17" s="3">
-        <v>0.3236983305072631</v>
+        <v>0.3882294992189357</v>
       </c>
       <c r="I17" s="3">
-        <v>0.3679299878999264</v>
+        <v>0.4131049766209</v>
       </c>
       <c r="J17" s="3">
-        <v>0.3827749690950537</v>
+        <v>0.4271277486054956</v>
       </c>
       <c r="K17" s="3">
-        <v>0.4755545388793386</v>
+        <v>0.4341847969307668</v>
       </c>
       <c r="L17" s="3">
-        <v>0.4755545388793386</v>
+        <v>0.4370152718964042</v>
       </c>
       <c r="M17" s="3">
-        <v>0.4856128158340013</v>
+        <v>0.438432061026354</v>
       </c>
       <c r="N17" s="3">
-        <v>0.4884891087822083</v>
+        <v>0.4426883662377072</v>
       </c>
       <c r="O17" s="3">
-        <v>0.4942437915888551</v>
+        <v>0.4540780772195163</v>
       </c>
       <c r="P17" s="3">
-        <v>0.4942437915888551</v>
+        <v>0.4569335079777882</v>
       </c>
       <c r="R17" s="3">
+        <v>0.5057562084111449</v>
+      </c>
+      <c r="S17" s="3">
         <v>0.5244454611206615</v>
       </c>
-      <c r="S17" s="3">
-        <v>0.5387780920571715</v>
-      </c>
       <c r="T17" s="3">
+        <v>0.5373473171664928</v>
+      </c>
+      <c r="U17" s="3">
         <v>0.5402082283237456</v>
       </c>
-      <c r="U17" s="3">
-        <v>0.550199353253537</v>
-      </c>
       <c r="V17" s="3">
-        <v>0.5700528235839882</v>
+        <v>0.5459219227804837</v>
       </c>
       <c r="W17" s="3">
-        <v>0.5714631174083814</v>
+        <v>0.554469374021676</v>
       </c>
       <c r="X17" s="3">
-        <v>0.5742802036545245</v>
+        <v>0.5558909611168531</v>
       </c>
       <c r="Y17" s="3">
-        <v>0.5938553852361779</v>
+        <v>0.5615679389736461</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2758,73 +2753,73 @@
         <v>20</v>
       </c>
       <c r="B18" s="3">
-        <v>0.1374880960086889</v>
+        <v>0.1890208418800522</v>
       </c>
       <c r="C18" s="3">
-        <v>0.1409369976233262</v>
+        <v>0.2159463161121849</v>
       </c>
       <c r="D18" s="3">
-        <v>0.1711823522457242</v>
+        <v>0.229903323339018</v>
       </c>
       <c r="E18" s="3">
-        <v>0.2054180849637705</v>
+        <v>0.2847472489508014</v>
       </c>
       <c r="F18" s="3">
-        <v>0.2238454246581693</v>
+        <v>0.293024705191459</v>
       </c>
       <c r="G18" s="3">
-        <v>0.2918336117187994</v>
+        <v>0.3026549214101468</v>
       </c>
       <c r="H18" s="3">
-        <v>0.3026549214101468</v>
+        <v>0.3827749690950537</v>
       </c>
       <c r="I18" s="3">
-        <v>0.3454800056175341</v>
+        <v>0.4075337694156682</v>
       </c>
       <c r="J18" s="3">
-        <v>0.3599350001971149</v>
+        <v>0.4215032476552573</v>
       </c>
       <c r="K18" s="3">
+        <v>0.4285368825916186</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.4313586081163324</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.4327711556570478</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.4370152718964042</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.4483764526890395</v>
+      </c>
+      <c r="P18" s="3">
         <v>0.4512256641402582</v>
       </c>
-      <c r="L18" s="3">
-        <v>0.4512256641402582</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0.4612219079428285</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0.4640840730548977</v>
-      </c>
-      <c r="O18" s="3">
-        <v>0.469815319996098</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0.469815319996098</v>
-      </c>
       <c r="Q18" s="3">
-        <v>0.4755545388793386</v>
+        <v>0.4942437915888551</v>
       </c>
       <c r="S18" s="3">
-        <v>0.5143871841659987</v>
+        <v>0.5186997779295586</v>
       </c>
       <c r="T18" s="3">
-        <v>0.515824985264735</v>
+        <v>0.5316182978281073</v>
       </c>
       <c r="U18" s="3">
-        <v>0.5258809308911691</v>
+        <v>0.5344839447268315</v>
       </c>
       <c r="V18" s="3">
-        <v>0.5459219227804837</v>
+        <v>0.5402082283237456</v>
       </c>
       <c r="W18" s="3">
-        <v>0.5473485180458647</v>
+        <v>0.5487743358597419</v>
       </c>
       <c r="X18" s="3">
         <v>0.550199353253537</v>
       </c>
       <c r="Y18" s="3">
-        <v>0.5700528235839882</v>
+        <v>0.5558909611168531</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2832,73 +2827,73 @@
         <v>21</v>
       </c>
       <c r="B19" s="3">
-        <v>0.1308031345449462</v>
+        <v>0.1778153888464977</v>
       </c>
       <c r="C19" s="3">
-        <v>0.1341104175449561</v>
+        <v>0.2035453002882742</v>
       </c>
       <c r="D19" s="3">
-        <v>0.1631690339971053</v>
+        <v>0.2169225565903239</v>
       </c>
       <c r="E19" s="3">
-        <v>0.1961814805753157</v>
+        <v>0.269754586702576</v>
       </c>
       <c r="F19" s="3">
-        <v>0.2140033977178425</v>
+        <v>0.2777654663508294</v>
       </c>
       <c r="G19" s="3">
-        <v>0.2800809940528481</v>
+        <v>0.287097842594546</v>
       </c>
       <c r="H19" s="3">
-        <v>0.2906453694012366</v>
+        <v>0.3652566649476832</v>
       </c>
       <c r="I19" s="3">
-        <v>0.332581578126777</v>
+        <v>0.389597577905311</v>
       </c>
       <c r="J19" s="3">
-        <v>0.3467828327811303</v>
+        <v>0.403370826694226</v>
       </c>
       <c r="K19" s="3">
-        <v>0.4370152718964042</v>
+        <v>0.41031649686005</v>
       </c>
       <c r="L19" s="3">
-        <v>0.4370152718964042</v>
+        <v>0.4131049766209</v>
       </c>
       <c r="M19" s="3">
-        <v>0.4469531048305375</v>
+        <v>0.4145013213281905</v>
       </c>
       <c r="N19" s="3">
-        <v>0.449800646746463</v>
+        <v>0.4186985216310851</v>
       </c>
       <c r="O19" s="3">
-        <v>0.4555054269169921</v>
+        <v>0.4299471764160118</v>
       </c>
       <c r="P19" s="3">
-        <v>0.4555054269169921</v>
+        <v>0.4327711556570478</v>
       </c>
       <c r="Q19" s="3">
-        <v>0.4612219079428285</v>
+        <v>0.4755545388793386</v>
       </c>
       <c r="R19" s="3">
-        <v>0.4856128158340013</v>
+        <v>0.4813002220704414</v>
       </c>
       <c r="T19" s="3">
-        <v>0.5014391117091528</v>
+        <v>0.5129491448928637</v>
       </c>
       <c r="U19" s="3">
-        <v>0.5115108912177917</v>
+        <v>0.515824985264735</v>
       </c>
       <c r="V19" s="3">
+        <v>0.5215733330511455</v>
+      </c>
+      <c r="W19" s="3">
+        <v>0.5301846800039021</v>
+      </c>
+      <c r="X19" s="3">
         <v>0.5316182978281073</v>
       </c>
-      <c r="W19" s="3">
-        <v>0.5330513938844411</v>
-      </c>
-      <c r="X19" s="3">
-        <v>0.5359159269451023</v>
-      </c>
       <c r="Y19" s="3">
-        <v>0.5558909611168531</v>
+        <v>0.5373473171664928</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2906,73 +2901,73 @@
         <v>22</v>
       </c>
       <c r="B20" s="3">
-        <v>0.1301500509256908</v>
+        <v>0.1703671765686566</v>
       </c>
       <c r="C20" s="3">
-        <v>0.1334433562104599</v>
+        <v>0.1952753065007406</v>
       </c>
       <c r="D20" s="3">
-        <v>0.1623845416286026</v>
+        <v>0.2082511624918156</v>
       </c>
       <c r="E20" s="3">
-        <v>0.1952753065007406</v>
+        <v>0.2596715804851696</v>
       </c>
       <c r="F20" s="3">
-        <v>0.2130367206105308</v>
+        <v>0.2674927102443324</v>
       </c>
       <c r="G20" s="3">
-        <v>0.2789217568024399</v>
+        <v>0.2766121305608295</v>
       </c>
       <c r="H20" s="3">
-        <v>0.2894599876301622</v>
+        <v>0.3533311576743853</v>
       </c>
       <c r="I20" s="3">
-        <v>0.3313050436926683</v>
+        <v>0.3773498042127379</v>
       </c>
       <c r="J20" s="3">
-        <v>0.3454800056175341</v>
+        <v>0.3909673965957605</v>
       </c>
       <c r="K20" s="3">
-        <v>0.4355995097595788</v>
+        <v>0.397841906825283</v>
       </c>
       <c r="L20" s="3">
-        <v>0.4355995097595788</v>
+        <v>0.4006032032907432</v>
       </c>
       <c r="M20" s="3">
-        <v>0.4455306259783239</v>
+        <v>0.4019862342306564</v>
       </c>
       <c r="N20" s="3">
-        <v>0.4483764526890395</v>
+        <v>0.4061446147638222</v>
       </c>
       <c r="O20" s="3">
-        <v>0.4540780772195163</v>
+        <v>0.4172981150357699</v>
       </c>
       <c r="P20" s="3">
-        <v>0.4540780772195163</v>
+        <v>0.4201002396421186</v>
       </c>
       <c r="Q20" s="3">
-        <v>0.4597917716762543</v>
+        <v>0.4626526828335072</v>
       </c>
       <c r="R20" s="3">
-        <v>0.4841750147352649</v>
+        <v>0.4683817021718927</v>
       </c>
       <c r="S20" s="3">
-        <v>0.4985608882908471</v>
+        <v>0.4870508551071362</v>
       </c>
       <c r="U20" s="3">
-        <v>0.5100724469274385</v>
+        <v>0.5028781995748109</v>
       </c>
       <c r="V20" s="3">
-        <v>0.5301846800039021</v>
+        <v>0.5086338358210827</v>
       </c>
       <c r="W20" s="3">
-        <v>0.5316182978281073</v>
+        <v>0.5172625244323762</v>
       </c>
       <c r="X20" s="3">
-        <v>0.5344839447268315</v>
+        <v>0.5186997779295586</v>
       </c>
       <c r="Y20" s="3">
-        <v>0.554469374021676</v>
+        <v>0.5244454611206615</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2980,73 +2975,73 @@
         <v>23</v>
       </c>
       <c r="B21" s="3">
-        <v>0.1256557731814538</v>
+        <v>0.1687460843479534</v>
       </c>
       <c r="C21" s="3">
-        <v>0.1288522015954445</v>
+        <v>0.1934724771828921</v>
       </c>
       <c r="D21" s="3">
-        <v>0.1569780355859638</v>
+        <v>0.2063592568118311</v>
       </c>
       <c r="E21" s="3">
-        <v>0.1890208418800522</v>
+        <v>0.2574644410569302</v>
       </c>
       <c r="F21" s="3">
-        <v>0.2063592568118311</v>
+        <v>0.2652429106834533</v>
       </c>
       <c r="G21" s="3">
-        <v>0.2708900371022475</v>
+        <v>0.2743143537282129</v>
       </c>
       <c r="H21" s="3">
-        <v>0.2812431701012181</v>
+        <v>0.3507050528890364</v>
       </c>
       <c r="I21" s="3">
-        <v>0.3224394199148994</v>
+        <v>0.3746486066924632</v>
       </c>
       <c r="J21" s="3">
-        <v>0.3364259019587045</v>
+        <v>0.3882294992189357</v>
       </c>
       <c r="K21" s="3">
-        <v>0.4257197963454756</v>
+        <v>0.3950870979920432</v>
       </c>
       <c r="L21" s="3">
-        <v>0.4257197963454756</v>
+        <v>0.397841906825283</v>
       </c>
       <c r="M21" s="3">
-        <v>0.4355995097595788</v>
+        <v>0.399221754109989</v>
       </c>
       <c r="N21" s="3">
-        <v>0.438432061026354</v>
+        <v>0.403370826694226</v>
       </c>
       <c r="O21" s="3">
-        <v>0.4441090388831469</v>
+        <v>0.4145013213281905</v>
       </c>
       <c r="P21" s="3">
-        <v>0.4441090388831469</v>
+        <v>0.4172981150357699</v>
       </c>
       <c r="Q21" s="3">
-        <v>0.449800646746463</v>
+        <v>0.4597917716762543</v>
       </c>
       <c r="R21" s="3">
-        <v>0.4741190691088309</v>
+        <v>0.4655160552731685</v>
       </c>
       <c r="S21" s="3">
-        <v>0.4884891087822083</v>
+        <v>0.4841750147352649</v>
       </c>
       <c r="T21" s="3">
-        <v>0.4899275530725615</v>
+        <v>0.4971218004251891</v>
       </c>
       <c r="V21" s="3">
-        <v>0.5201367220358165</v>
+        <v>0.5057562084111449</v>
       </c>
       <c r="W21" s="3">
+        <v>0.5143871841659987</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0.515824985264735</v>
+      </c>
+      <c r="Y21" s="3">
         <v>0.5215733330511455</v>
-      </c>
-      <c r="X21" s="3">
-        <v>0.5244454611206615</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>0.544494573083008</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -3054,73 +3049,73 @@
         <v>24</v>
       </c>
       <c r="B22" s="3">
-        <v>0.1170653958743179</v>
+        <v>0.1655408182910169</v>
       </c>
       <c r="C22" s="3">
-        <v>0.1200733119893831</v>
+        <v>0.1899048413952433</v>
       </c>
       <c r="D22" s="3">
-        <v>0.1466053778881182</v>
+        <v>0.2026136859722963</v>
       </c>
       <c r="E22" s="3">
-        <v>0.1769753710782679</v>
+        <v>0.2530870785710568</v>
       </c>
       <c r="F22" s="3">
-        <v>0.1934724771828921</v>
+        <v>0.2607797458593321</v>
       </c>
       <c r="G22" s="3">
-        <v>0.2552695931349653</v>
+        <v>0.269754586702576</v>
       </c>
       <c r="H22" s="3">
-        <v>0.2652429106834533</v>
+        <v>0.3454800056175341</v>
       </c>
       <c r="I22" s="3">
-        <v>0.3050902872704974</v>
+        <v>0.3692697113837977</v>
       </c>
       <c r="J22" s="3">
-        <v>0.3186781648336063</v>
+        <v>0.3827749690950537</v>
       </c>
       <c r="K22" s="3">
-        <v>0.4061446147638222</v>
+        <v>0.389597577905311</v>
       </c>
       <c r="L22" s="3">
-        <v>0.4061446147638222</v>
+        <v>0.3923389358731801</v>
       </c>
       <c r="M22" s="3">
-        <v>0.415899041186322</v>
+        <v>0.3937121762145718</v>
       </c>
       <c r="N22" s="3">
-        <v>0.4186985216310851</v>
+        <v>0.397841906825283</v>
       </c>
       <c r="O22" s="3">
-        <v>0.4243130476235704</v>
+        <v>0.4089244036850566</v>
       </c>
       <c r="P22" s="3">
-        <v>0.4243130476235704</v>
+        <v>0.4117100281368372</v>
       </c>
       <c r="Q22" s="3">
-        <v>0.4299471764160118</v>
+        <v>0.4540780772195163</v>
       </c>
       <c r="R22" s="3">
-        <v>0.4540780772195163</v>
+        <v>0.4597917716762543</v>
       </c>
       <c r="S22" s="3">
-        <v>0.4683817021718927</v>
+        <v>0.4784266669488546</v>
       </c>
       <c r="T22" s="3">
-        <v>0.469815319996098</v>
+        <v>0.4913661641789174</v>
       </c>
       <c r="U22" s="3">
-        <v>0.4798632779641835</v>
+        <v>0.4942437915888551</v>
       </c>
       <c r="W22" s="3">
-        <v>0.5014391117091528</v>
+        <v>0.5086338358210827</v>
       </c>
       <c r="X22" s="3">
-        <v>0.5043172397550598</v>
+        <v>0.5100724469274385</v>
       </c>
       <c r="Y22" s="3">
-        <v>0.5244454611206615</v>
+        <v>0.515824985264735</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -3128,73 +3123,73 @@
         <v>25</v>
       </c>
       <c r="B23" s="3">
-        <v>0.1164717119435607</v>
+        <v>0.1608246821473244</v>
       </c>
       <c r="C23" s="3">
-        <v>0.1194664377525988</v>
+        <v>0.1846481847166994</v>
       </c>
       <c r="D23" s="3">
-        <v>0.1458866380543756</v>
+        <v>0.1970908298461841</v>
       </c>
       <c r="E23" s="3">
-        <v>0.1761384714944276</v>
+        <v>0.2466139222143855</v>
       </c>
       <c r="F23" s="3">
-        <v>0.1925758183287208</v>
+        <v>0.2541767916495005</v>
       </c>
       <c r="G23" s="3">
-        <v>0.2541767916495005</v>
+        <v>0.2630052394593107</v>
       </c>
       <c r="H23" s="3">
-        <v>0.2641225558985236</v>
+        <v>0.3377122025691112</v>
       </c>
       <c r="I23" s="3">
-        <v>0.3038712295704002</v>
+        <v>0.3612622508882752</v>
       </c>
       <c r="J23" s="3">
-        <v>0.3174296145252281</v>
+        <v>0.3746486066924632</v>
       </c>
       <c r="K23" s="3">
-        <v>0.4047569603484281</v>
+        <v>0.3814158779109693</v>
       </c>
       <c r="L23" s="3">
-        <v>0.4047569603484281</v>
+        <v>0.384135895746244</v>
       </c>
       <c r="M23" s="3">
-        <v>0.4145013213281905</v>
+        <v>0.3854986389914422</v>
       </c>
       <c r="N23" s="3">
-        <v>0.4172981150357699</v>
+        <v>0.389597577905311</v>
       </c>
       <c r="O23" s="3">
-        <v>0.422907524174671</v>
+        <v>0.4006032032907432</v>
       </c>
       <c r="P23" s="3">
-        <v>0.422907524174671</v>
+        <v>0.403370826694226</v>
       </c>
       <c r="Q23" s="3">
-        <v>0.4285368825916186</v>
+        <v>0.4455306259783239</v>
       </c>
       <c r="R23" s="3">
-        <v>0.4526514819541353</v>
+        <v>0.4512256641402582</v>
       </c>
       <c r="S23" s="3">
-        <v>0.4669486061155589</v>
+        <v>0.469815319996098</v>
       </c>
       <c r="T23" s="3">
-        <v>0.4683817021718927</v>
+        <v>0.4827374755676238</v>
       </c>
       <c r="U23" s="3">
-        <v>0.4784266669488546</v>
+        <v>0.4856128158340013</v>
       </c>
       <c r="V23" s="3">
-        <v>0.4985608882908471</v>
+        <v>0.4913661641789174</v>
       </c>
       <c r="X23" s="3">
-        <v>0.5028781995748109</v>
+        <v>0.5014391117091528</v>
       </c>
       <c r="Y23" s="3">
-        <v>0.5230095872975623</v>
+        <v>0.5071950817090514</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -3202,73 +3197,73 @@
         <v>26</v>
       </c>
       <c r="B24" s="3">
-        <v>0.1152921835088358</v>
+        <v>0.1600493053652466</v>
       </c>
       <c r="C24" s="3">
-        <v>0.1182606406580926</v>
+        <v>0.1837831034243972</v>
       </c>
       <c r="D24" s="3">
-        <v>0.1444579251073025</v>
+        <v>0.1961814805753157</v>
       </c>
       <c r="E24" s="3">
-        <v>0.1744740126388183</v>
+        <v>0.2455459580578135</v>
       </c>
       <c r="F24" s="3">
-        <v>0.1907920025141619</v>
+        <v>0.2530870785710568</v>
       </c>
       <c r="G24" s="3">
-        <v>0.2520004588039456</v>
+        <v>0.2618909674595814</v>
       </c>
       <c r="H24" s="3">
-        <v>0.2618909674595814</v>
+        <v>0.3364259019587045</v>
       </c>
       <c r="I24" s="3">
-        <v>0.301441373581977</v>
+        <v>0.3599350001971149</v>
       </c>
       <c r="J24" s="3">
-        <v>0.3149403910066497</v>
+        <v>0.373300918333268</v>
       </c>
       <c r="K24" s="3">
+        <v>0.3800586409554767</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0.3827749690950537</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0.384135895746244</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0.3882294992189357</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0.399221754109989</v>
+      </c>
+      <c r="P24" s="3">
         <v>0.4019862342306564</v>
       </c>
-      <c r="L24" s="3">
-        <v>0.4019862342306564</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0.4117100281368372</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0.4145013213281905</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0.4201002396421186</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0.4201002396421186</v>
-      </c>
       <c r="Q24" s="3">
-        <v>0.4257197963454756</v>
+        <v>0.4441090388831469</v>
       </c>
       <c r="R24" s="3">
         <v>0.449800646746463</v>
       </c>
       <c r="S24" s="3">
-        <v>0.4640840730548977</v>
+        <v>0.4683817021718927</v>
       </c>
       <c r="T24" s="3">
-        <v>0.4655160552731685</v>
+        <v>0.4813002220704414</v>
       </c>
       <c r="U24" s="3">
-        <v>0.4755545388793386</v>
+        <v>0.4841750147352649</v>
       </c>
       <c r="V24" s="3">
-        <v>0.4956827602449402</v>
+        <v>0.4899275530725615</v>
       </c>
       <c r="W24" s="3">
-        <v>0.4971218004251891</v>
+        <v>0.4985608882908471</v>
       </c>
       <c r="Y24" s="3">
-        <v>0.5201367220358165</v>
+        <v>0.5057562084111449</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -3276,73 +3271,73 @@
         <v>27</v>
       </c>
       <c r="B25" s="3">
-        <v>0.1073233399938459</v>
+        <v>0.1569780355859638</v>
       </c>
       <c r="C25" s="3">
-        <v>0.1101121578188672</v>
+        <v>0.1803541855053107</v>
       </c>
       <c r="D25" s="3">
-        <v>0.1347802947714417</v>
+        <v>0.1925758183287208</v>
       </c>
       <c r="E25" s="3">
-        <v>0.1631690339971053</v>
+        <v>0.2413053798531443</v>
       </c>
       <c r="F25" s="3">
-        <v>0.178658528262988</v>
+        <v>0.2487592064662893</v>
       </c>
       <c r="G25" s="3">
-        <v>0.2371150196947458</v>
+        <v>0.2574644410569302</v>
       </c>
       <c r="H25" s="3">
-        <v>0.2466139222143855</v>
+        <v>0.3313050436926683</v>
       </c>
       <c r="I25" s="3">
-        <v>0.2847472489508014</v>
+        <v>0.3546475495606176</v>
       </c>
       <c r="J25" s="3">
-        <v>0.2978173979094794</v>
+        <v>0.3679299878999264</v>
       </c>
       <c r="K25" s="3">
+        <v>0.3746486066924632</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0.3773498042127379</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0.3787032768775454</v>
+      </c>
+      <c r="N25" s="3">
         <v>0.3827749690950537</v>
       </c>
-      <c r="L25" s="3">
-        <v>0.3827749690950537</v>
-      </c>
-      <c r="M25" s="3">
-        <v>0.3923389358731801</v>
-      </c>
-      <c r="N25" s="3">
-        <v>0.3950870979920432</v>
-      </c>
       <c r="O25" s="3">
-        <v>0.4006032032907432</v>
+        <v>0.3937121762145718</v>
       </c>
       <c r="P25" s="3">
-        <v>0.4006032032907432</v>
+        <v>0.3964636814738219</v>
       </c>
       <c r="Q25" s="3">
-        <v>0.4061446147638222</v>
+        <v>0.438432061026354</v>
       </c>
       <c r="R25" s="3">
-        <v>0.4299471764160118</v>
+        <v>0.4441090388831469</v>
       </c>
       <c r="S25" s="3">
-        <v>0.4441090388831469</v>
+        <v>0.4626526828335072</v>
       </c>
       <c r="T25" s="3">
-        <v>0.4455306259783239</v>
+        <v>0.4755545388793386</v>
       </c>
       <c r="U25" s="3">
-        <v>0.4555054269169921</v>
+        <v>0.4784266669488546</v>
       </c>
       <c r="V25" s="3">
-        <v>0.4755545388793386</v>
+        <v>0.4841750147352649</v>
       </c>
       <c r="W25" s="3">
-        <v>0.4769904127024377</v>
+        <v>0.4928049182909486</v>
       </c>
       <c r="X25" s="3">
-        <v>0.4798632779641835</v>
+        <v>0.4942437915888551</v>
       </c>
     </row>
   </sheetData>
@@ -3394,19 +3389,19 @@
         <v>4</v>
       </c>
       <c r="C2" s="1">
-        <v>2200</v>
+        <v>2121</v>
       </c>
       <c r="D2">
         <v>23</v>
       </c>
       <c r="E2" s="1">
-        <v>18.26197274582883</v>
+        <v>17.33328013943989</v>
       </c>
       <c r="F2" s="1">
-        <v>36.52394549165766</v>
+        <v>34.66656027887977</v>
       </c>
       <c r="G2" s="1">
-        <v>1.587997630072072</v>
+        <v>1.507241751255642</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3417,19 +3412,19 @@
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>2195</v>
+        <v>2092</v>
       </c>
       <c r="D3">
         <v>23</v>
       </c>
       <c r="E3" s="1">
-        <v>18.15359246151616</v>
+        <v>16.58142485902778</v>
       </c>
       <c r="F3" s="1">
-        <v>36.30718492303232</v>
+        <v>33.16284971805556</v>
       </c>
       <c r="G3" s="1">
-        <v>1.578573257523145</v>
+        <v>1.441863031219807</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3440,19 +3435,19 @@
         <v>6</v>
       </c>
       <c r="C4" s="1">
-        <v>2155</v>
+        <v>2078</v>
       </c>
       <c r="D4">
         <v>23</v>
       </c>
       <c r="E4" s="1">
-        <v>17.23324497683946</v>
+        <v>16.20021003043394</v>
       </c>
       <c r="F4" s="1">
-        <v>34.46648995367892</v>
+        <v>32.40042006086788</v>
       </c>
       <c r="G4" s="1">
-        <v>1.498543041464301</v>
+        <v>1.408713915689908</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3463,19 +3458,19 @@
         <v>7</v>
       </c>
       <c r="C5" s="1">
-        <v>2116</v>
+        <v>2028</v>
       </c>
       <c r="D5">
         <v>23</v>
       </c>
       <c r="E5" s="1">
-        <v>16.24810368980516</v>
+        <v>14.7520079594869</v>
       </c>
       <c r="F5" s="1">
-        <v>32.49620737961033</v>
+        <v>29.50401591897379</v>
       </c>
       <c r="G5" s="1">
-        <v>1.412878581722188</v>
+        <v>1.282783300824947</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3486,19 +3481,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="1">
-        <v>2097</v>
+        <v>2021</v>
       </c>
       <c r="D6">
         <v>23</v>
       </c>
       <c r="E6" s="1">
-        <v>15.7389550027861</v>
+        <v>14.53969816463275</v>
       </c>
       <c r="F6" s="1">
-        <v>31.47791000557219</v>
+        <v>29.0793963292655</v>
       </c>
       <c r="G6" s="1">
-        <v>1.368604782850965</v>
+        <v>1.264321579533283</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3509,19 +3504,19 @@
         <v>9</v>
       </c>
       <c r="C7" s="1">
-        <v>2035</v>
+        <v>2013</v>
       </c>
       <c r="D7">
         <v>23</v>
       </c>
       <c r="E7" s="1">
-        <v>13.96361819448427</v>
+        <v>14.2945843224385</v>
       </c>
       <c r="F7" s="1">
-        <v>27.92723638896855</v>
+        <v>28.58916864487699</v>
       </c>
       <c r="G7" s="1">
-        <v>1.214227669085589</v>
+        <v>1.243007332385956</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3532,19 +3527,19 @@
         <v>10</v>
       </c>
       <c r="C8" s="1">
-        <v>2026</v>
+        <v>1951</v>
       </c>
       <c r="D8">
         <v>23</v>
       </c>
       <c r="E8" s="1">
-        <v>13.69378680716932</v>
+        <v>12.32615967133275</v>
       </c>
       <c r="F8" s="1">
-        <v>27.38757361433865</v>
+        <v>24.6523193426655</v>
       </c>
       <c r="G8" s="1">
-        <v>1.190764070188637</v>
+        <v>1.071839971420239</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3555,19 +3550,19 @@
         <v>11</v>
       </c>
       <c r="C9" s="1">
-        <v>1992</v>
+        <v>1933</v>
       </c>
       <c r="D9">
         <v>23</v>
       </c>
       <c r="E9" s="1">
-        <v>12.65433751464623</v>
+        <v>11.74049050581647</v>
       </c>
       <c r="F9" s="1">
-        <v>25.30867502929246</v>
+        <v>23.48098101163294</v>
       </c>
       <c r="G9" s="1">
-        <v>1.100377175186628</v>
+        <v>1.020912217897084</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3578,19 +3573,19 @@
         <v>12</v>
       </c>
       <c r="C10" s="1">
-        <v>1981</v>
+        <v>1923</v>
       </c>
       <c r="D10">
         <v>23</v>
       </c>
       <c r="E10" s="1">
-        <v>12.31276852849071</v>
+        <v>11.41419969237965</v>
       </c>
       <c r="F10" s="1">
-        <v>24.62553705698141</v>
+        <v>22.82839938475929</v>
       </c>
       <c r="G10" s="1">
-        <v>1.070675524216583</v>
+        <v>0.9925391036851867</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3601,19 +3596,19 @@
         <v>13</v>
       </c>
       <c r="C11" s="1">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="D11">
         <v>23</v>
       </c>
       <c r="E11" s="1">
-        <v>10.24445375146869</v>
+        <v>11.25099645670812</v>
       </c>
       <c r="F11" s="1">
-        <v>20.48890750293739</v>
+        <v>22.50199291341623</v>
       </c>
       <c r="G11" s="1">
-        <v>0.8908220653451038</v>
+        <v>0.9783475179746187</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3624,19 +3619,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="1">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="D12">
         <v>23</v>
       </c>
       <c r="E12" s="1">
-        <v>10.24445375146869</v>
+        <v>11.18572259695124</v>
       </c>
       <c r="F12" s="1">
-        <v>20.48890750293739</v>
+        <v>22.37144519390249</v>
       </c>
       <c r="G12" s="1">
-        <v>0.8908220653451038</v>
+        <v>0.9726715301696734</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3647,19 +3642,19 @@
         <v>15</v>
       </c>
       <c r="C13" s="1">
-        <v>1908</v>
+        <v>1915</v>
       </c>
       <c r="D13">
         <v>23</v>
       </c>
       <c r="E13" s="1">
-        <v>10.0260224261215</v>
+        <v>11.15308910141949</v>
       </c>
       <c r="F13" s="1">
-        <v>20.05204485224299</v>
+        <v>22.30617820283898</v>
       </c>
       <c r="G13" s="1">
-        <v>0.8718280370540432</v>
+        <v>0.9698338349060427</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3670,19 +3665,19 @@
         <v>16</v>
       </c>
       <c r="C14" s="1">
-        <v>1906</v>
+        <v>1912</v>
       </c>
       <c r="D14">
         <v>23</v>
       </c>
       <c r="E14" s="1">
-        <v>9.963737066547042</v>
+        <v>11.05520787804356</v>
       </c>
       <c r="F14" s="1">
-        <v>19.92747413309408</v>
+        <v>22.11041575608713</v>
       </c>
       <c r="G14" s="1">
-        <v>0.8664119188301775</v>
+        <v>0.9613224241777011</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3693,19 +3688,19 @@
         <v>17</v>
       </c>
       <c r="C15" s="1">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="D15">
         <v>23</v>
       </c>
       <c r="E15" s="1">
-        <v>9.839352032150439</v>
+        <v>10.79441357386655</v>
       </c>
       <c r="F15" s="1">
-        <v>19.67870406430088</v>
+        <v>21.58882714773311</v>
       </c>
       <c r="G15" s="1">
-        <v>0.8555958288826468</v>
+        <v>0.9386446585970916</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3722,13 +3717,13 @@
         <v>23</v>
       </c>
       <c r="E16" s="1">
-        <v>9.839352032150439</v>
+        <v>10.72928545240046</v>
       </c>
       <c r="F16" s="1">
-        <v>19.67870406430088</v>
+        <v>21.45857090480093</v>
       </c>
       <c r="G16" s="1">
-        <v>0.8555958288826468</v>
+        <v>0.9329813436869968</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3739,19 +3734,19 @@
         <v>19</v>
       </c>
       <c r="C17" s="1">
-        <v>1898</v>
+        <v>1872</v>
       </c>
       <c r="D17">
         <v>23</v>
       </c>
       <c r="E17" s="1">
-        <v>9.715235922990503</v>
+        <v>9.758667254177768</v>
       </c>
       <c r="F17" s="1">
-        <v>19.43047184598101</v>
+        <v>19.51733450835554</v>
       </c>
       <c r="G17" s="1">
-        <v>0.8448031237383047</v>
+        <v>0.8485797612328494</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3762,19 +3757,19 @@
         <v>20</v>
       </c>
       <c r="C18" s="1">
-        <v>1881</v>
+        <v>1868</v>
       </c>
       <c r="D18">
         <v>23</v>
       </c>
       <c r="E18" s="1">
-        <v>9.19133270057883</v>
+        <v>9.630512068767572</v>
       </c>
       <c r="F18" s="1">
-        <v>18.38266540115766</v>
+        <v>19.26102413753514</v>
       </c>
       <c r="G18" s="1">
-        <v>0.7992463217894634</v>
+        <v>0.8374358320667454</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3785,19 +3780,19 @@
         <v>21</v>
       </c>
       <c r="C19" s="1">
-        <v>1871</v>
+        <v>1855</v>
       </c>
       <c r="D19">
         <v>23</v>
       </c>
       <c r="E19" s="1">
-        <v>8.886414694424229</v>
+        <v>9.216818378590578</v>
       </c>
       <c r="F19" s="1">
-        <v>17.77282938884846</v>
+        <v>18.43363675718116</v>
       </c>
       <c r="G19" s="1">
-        <v>0.7727317125586286</v>
+        <v>0.8014624677035285</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3808,19 +3803,19 @@
         <v>22</v>
       </c>
       <c r="C20" s="1">
-        <v>1870</v>
+        <v>1846</v>
       </c>
       <c r="D20">
         <v>23</v>
       </c>
       <c r="E20" s="1">
-        <v>8.856075440454706</v>
+        <v>8.933297778113847</v>
       </c>
       <c r="F20" s="1">
-        <v>17.71215088090941</v>
+        <v>17.86659555622769</v>
       </c>
       <c r="G20" s="1">
-        <v>0.7700935165612788</v>
+        <v>0.7768085024446824</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3831,19 +3826,19 @@
         <v>23</v>
       </c>
       <c r="C21" s="1">
-        <v>1863</v>
+        <v>1844</v>
       </c>
       <c r="D21">
         <v>23</v>
       </c>
       <c r="E21" s="1">
-        <v>8.644540346375688</v>
+        <v>8.870650057600111</v>
       </c>
       <c r="F21" s="1">
-        <v>17.28908069275138</v>
+        <v>17.74130011520022</v>
       </c>
       <c r="G21" s="1">
-        <v>0.7516991605544077</v>
+        <v>0.7713608745739227</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3854,19 +3849,19 @@
         <v>24</v>
       </c>
       <c r="C22" s="1">
-        <v>1849</v>
+        <v>1840</v>
       </c>
       <c r="D22">
         <v>23</v>
       </c>
       <c r="E22" s="1">
-        <v>8.226273143880269</v>
+        <v>8.745768211153798</v>
       </c>
       <c r="F22" s="1">
-        <v>16.45254628776054</v>
+        <v>17.4915364223076</v>
       </c>
       <c r="G22" s="1">
-        <v>0.7153280994678495</v>
+        <v>0.7605015835785912</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3877,19 +3872,19 @@
         <v>25</v>
       </c>
       <c r="C23" s="1">
-        <v>1848</v>
+        <v>1834</v>
       </c>
       <c r="D23">
         <v>23</v>
       </c>
       <c r="E23" s="1">
-        <v>8.196661689572776</v>
+        <v>8.559526989835616</v>
       </c>
       <c r="F23" s="1">
-        <v>16.39332337914555</v>
+        <v>17.11905397967123</v>
       </c>
       <c r="G23" s="1">
-        <v>0.7127531903976327</v>
+        <v>0.7443066947683145</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3900,19 +3895,19 @@
         <v>26</v>
       </c>
       <c r="C24" s="1">
-        <v>1846</v>
+        <v>1833</v>
       </c>
       <c r="D24">
         <v>23</v>
       </c>
       <c r="E24" s="1">
-        <v>8.137550645495232</v>
+        <v>8.528617981680616</v>
       </c>
       <c r="F24" s="1">
-        <v>16.27510129099046</v>
+        <v>17.05723596336123</v>
       </c>
       <c r="G24" s="1">
-        <v>0.707613099608281</v>
+        <v>0.7416189549287493</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3923,19 +3918,19 @@
         <v>27</v>
       </c>
       <c r="C25" s="1">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="D25">
         <v>23</v>
       </c>
       <c r="E25" s="1">
-        <v>7.728164434754732</v>
+        <v>8.405370875702035</v>
       </c>
       <c r="F25" s="1">
-        <v>15.45632886950946</v>
+        <v>16.81074175140407</v>
       </c>
       <c r="G25" s="1">
-        <v>0.6720142986743245</v>
+        <v>0.7309018152784378</v>
       </c>
     </row>
   </sheetData>
@@ -3954,9 +3949,7 @@
     <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
     <col min="5" max="28" width="7.7109375" style="3" customWidth="1"/>
     <col min="29" max="29" width="8.7109375" style="3" customWidth="1"/>
-    <col min="30" max="30" width="21.7109375" style="3" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="3" customWidth="1"/>
-    <col min="32" max="34" width="22.7109375" style="3" customWidth="1"/>
+    <col min="30" max="34" width="22.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -4068,58 +4061,58 @@
         <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>2200</v>
+        <v>2121</v>
       </c>
       <c r="C2" s="1">
-        <v>36.562</v>
+        <v>34.772</v>
       </c>
       <c r="D2" s="1">
-        <v>18.281</v>
+        <v>17.386</v>
       </c>
       <c r="E2" s="3">
-        <v>0.444</v>
+        <v>0.474</v>
       </c>
       <c r="F2" s="3">
-        <v>0.24</v>
+        <v>0.238</v>
       </c>
       <c r="G2" s="3">
-        <v>0.168</v>
+        <v>0.12</v>
       </c>
       <c r="H2" s="3">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="I2" s="3">
-        <v>0.038</v>
+        <v>0.045</v>
       </c>
       <c r="J2" s="3">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="K2" s="3">
         <v>0.007</v>
       </c>
       <c r="L2" s="3">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0.006</v>
+      </c>
+      <c r="N2" s="3">
         <v>0.002</v>
       </c>
-      <c r="M2" s="3">
-        <v>0</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0</v>
-      </c>
       <c r="O2" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="P2" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="Q2" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="R2" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="S2" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="T2" s="3">
         <v>0</v>
@@ -4149,22 +4142,22 @@
         <v>0</v>
       </c>
       <c r="AC2" s="3">
-        <v>0.444</v>
+        <v>0.474</v>
       </c>
       <c r="AD2" s="3">
-        <v>0.6839999999999999</v>
+        <v>0.712</v>
       </c>
       <c r="AE2" s="3">
-        <v>0.852</v>
+        <v>0.832</v>
       </c>
       <c r="AF2" s="3">
-        <v>0.9289999999999999</v>
+        <v>0.9049999999999999</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.967</v>
+        <v>0.95</v>
       </c>
       <c r="AH2" s="3">
-        <v>1</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="3" spans="1:34">
@@ -4172,61 +4165,61 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>2195</v>
+        <v>2092</v>
       </c>
       <c r="C3" s="1">
-        <v>36.41</v>
+        <v>33.18</v>
       </c>
       <c r="D3" s="1">
-        <v>18.205</v>
+        <v>16.59</v>
       </c>
       <c r="E3" s="3">
-        <v>0.318</v>
+        <v>0.236</v>
       </c>
       <c r="F3" s="3">
-        <v>0.322</v>
+        <v>0.282</v>
       </c>
       <c r="G3" s="3">
-        <v>0.181</v>
+        <v>0.176</v>
       </c>
       <c r="H3" s="3">
-        <v>0.093</v>
+        <v>0.115</v>
       </c>
       <c r="I3" s="3">
-        <v>0.051</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J3" s="3">
-        <v>0.023</v>
+        <v>0.043</v>
       </c>
       <c r="K3" s="3">
+        <v>0.034</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.022</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.008</v>
+      </c>
+      <c r="N3" s="3">
         <v>0.006</v>
       </c>
-      <c r="L3" s="3">
-        <v>0.005</v>
-      </c>
-      <c r="M3" s="3">
+      <c r="O3" s="3">
         <v>0.001</v>
       </c>
-      <c r="N3" s="3">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0</v>
-      </c>
       <c r="P3" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="Q3" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="R3" s="3">
         <v>0</v>
       </c>
       <c r="S3" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="T3" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="U3" s="3">
         <v>0</v>
@@ -4253,22 +4246,22 @@
         <v>0</v>
       </c>
       <c r="AC3" s="3">
-        <v>0.318</v>
+        <v>0.236</v>
       </c>
       <c r="AD3" s="3">
-        <v>0.64</v>
+        <v>0.518</v>
       </c>
       <c r="AE3" s="3">
-        <v>0.821</v>
+        <v>0.694</v>
       </c>
       <c r="AF3" s="3">
-        <v>0.9139999999999999</v>
+        <v>0.8089999999999999</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.965</v>
+        <v>0.879</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.999</v>
+        <v>0.9780000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -4276,71 +4269,71 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>2155</v>
+        <v>2078</v>
       </c>
       <c r="C4" s="1">
-        <v>34.334</v>
+        <v>32.182</v>
       </c>
       <c r="D4" s="1">
-        <v>17.167</v>
+        <v>16.091</v>
       </c>
       <c r="E4" s="3">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="F4" s="3">
-        <v>0.204</v>
+        <v>0.198</v>
       </c>
       <c r="G4" s="3">
-        <v>0.234</v>
+        <v>0.227</v>
       </c>
       <c r="H4" s="3">
-        <v>0.198</v>
+        <v>0.151</v>
       </c>
       <c r="I4" s="3">
-        <v>0.103</v>
+        <v>0.109</v>
       </c>
       <c r="J4" s="3">
-        <v>0.057</v>
+        <v>0.047</v>
       </c>
       <c r="K4" s="3">
-        <v>0.025</v>
+        <v>0.038</v>
       </c>
       <c r="L4" s="3">
-        <v>0.013</v>
+        <v>0.024</v>
       </c>
       <c r="M4" s="3">
+        <v>0.021</v>
+      </c>
+      <c r="N4" s="3">
         <v>0.008999999999999999</v>
       </c>
-      <c r="N4" s="3">
-        <v>0.003</v>
-      </c>
       <c r="O4" s="3">
-        <v>0.003</v>
+        <v>0.007</v>
       </c>
       <c r="P4" s="3">
+        <v>0.004</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.005</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0.007</v>
+      </c>
+      <c r="S4" s="3">
         <v>0.001</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="T4" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="U4" s="3">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0</v>
+      </c>
+      <c r="W4" s="3">
         <v>0.001</v>
       </c>
-      <c r="R4" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="S4" s="3">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3">
-        <v>0</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="V4" s="3">
-        <v>0</v>
-      </c>
-      <c r="W4" s="3">
-        <v>0</v>
-      </c>
       <c r="X4" s="3">
         <v>0</v>
       </c>
@@ -4357,22 +4350,22 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="AD4" s="3">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="AE4" s="3">
-        <v>0.585</v>
+        <v>0.574</v>
       </c>
       <c r="AF4" s="3">
-        <v>0.7829999999999999</v>
+        <v>0.725</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.8859999999999999</v>
+        <v>0.834</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.981</v>
+        <v>0.9430000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:34">
@@ -4380,103 +4373,103 @@
         <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>2116</v>
+        <v>2028</v>
       </c>
       <c r="C5" s="1">
-        <v>32.458</v>
+        <v>29.56</v>
       </c>
       <c r="D5" s="1">
-        <v>16.229</v>
+        <v>14.78</v>
       </c>
       <c r="E5" s="3">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="F5" s="3">
-        <v>0.121</v>
+        <v>0.106</v>
       </c>
       <c r="G5" s="3">
-        <v>0.183</v>
+        <v>0.127</v>
       </c>
       <c r="H5" s="3">
-        <v>0.239</v>
+        <v>0.179</v>
       </c>
       <c r="I5" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.076</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.043</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.042</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0.029</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.036</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0.018</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0.011</v>
+      </c>
+      <c r="S5" s="3">
+        <v>0.007</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="U5" s="3">
+        <v>0.003</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>0.052</v>
+      </c>
+      <c r="AD5" s="3">
         <v>0.158</v>
       </c>
-      <c r="J5" s="3">
-        <v>0.111</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0.067</v>
-      </c>
-      <c r="L5" s="3">
-        <v>0.024</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0.019</v>
-      </c>
-      <c r="N5" s="3">
-        <v>0.015</v>
-      </c>
-      <c r="O5" s="3">
-        <v>0.006</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0.006</v>
-      </c>
-      <c r="Q5" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="R5" s="3">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3">
-        <v>0</v>
-      </c>
-      <c r="T5" s="3">
-        <v>0</v>
-      </c>
-      <c r="U5" s="3">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3">
-        <v>0</v>
-      </c>
-      <c r="W5" s="3">
-        <v>0</v>
-      </c>
-      <c r="X5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="AD5" s="3">
-        <v>0.171</v>
-      </c>
       <c r="AE5" s="3">
-        <v>0.354</v>
+        <v>0.285</v>
       </c>
       <c r="AF5" s="3">
-        <v>0.593</v>
+        <v>0.464</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.751</v>
+        <v>0.5940000000000001</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.9530000000000001</v>
+        <v>0.8380000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -4484,80 +4477,80 @@
         <v>8</v>
       </c>
       <c r="B6" s="1">
-        <v>2097</v>
+        <v>2021</v>
       </c>
       <c r="C6" s="1">
-        <v>31.398</v>
+        <v>29.09</v>
       </c>
       <c r="D6" s="1">
-        <v>15.699</v>
+        <v>14.545</v>
       </c>
       <c r="E6" s="3">
-        <v>0.028</v>
+        <v>0.04</v>
       </c>
       <c r="F6" s="3">
-        <v>0.076</v>
+        <v>0.073</v>
       </c>
       <c r="G6" s="3">
-        <v>0.137</v>
+        <v>0.127</v>
       </c>
       <c r="H6" s="3">
-        <v>0.194</v>
+        <v>0.148</v>
       </c>
       <c r="I6" s="3">
-        <v>0.229</v>
+        <v>0.151</v>
       </c>
       <c r="J6" s="3">
-        <v>0.124</v>
+        <v>0.12</v>
       </c>
       <c r="K6" s="3">
-        <v>0.107</v>
+        <v>0.109</v>
       </c>
       <c r="L6" s="3">
-        <v>0.052</v>
+        <v>0.073</v>
       </c>
       <c r="M6" s="3">
-        <v>0.023</v>
+        <v>0.049</v>
       </c>
       <c r="N6" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="O6" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="P6" s="3">
+        <v>0.019</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>0.011</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0.011</v>
+      </c>
+      <c r="S6" s="3">
         <v>0.008</v>
       </c>
-      <c r="P6" s="3">
+      <c r="T6" s="3">
         <v>0.006</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="U6" s="3">
+        <v>0.006</v>
+      </c>
+      <c r="V6" s="3">
+        <v>0.004</v>
+      </c>
+      <c r="W6" s="3">
         <v>0.002</v>
       </c>
-      <c r="R6" s="3">
+      <c r="X6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3">
         <v>0.001</v>
       </c>
-      <c r="S6" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="T6" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="U6" s="3">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3">
-        <v>0</v>
-      </c>
-      <c r="W6" s="3">
-        <v>0</v>
-      </c>
-      <c r="X6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>0</v>
-      </c>
       <c r="AA6" s="3">
         <v>0</v>
       </c>
@@ -4565,22 +4558,22 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3">
-        <v>0.028</v>
+        <v>0.04</v>
       </c>
       <c r="AD6" s="3">
-        <v>0.104</v>
+        <v>0.113</v>
       </c>
       <c r="AE6" s="3">
-        <v>0.241</v>
+        <v>0.24</v>
       </c>
       <c r="AF6" s="3">
-        <v>0.435</v>
+        <v>0.388</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.664</v>
+        <v>0.539</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.9470000000000001</v>
+        <v>0.841</v>
       </c>
     </row>
     <row r="7" spans="1:34">
@@ -4588,73 +4581,73 @@
         <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>2035</v>
+        <v>2013</v>
       </c>
       <c r="C7" s="1">
-        <v>27.91</v>
+        <v>28.506</v>
       </c>
       <c r="D7" s="1">
-        <v>13.955</v>
+        <v>14.253</v>
       </c>
       <c r="E7" s="3">
-        <v>0.007</v>
+        <v>0.033</v>
       </c>
       <c r="F7" s="3">
+        <v>0.058</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.099</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="I7" s="3">
+        <v>0.144</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.134</v>
+      </c>
+      <c r="K7" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="L7" s="3">
+        <v>0.082</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0.061</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0.034</v>
+      </c>
+      <c r="O7" s="3">
+        <v>0.032</v>
+      </c>
+      <c r="P7" s="3">
+        <v>0.023</v>
+      </c>
+      <c r="Q7" s="3">
         <v>0.019</v>
       </c>
-      <c r="G7" s="3">
-        <v>0.037</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.137</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.187</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0.161</v>
-      </c>
-      <c r="L7" s="3">
-        <v>0.102</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="N7" s="3">
-        <v>0.064</v>
-      </c>
-      <c r="O7" s="3">
-        <v>0.037</v>
-      </c>
-      <c r="P7" s="3">
-        <v>0.018</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>0.023</v>
-      </c>
       <c r="R7" s="3">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="S7" s="3">
-        <v>0.005</v>
+        <v>0.014</v>
       </c>
       <c r="T7" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="U7" s="3">
         <v>0.006</v>
       </c>
       <c r="V7" s="3">
+        <v>0.006</v>
+      </c>
+      <c r="W7" s="3">
         <v>0.002</v>
       </c>
-      <c r="W7" s="3">
-        <v>0.003</v>
-      </c>
       <c r="X7" s="3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="Y7" s="3">
         <v>0.001</v>
@@ -4669,22 +4662,22 @@
         <v>0</v>
       </c>
       <c r="AC7" s="3">
-        <v>0.007</v>
+        <v>0.033</v>
       </c>
       <c r="AD7" s="3">
-        <v>0.026</v>
+        <v>0.091</v>
       </c>
       <c r="AE7" s="3">
-        <v>0.063</v>
+        <v>0.19</v>
       </c>
       <c r="AF7" s="3">
-        <v>0.148</v>
+        <v>0.32</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.285</v>
+        <v>0.464</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.735</v>
+        <v>0.7819999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -4692,415 +4685,415 @@
         <v>10</v>
       </c>
       <c r="B8" s="1">
-        <v>2026</v>
+        <v>1951</v>
       </c>
       <c r="C8" s="1">
-        <v>27.432</v>
+        <v>24.688</v>
       </c>
       <c r="D8" s="1">
-        <v>13.716</v>
+        <v>12.344</v>
       </c>
       <c r="E8" s="3">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="F8" s="3">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="G8" s="3">
         <v>0.033</v>
       </c>
       <c r="H8" s="3">
-        <v>0.053</v>
+        <v>0.043</v>
       </c>
       <c r="I8" s="3">
-        <v>0.128</v>
+        <v>0.074</v>
       </c>
       <c r="J8" s="3">
-        <v>0.171</v>
+        <v>0.097</v>
       </c>
       <c r="K8" s="3">
-        <v>0.181</v>
+        <v>0.102</v>
       </c>
       <c r="L8" s="3">
-        <v>0.125</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="M8" s="3">
-        <v>0.08799999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N8" s="3">
-        <v>0.054</v>
+        <v>0.08</v>
       </c>
       <c r="O8" s="3">
-        <v>0.041</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="P8" s="3">
-        <v>0.031</v>
+        <v>0.064</v>
       </c>
       <c r="Q8" s="3">
-        <v>0.031</v>
+        <v>0.051</v>
       </c>
       <c r="R8" s="3">
-        <v>0.014</v>
+        <v>0.036</v>
       </c>
       <c r="S8" s="3">
+        <v>0.037</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0.024</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0.025</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0.023</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0.011</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0.003</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0.005</v>
+      </c>
+      <c r="AD8" s="3">
         <v>0.017</v>
       </c>
-      <c r="T8" s="3">
-        <v>0.006</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0.003</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0.004</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>0.016</v>
-      </c>
       <c r="AE8" s="3">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="AF8" s="3">
-        <v>0.102</v>
+        <v>0.093</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.23</v>
+        <v>0.167</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.7070000000000001</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9" spans="1:34">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1">
-        <v>1992</v>
+        <v>1915</v>
       </c>
       <c r="C9" s="1">
-        <v>25.184</v>
+        <v>22.396</v>
       </c>
       <c r="D9" s="1">
-        <v>12.592</v>
+        <v>11.198</v>
       </c>
       <c r="E9" s="3">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F9" s="3">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="G9" s="3">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="H9" s="3">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="I9" s="3">
-        <v>0.053</v>
+        <v>0.03</v>
       </c>
       <c r="J9" s="3">
-        <v>0.106</v>
+        <v>0.044</v>
       </c>
       <c r="K9" s="3">
-        <v>0.13</v>
+        <v>0.043</v>
       </c>
       <c r="L9" s="3">
-        <v>0.148</v>
+        <v>0.073</v>
       </c>
       <c r="M9" s="3">
-        <v>0.124</v>
+        <v>0.075</v>
       </c>
       <c r="N9" s="3">
-        <v>0.099</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="O9" s="3">
-        <v>0.07099999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="P9" s="3">
-        <v>0.054</v>
+        <v>0.079</v>
       </c>
       <c r="Q9" s="3">
-        <v>0.04</v>
+        <v>0.076</v>
       </c>
       <c r="R9" s="3">
+        <v>0.055</v>
+      </c>
+      <c r="S9" s="3">
+        <v>0.067</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="U9" s="3">
+        <v>0.058</v>
+      </c>
+      <c r="V9" s="3">
         <v>0.033</v>
       </c>
-      <c r="S9" s="3">
-        <v>0.022</v>
-      </c>
-      <c r="T9" s="3">
-        <v>0.017</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
+        <v>0.039</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0.023</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>0.018</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>0.027</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>0.023</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>0.007</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>0.003</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>0.006</v>
+      </c>
+      <c r="AE9" s="3">
         <v>0.016</v>
       </c>
-      <c r="V9" s="3">
-        <v>0.016</v>
-      </c>
-      <c r="W9" s="3">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0.006</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>0.004</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>0.005</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>0.004</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>0.019</v>
-      </c>
       <c r="AF9" s="3">
-        <v>0.045</v>
+        <v>0.032</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.098</v>
+        <v>0.062</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.482</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="10" spans="1:34">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1">
-        <v>1981</v>
+        <v>1933</v>
       </c>
       <c r="C10" s="1">
-        <v>24.474</v>
+        <v>23.396</v>
       </c>
       <c r="D10" s="1">
-        <v>12.237</v>
+        <v>11.698</v>
       </c>
       <c r="E10" s="3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F10" s="3">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="G10" s="3">
-        <v>0.008</v>
+        <v>0.017</v>
       </c>
       <c r="H10" s="3">
-        <v>0.019</v>
+        <v>0.029</v>
       </c>
       <c r="I10" s="3">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="J10" s="3">
-        <v>0.068</v>
+        <v>0.062</v>
       </c>
       <c r="K10" s="3">
-        <v>0.108</v>
+        <v>0.081</v>
       </c>
       <c r="L10" s="3">
-        <v>0.15</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="M10" s="3">
-        <v>0.08699999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="N10" s="3">
-        <v>0.143</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="O10" s="3">
-        <v>0.08</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="P10" s="3">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.043</v>
+        <v>0.056</v>
       </c>
       <c r="R10" s="3">
         <v>0.05</v>
       </c>
       <c r="S10" s="3">
-        <v>0.027</v>
+        <v>0.043</v>
       </c>
       <c r="T10" s="3">
-        <v>0.019</v>
+        <v>0.047</v>
       </c>
       <c r="U10" s="3">
-        <v>0.021</v>
+        <v>0.033</v>
       </c>
       <c r="V10" s="3">
-        <v>0.019</v>
+        <v>0.037</v>
       </c>
       <c r="W10" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.033</v>
       </c>
       <c r="X10" s="3">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="Y10" s="3">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="Z10" s="3">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="AA10" s="3">
         <v>0.003</v>
       </c>
       <c r="AB10" s="3">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="AC10" s="3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AD10" s="3">
-        <v>0.002</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="AE10" s="3">
-        <v>0.01</v>
+        <v>0.026</v>
       </c>
       <c r="AF10" s="3">
-        <v>0.029</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.07999999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.406</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="11" spans="1:34">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1">
-        <v>1908</v>
+        <v>1923</v>
       </c>
       <c r="C11" s="1">
-        <v>20.212</v>
+        <v>22.734</v>
       </c>
       <c r="D11" s="1">
-        <v>10.106</v>
+        <v>11.367</v>
       </c>
       <c r="E11" s="3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G11" s="3">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="H11" s="3">
-        <v>0.003</v>
+        <v>0.028</v>
       </c>
       <c r="I11" s="3">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="J11" s="3">
-        <v>0.013</v>
+        <v>0.048</v>
       </c>
       <c r="K11" s="3">
-        <v>0.029</v>
+        <v>0.056</v>
       </c>
       <c r="L11" s="3">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0.081</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0.095</v>
+      </c>
+      <c r="O11" s="3">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0.075</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.068</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0.068</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0.048</v>
+      </c>
+      <c r="T11" s="3">
         <v>0.044</v>
       </c>
-      <c r="M11" s="3">
-        <v>0.062</v>
-      </c>
-      <c r="N11" s="3">
-        <v>0.073</v>
-      </c>
-      <c r="O11" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="S11" s="3">
-        <v>0.076</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0.061</v>
-      </c>
       <c r="U11" s="3">
-        <v>0.065</v>
+        <v>0.049</v>
       </c>
       <c r="V11" s="3">
-        <v>0.049</v>
+        <v>0.041</v>
       </c>
       <c r="W11" s="3">
-        <v>0.04</v>
+        <v>0.031</v>
       </c>
       <c r="X11" s="3">
-        <v>0.044</v>
+        <v>0.018</v>
       </c>
       <c r="Y11" s="3">
-        <v>0.027</v>
+        <v>0.023</v>
       </c>
       <c r="Z11" s="3">
-        <v>0.039</v>
+        <v>0.01</v>
       </c>
       <c r="AA11" s="3">
-        <v>0.031</v>
+        <v>0.012</v>
       </c>
       <c r="AB11" s="3">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="AC11" s="3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AD11" s="3">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AE11" s="3">
-        <v>0.001</v>
+        <v>0.017</v>
       </c>
       <c r="AF11" s="3">
-        <v>0.004</v>
+        <v>0.045</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.012</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.098</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -5108,103 +5101,103 @@
         <v>13</v>
       </c>
       <c r="B12" s="1">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="C12" s="1">
-        <v>20.428</v>
+        <v>22.448</v>
       </c>
       <c r="D12" s="1">
-        <v>10.214</v>
+        <v>11.224</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G12" s="3">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.025</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.035</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0.045</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.062</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.081</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.063</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.073</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0.053</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0.053</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0.046</v>
+      </c>
+      <c r="U12" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="V12" s="3">
+        <v>0.044</v>
+      </c>
+      <c r="W12" s="3">
+        <v>0.045</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0.027</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>0.025</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>0.025</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="AC12" s="3">
         <v>0.001</v>
       </c>
-      <c r="H12" s="3">
-        <v>0.002</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0.006</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0.025</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0.025</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0.047</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0.083</v>
-      </c>
-      <c r="N12" s="3">
-        <v>0.078</v>
-      </c>
-      <c r="O12" s="3">
-        <v>0.09</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="R12" s="3">
-        <v>0.061</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0.059</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0.054</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0.061</v>
-      </c>
-      <c r="V12" s="3">
-        <v>0.057</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0.043</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0.037</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>0.031</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>0.031</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>0.022</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>0.018</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>0</v>
-      </c>
       <c r="AD12" s="3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AE12" s="3">
-        <v>0.001</v>
+        <v>0.014</v>
       </c>
       <c r="AF12" s="3">
-        <v>0.003</v>
+        <v>0.039</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.009000000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.106</v>
+        <v>0.262</v>
       </c>
     </row>
     <row r="13" spans="1:34">
@@ -5212,103 +5205,103 @@
         <v>14</v>
       </c>
       <c r="B13" s="1">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="C13" s="1">
-        <v>20.292</v>
+        <v>22.272</v>
       </c>
       <c r="D13" s="1">
-        <v>10.146</v>
+        <v>11.136</v>
       </c>
       <c r="E13" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F13" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G13" s="3">
-        <v>0.002</v>
+        <v>0.011</v>
       </c>
       <c r="H13" s="3">
-        <v>0.001</v>
+        <v>0.02</v>
       </c>
       <c r="I13" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.037</v>
       </c>
       <c r="J13" s="3">
-        <v>0.018</v>
+        <v>0.044</v>
       </c>
       <c r="K13" s="3">
+        <v>0.065</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.067</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.054</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0.073</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0.054</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0.065</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.038</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0.033</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.03</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="Z13" s="3">
         <v>0.031</v>
       </c>
-      <c r="L13" s="3">
-        <v>0.052</v>
-      </c>
-      <c r="M13" s="3">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0.077</v>
-      </c>
-      <c r="O13" s="3">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="P13" s="3">
-        <v>0.057</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="R13" s="3">
-        <v>0.068</v>
-      </c>
-      <c r="S13" s="3">
-        <v>0.076</v>
-      </c>
-      <c r="T13" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="U13" s="3">
-        <v>0.067</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0.049</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0.051</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0.024</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>0.044</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>0.038</v>
-      </c>
       <c r="AA13" s="3">
-        <v>0.024</v>
+        <v>0.014</v>
       </c>
       <c r="AB13" s="3">
         <v>0.016</v>
       </c>
       <c r="AC13" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AD13" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AE13" s="3">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="AF13" s="3">
-        <v>0.003</v>
+        <v>0.034</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.012</v>
+        <v>0.07100000000000001</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.113</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -5316,311 +5309,311 @@
         <v>16</v>
       </c>
       <c r="B14" s="1">
-        <v>1906</v>
+        <v>1912</v>
       </c>
       <c r="C14" s="1">
-        <v>19.946</v>
+        <v>22.058</v>
       </c>
       <c r="D14" s="1">
-        <v>9.973000000000001</v>
+        <v>11.029</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F14" s="3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="H14" s="3">
-        <v>0.002</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I14" s="3">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="J14" s="3">
-        <v>0.01</v>
+        <v>0.033</v>
       </c>
       <c r="K14" s="3">
-        <v>0.026</v>
+        <v>0.057</v>
       </c>
       <c r="L14" s="3">
+        <v>0.053</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0.065</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.073</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.073</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0.073</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0.065</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0.039</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0.032</v>
+      </c>
+      <c r="X14" s="3">
         <v>0.042</v>
       </c>
-      <c r="M14" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0.045</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0.073</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0.074</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0.055</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0.056</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0.044</v>
-      </c>
       <c r="Y14" s="3">
-        <v>0.048</v>
+        <v>0.034</v>
       </c>
       <c r="Z14" s="3">
         <v>0.028</v>
       </c>
       <c r="AA14" s="3">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="AB14" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0.003</v>
+      </c>
+      <c r="AE14" s="3">
         <v>0.011</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0.001</v>
-      </c>
       <c r="AF14" s="3">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.005</v>
+        <v>0.047</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.08299999999999999</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="15" spans="1:34">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1">
         <v>1902</v>
       </c>
       <c r="C15" s="1">
-        <v>19.772</v>
+        <v>21.418</v>
       </c>
       <c r="D15" s="1">
-        <v>9.885999999999999</v>
+        <v>10.709</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H15" s="3">
+        <v>0.008</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.017</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.039</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0.036</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.055</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0.061</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0.063</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0.067</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0.067</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0.048</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0.063</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0.055</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0.041</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0.047</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0.025</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="AC15" s="3">
         <v>0.001</v>
       </c>
-      <c r="I15" s="3">
+      <c r="AD15" s="3">
         <v>0.004</v>
       </c>
-      <c r="J15" s="3">
+      <c r="AE15" s="3">
+        <v>0.011</v>
+      </c>
+      <c r="AF15" s="3">
         <v>0.019</v>
       </c>
-      <c r="K15" s="3">
-        <v>0.025</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0.032</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0.054</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0.056</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0.062</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0.066</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0.066</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0.064</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0.067</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0.059</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0.048</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0.045</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>0.037</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>0.035</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>0.025</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>0.001</v>
-      </c>
       <c r="AG15" s="3">
-        <v>0.005</v>
+        <v>0.036</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.081</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="16" spans="1:34">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C16" s="1">
-        <v>19.718</v>
+        <v>21.734</v>
       </c>
       <c r="D16" s="1">
-        <v>9.859</v>
+        <v>10.867</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="G16" s="3">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H16" s="3">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I16" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.025</v>
       </c>
       <c r="J16" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="K16" s="3">
-        <v>0.014</v>
+        <v>0.04</v>
       </c>
       <c r="L16" s="3">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
       <c r="M16" s="3">
-        <v>0.058</v>
+        <v>0.055</v>
       </c>
       <c r="N16" s="3">
-        <v>0.049</v>
+        <v>0.073</v>
       </c>
       <c r="O16" s="3">
-        <v>0.07099999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="P16" s="3">
+        <v>0.066</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="R16" s="3">
+        <v>0.057</v>
+      </c>
+      <c r="S16" s="3">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="T16" s="3">
         <v>0.06900000000000001</v>
       </c>
-      <c r="Q16" s="3">
-        <v>0.076</v>
-      </c>
-      <c r="R16" s="3">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="S16" s="3">
-        <v>0.059</v>
-      </c>
-      <c r="T16" s="3">
-        <v>0.073</v>
-      </c>
       <c r="U16" s="3">
-        <v>0.067</v>
+        <v>0.051</v>
       </c>
       <c r="V16" s="3">
-        <v>0.068</v>
+        <v>0.053</v>
       </c>
       <c r="W16" s="3">
-        <v>0.056</v>
+        <v>0.036</v>
       </c>
       <c r="X16" s="3">
-        <v>0.059</v>
+        <v>0.039</v>
       </c>
       <c r="Y16" s="3">
-        <v>0.045</v>
+        <v>0.034</v>
       </c>
       <c r="Z16" s="3">
-        <v>0.043</v>
+        <v>0.031</v>
       </c>
       <c r="AA16" s="3">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="AB16" s="3">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="AC16" s="3">
         <v>0</v>
       </c>
       <c r="AD16" s="3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AE16" s="3">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AF16" s="3">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.047</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.07200000000000001</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="17" spans="1:34">
@@ -5628,28 +5621,28 @@
         <v>19</v>
       </c>
       <c r="B17" s="1">
-        <v>1898</v>
+        <v>1872</v>
       </c>
       <c r="C17" s="1">
-        <v>19.316</v>
+        <v>19.444</v>
       </c>
       <c r="D17" s="1">
-        <v>9.657999999999999</v>
+        <v>9.722</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
       </c>
       <c r="F17" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G17" s="3">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H17" s="3">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="I17" s="3">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="J17" s="3">
         <v>0.012</v>
@@ -5658,73 +5651,73 @@
         <v>0.021</v>
       </c>
       <c r="L17" s="3">
-        <v>0.031</v>
+        <v>0.027</v>
       </c>
       <c r="M17" s="3">
+        <v>0.037</v>
+      </c>
+      <c r="N17" s="3">
+        <v>0.037</v>
+      </c>
+      <c r="O17" s="3">
+        <v>0.046</v>
+      </c>
+      <c r="P17" s="3">
+        <v>0.061</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>0.054</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0.056</v>
+      </c>
+      <c r="S17" s="3">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="T17" s="3">
+        <v>0.057</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0.081</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="W17" s="3">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0.066</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0.062</v>
+      </c>
+      <c r="AA17" s="3">
+        <v>0.053</v>
+      </c>
+      <c r="AB17" s="3">
         <v>0.036</v>
       </c>
-      <c r="N17" s="3">
-        <v>0.043</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0.056</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="AC17" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>0.004</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>0.007</v>
+      </c>
+      <c r="AG17" s="3">
+        <v>0.017</v>
+      </c>
+      <c r="AH17" s="3">
         <v>0.077</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>0.064</v>
-      </c>
-      <c r="R17" s="3">
-        <v>0.079</v>
-      </c>
-      <c r="S17" s="3">
-        <v>0.065</v>
-      </c>
-      <c r="T17" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="U17" s="3">
-        <v>0.064</v>
-      </c>
-      <c r="V17" s="3">
-        <v>0.077</v>
-      </c>
-      <c r="W17" s="3">
-        <v>0.065</v>
-      </c>
-      <c r="X17" s="3">
-        <v>0.056</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>0.048</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>0.047</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>0.042</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>0.029</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AF17" s="3">
-        <v>0.003</v>
-      </c>
-      <c r="AG17" s="3">
-        <v>0.008</v>
-      </c>
-      <c r="AH17" s="3">
-        <v>0.07200000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:34">
@@ -5732,103 +5725,103 @@
         <v>20</v>
       </c>
       <c r="B18" s="1">
-        <v>1881</v>
+        <v>1868</v>
       </c>
       <c r="C18" s="1">
-        <v>18.518</v>
+        <v>19.426</v>
       </c>
       <c r="D18" s="1">
-        <v>9.259</v>
+        <v>9.712999999999999</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
       </c>
       <c r="F18" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
       </c>
       <c r="H18" s="3">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="I18" s="3">
+        <v>0.006</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.016</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0.027</v>
+      </c>
+      <c r="M18" s="3">
+        <v>0.018</v>
+      </c>
+      <c r="N18" s="3">
+        <v>0.047</v>
+      </c>
+      <c r="O18" s="3">
+        <v>0.048</v>
+      </c>
+      <c r="P18" s="3">
+        <v>0.048</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>0.052</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0.073</v>
+      </c>
+      <c r="S18" s="3">
+        <v>0.059</v>
+      </c>
+      <c r="T18" s="3">
+        <v>0.074</v>
+      </c>
+      <c r="U18" s="3">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0.083</v>
+      </c>
+      <c r="W18" s="3">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0.074</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0.068</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0.067</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>0.044</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>0.037</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>0.002</v>
       </c>
-      <c r="J18" s="3">
-        <v>0.008</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0.011</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0.021</v>
-      </c>
-      <c r="M18" s="3">
-        <v>0.031</v>
-      </c>
-      <c r="N18" s="3">
-        <v>0.041</v>
-      </c>
-      <c r="O18" s="3">
-        <v>0.038</v>
-      </c>
-      <c r="P18" s="3">
-        <v>0.056</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>0.061</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="S18" s="3">
-        <v>0.076</v>
-      </c>
-      <c r="T18" s="3">
-        <v>0.065</v>
-      </c>
-      <c r="U18" s="3">
-        <v>0.083</v>
-      </c>
-      <c r="V18" s="3">
-        <v>0.068</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0.092</v>
-      </c>
-      <c r="X18" s="3">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>0.062</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>0.049</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>0.055</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
       <c r="AE18" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AF18" s="3">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.003</v>
+        <v>0.012</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.043</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="19" spans="1:34">
@@ -5836,13 +5829,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="1">
-        <v>1871</v>
+        <v>1855</v>
       </c>
       <c r="C19" s="1">
-        <v>17.808</v>
+        <v>18.566</v>
       </c>
       <c r="D19" s="1">
-        <v>8.904</v>
+        <v>9.282999999999999</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
@@ -5851,70 +5844,70 @@
         <v>0</v>
       </c>
       <c r="G19" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H19" s="3">
         <v>0.001</v>
       </c>
       <c r="I19" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="J19" s="3">
-        <v>0.003</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K19" s="3">
-        <v>0.007</v>
+        <v>0.015</v>
       </c>
       <c r="L19" s="3">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="M19" s="3">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="N19" s="3">
-        <v>0.029</v>
+        <v>0.019</v>
       </c>
       <c r="O19" s="3">
-        <v>0.031</v>
+        <v>0.035</v>
       </c>
       <c r="P19" s="3">
-        <v>0.042</v>
+        <v>0.037</v>
       </c>
       <c r="Q19" s="3">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="R19" s="3">
-        <v>0.056</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="S19" s="3">
+        <v>0.059</v>
+      </c>
+      <c r="T19" s="3">
+        <v>0.076</v>
+      </c>
+      <c r="U19" s="3">
+        <v>0.063</v>
+      </c>
+      <c r="V19" s="3">
         <v>0.082</v>
       </c>
-      <c r="T19" s="3">
-        <v>0.074</v>
-      </c>
-      <c r="U19" s="3">
-        <v>0.059</v>
-      </c>
-      <c r="V19" s="3">
-        <v>0.075</v>
-      </c>
       <c r="W19" s="3">
+        <v>0.073</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="Y19" s="3">
         <v>0.08</v>
       </c>
-      <c r="X19" s="3">
-        <v>0.089</v>
-      </c>
-      <c r="Y19" s="3">
-        <v>0.079</v>
-      </c>
       <c r="Z19" s="3">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AA19" s="3">
-        <v>0.07000000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="AB19" s="3">
-        <v>0.056</v>
+        <v>0.061</v>
       </c>
       <c r="AC19" s="3">
         <v>0</v>
@@ -5923,16 +5916,16 @@
         <v>0</v>
       </c>
       <c r="AE19" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AF19" s="3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.029</v>
+        <v>0.03999999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -5940,13 +5933,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="1">
-        <v>1870</v>
+        <v>1846</v>
       </c>
       <c r="C20" s="1">
-        <v>17.756</v>
+        <v>17.892</v>
       </c>
       <c r="D20" s="1">
-        <v>8.878</v>
+        <v>8.946</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -5955,70 +5948,70 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H20" s="3">
         <v>0.001</v>
       </c>
       <c r="I20" s="3">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="J20" s="3">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="K20" s="3">
         <v>0.007</v>
       </c>
       <c r="L20" s="3">
-        <v>0.008999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="M20" s="3">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="N20" s="3">
-        <v>0.037</v>
+        <v>0.028</v>
       </c>
       <c r="O20" s="3">
-        <v>0.047</v>
+        <v>0.032</v>
       </c>
       <c r="P20" s="3">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="Q20" s="3">
-        <v>0.057</v>
+        <v>0.048</v>
       </c>
       <c r="R20" s="3">
-        <v>0.054</v>
+        <v>0.038</v>
       </c>
       <c r="S20" s="3">
-        <v>0.064</v>
+        <v>0.055</v>
       </c>
       <c r="T20" s="3">
-        <v>0.064</v>
+        <v>0.061</v>
       </c>
       <c r="U20" s="3">
-        <v>0.068</v>
+        <v>0.06</v>
       </c>
       <c r="V20" s="3">
-        <v>0.065</v>
+        <v>0.061</v>
       </c>
       <c r="W20" s="3">
-        <v>0.08400000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="X20" s="3">
-        <v>0.079</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Y20" s="3">
-        <v>0.07099999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Z20" s="3">
-        <v>0.08400000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AA20" s="3">
-        <v>0.08500000000000001</v>
+        <v>0.097</v>
       </c>
       <c r="AB20" s="3">
-        <v>0.061</v>
+        <v>0.076</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
@@ -6027,16 +6020,16 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AF20" s="3">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="1:34">
@@ -6044,13 +6037,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>1863</v>
+        <v>1844</v>
       </c>
       <c r="C21" s="1">
-        <v>17.28</v>
+        <v>17.736</v>
       </c>
       <c r="D21" s="1">
-        <v>8.640000000000001</v>
+        <v>8.868</v>
       </c>
       <c r="E21" s="3">
         <v>0</v>
@@ -6062,105 +6055,105 @@
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="I21" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.008</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0.014</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0.012</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0.017</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0.021</v>
+      </c>
+      <c r="P21" s="3">
+        <v>0.031</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>0.032</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0.046</v>
+      </c>
+      <c r="S21" s="3">
+        <v>0.042</v>
+      </c>
+      <c r="T21" s="3">
+        <v>0.052</v>
+      </c>
+      <c r="U21" s="3">
+        <v>0.078</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0.082</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0.078</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>0.096</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>0.096</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3">
         <v>0.002</v>
       </c>
-      <c r="J21" s="3">
-        <v>0.006</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="AG21" s="3">
         <v>0.003</v>
       </c>
-      <c r="L21" s="3">
-        <v>0.015</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0.019</v>
-      </c>
-      <c r="N21" s="3">
-        <v>0.019</v>
-      </c>
-      <c r="O21" s="3">
-        <v>0.024</v>
-      </c>
-      <c r="P21" s="3">
-        <v>0.046</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>0.035</v>
-      </c>
-      <c r="R21" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="S21" s="3">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="T21" s="3">
-        <v>0.056</v>
-      </c>
-      <c r="U21" s="3">
-        <v>0.068</v>
-      </c>
-      <c r="V21" s="3">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="W21" s="3">
-        <v>0.073</v>
-      </c>
-      <c r="X21" s="3">
-        <v>0.097</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>0.083</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>0.094</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>0.079</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>0.002</v>
-      </c>
       <c r="AH21" s="3">
-        <v>0.026</v>
+        <v>0.03700000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:34">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="1">
-        <v>1848</v>
+        <v>1840</v>
       </c>
       <c r="C22" s="1">
-        <v>16.646</v>
+        <v>17.372</v>
       </c>
       <c r="D22" s="1">
-        <v>8.323</v>
+        <v>8.686</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -6169,96 +6162,96 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="J22" s="3">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="K22" s="3">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="L22" s="3">
-        <v>0.004</v>
+        <v>0.011</v>
       </c>
       <c r="M22" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0.016</v>
+      </c>
+      <c r="O22" s="3">
         <v>0.017</v>
       </c>
-      <c r="N22" s="3">
-        <v>0.011</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0.023</v>
-      </c>
       <c r="P22" s="3">
-        <v>0.037</v>
+        <v>0.029</v>
       </c>
       <c r="Q22" s="3">
-        <v>0.036</v>
+        <v>0.031</v>
       </c>
       <c r="R22" s="3">
-        <v>0.047</v>
+        <v>0.041</v>
       </c>
       <c r="S22" s="3">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="T22" s="3">
         <v>0.058</v>
       </c>
       <c r="U22" s="3">
-        <v>0.055</v>
+        <v>0.061</v>
       </c>
       <c r="V22" s="3">
-        <v>0.063</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="W22" s="3">
-        <v>0.074</v>
+        <v>0.073</v>
       </c>
       <c r="X22" s="3">
-        <v>0.083</v>
+        <v>0.108</v>
       </c>
       <c r="Y22" s="3">
         <v>0.102</v>
       </c>
       <c r="Z22" s="3">
-        <v>0.117</v>
+        <v>0.093</v>
       </c>
       <c r="AA22" s="3">
-        <v>0.115</v>
+        <v>0.114</v>
       </c>
       <c r="AB22" s="3">
-        <v>0.114</v>
+        <v>0.108</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
       <c r="AD22" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AE22" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AF22" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG22" s="3">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.007</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="23" spans="1:34">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1">
-        <v>1849</v>
+        <v>1834</v>
       </c>
       <c r="C23" s="1">
-        <v>16.36</v>
+        <v>17.352</v>
       </c>
       <c r="D23" s="1">
-        <v>8.18</v>
+        <v>8.676</v>
       </c>
       <c r="E23" s="3">
         <v>0</v>
@@ -6270,64 +6263,64 @@
         <v>0</v>
       </c>
       <c r="H23" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="J23" s="3">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="K23" s="3">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="L23" s="3">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="M23" s="3">
-        <v>0.011</v>
+        <v>0.015</v>
       </c>
       <c r="N23" s="3">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="O23" s="3">
         <v>0.021</v>
       </c>
       <c r="P23" s="3">
-        <v>0.026</v>
+        <v>0.016</v>
       </c>
       <c r="Q23" s="3">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="R23" s="3">
-        <v>0.033</v>
+        <v>0.048</v>
       </c>
       <c r="S23" s="3">
+        <v>0.053</v>
+      </c>
+      <c r="T23" s="3">
         <v>0.044</v>
       </c>
-      <c r="T23" s="3">
-        <v>0.073</v>
-      </c>
       <c r="U23" s="3">
-        <v>0.062</v>
+        <v>0.057</v>
       </c>
       <c r="V23" s="3">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="W23" s="3">
-        <v>0.076</v>
+        <v>0.067</v>
       </c>
       <c r="X23" s="3">
-        <v>0.092</v>
+        <v>0.101</v>
       </c>
       <c r="Y23" s="3">
-        <v>0.118</v>
+        <v>0.095</v>
       </c>
       <c r="Z23" s="3">
-        <v>0.096</v>
+        <v>0.114</v>
       </c>
       <c r="AA23" s="3">
-        <v>0.108</v>
+        <v>0.125</v>
       </c>
       <c r="AB23" s="3">
         <v>0.123</v>
@@ -6342,13 +6335,13 @@
         <v>0</v>
       </c>
       <c r="AF23" s="3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AG23" s="3">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AH23" s="3">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -6356,103 +6349,103 @@
         <v>26</v>
       </c>
       <c r="B24" s="1">
-        <v>1846</v>
+        <v>1833</v>
       </c>
       <c r="C24" s="1">
-        <v>16.282</v>
+        <v>17.066</v>
       </c>
       <c r="D24" s="1">
-        <v>8.141</v>
+        <v>8.532999999999999</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="I24" s="3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="J24" s="3">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="K24" s="3">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="L24" s="3">
-        <v>0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M24" s="3">
         <v>0.013</v>
       </c>
       <c r="N24" s="3">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="O24" s="3">
-        <v>0.017</v>
+        <v>0.024</v>
       </c>
       <c r="P24" s="3">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="Q24" s="3">
-        <v>0.026</v>
+        <v>0.019</v>
       </c>
       <c r="R24" s="3">
-        <v>0.047</v>
+        <v>0.035</v>
       </c>
       <c r="S24" s="3">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="T24" s="3">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
       <c r="U24" s="3">
-        <v>0.052</v>
+        <v>0.061</v>
       </c>
       <c r="V24" s="3">
-        <v>0.067</v>
+        <v>0.056</v>
       </c>
       <c r="W24" s="3">
-        <v>0.06900000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X24" s="3">
-        <v>0.081</v>
+        <v>0.06</v>
       </c>
       <c r="Y24" s="3">
-        <v>0.089</v>
+        <v>0.11</v>
       </c>
       <c r="Z24" s="3">
-        <v>0.115</v>
+        <v>0.096</v>
       </c>
       <c r="AA24" s="3">
-        <v>0.117</v>
+        <v>0.123</v>
       </c>
       <c r="AB24" s="3">
-        <v>0.17</v>
+        <v>0.177</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
       <c r="AD24" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AE24" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AF24" s="3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AG24" s="3">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="AH24" s="3">
-        <v>0.018</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="25" spans="1:34">
@@ -6460,13 +6453,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="1">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="C25" s="1">
-        <v>15.504</v>
+        <v>16.712</v>
       </c>
       <c r="D25" s="1">
-        <v>7.752</v>
+        <v>8.356</v>
       </c>
       <c r="E25" s="3">
         <v>0</v>
@@ -6475,70 +6468,70 @@
         <v>0</v>
       </c>
       <c r="G25" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H25" s="3">
+        <v>0.002</v>
+      </c>
+      <c r="I25" s="3">
         <v>0.001</v>
       </c>
-      <c r="I25" s="3">
-        <v>0</v>
-      </c>
       <c r="J25" s="3">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="K25" s="3">
         <v>0.004</v>
       </c>
       <c r="L25" s="3">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M25" s="3">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="N25" s="3">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="O25" s="3">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
       <c r="P25" s="3">
         <v>0.02</v>
       </c>
       <c r="Q25" s="3">
-        <v>0.026</v>
+        <v>0.027</v>
       </c>
       <c r="R25" s="3">
-        <v>0.018</v>
+        <v>0.025</v>
       </c>
       <c r="S25" s="3">
-        <v>0.036</v>
+        <v>0.045</v>
       </c>
       <c r="T25" s="3">
-        <v>0.049</v>
+        <v>0.035</v>
       </c>
       <c r="U25" s="3">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="V25" s="3">
-        <v>0.051</v>
+        <v>0.059</v>
       </c>
       <c r="W25" s="3">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="X25" s="3">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="Y25" s="3">
         <v>0.082</v>
       </c>
-      <c r="Y25" s="3">
-        <v>0.096</v>
-      </c>
       <c r="Z25" s="3">
-        <v>0.106</v>
+        <v>0.109</v>
       </c>
       <c r="AA25" s="3">
         <v>0.139</v>
       </c>
       <c r="AB25" s="3">
-        <v>0.227</v>
+        <v>0.208</v>
       </c>
       <c r="AC25" s="3">
         <v>0</v>
@@ -6547,16 +6540,16 @@
         <v>0</v>
       </c>
       <c r="AE25" s="3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AF25" s="3">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="AG25" s="3">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="AH25" s="3">
-        <v>0.006</v>
+        <v>0.019</v>
       </c>
     </row>
   </sheetData>
